--- a/bill-docs-k7m2v9/AllPro_Tax_2025.xlsx
+++ b/bill-docs-k7m2v9/AllPro_Tax_2025.xlsx
@@ -8,11 +8,12 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overall Writeoffs" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RAW_2025" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CATEGORIZED_2025" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="P&amp;L_2025" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MONTHLY_2025" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LABOR_2025" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RECON_2025" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RAW_2025" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CATEGORIZED_2025" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="P&amp;L_2025" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MONTHLY_2025" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LABOR_2025" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -459,7 +460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K22"/>
+  <dimension ref="A1:K19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -488,324 +489,294 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>1099 Employees</t>
+          <t>Payroll</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Bryan</t>
+          <t>Payroll Total</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>29578.02</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Jameson</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="n">
-        <v>0</v>
+        <v>49194.49</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Casey</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="n">
-        <v>19616.47</v>
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>Month</t>
+        </is>
+      </c>
+      <c r="B6" s="1" t="inlineStr">
+        <is>
+          <t>Deposits</t>
+        </is>
+      </c>
+      <c r="C6" s="1" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="inlineStr">
+        <is>
+          <t>Bill Pay</t>
+        </is>
+      </c>
+      <c r="G6" s="1" t="inlineStr">
+        <is>
+          <t>Difference</t>
+        </is>
+      </c>
+      <c r="H6" s="1" t="inlineStr">
+        <is>
+          <t>Car Write off</t>
+        </is>
+      </c>
+      <c r="I6" s="1" t="inlineStr">
+        <is>
+          <t>Difference</t>
+        </is>
+      </c>
+      <c r="J6" s="1" t="inlineStr">
+        <is>
+          <t>Payroll</t>
+        </is>
+      </c>
+      <c r="K6" s="1" t="inlineStr">
+        <is>
+          <t>Total Loss</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Tony</t>
+          <t>January</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
+        <v>7113.78</v>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>11377.59</v>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>8590</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>February</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="C8" s="2" t="n">
+        <v>25311.08</v>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>7205.5</v>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>Month</t>
-        </is>
-      </c>
-      <c r="B9" s="1" t="inlineStr">
-        <is>
-          <t>Deposits</t>
-        </is>
-      </c>
-      <c r="C9" s="1" t="inlineStr">
-        <is>
-          <t>Expenses</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="inlineStr">
-        <is>
-          <t>Bill Pay</t>
-        </is>
-      </c>
-      <c r="G9" s="1" t="inlineStr">
-        <is>
-          <t>Difference</t>
-        </is>
-      </c>
-      <c r="H9" s="1" t="inlineStr">
-        <is>
-          <t>Car Write off</t>
-        </is>
-      </c>
-      <c r="I9" s="1" t="inlineStr">
-        <is>
-          <t>Difference</t>
-        </is>
-      </c>
-      <c r="J9" s="1" t="inlineStr">
-        <is>
-          <t>1099</t>
-        </is>
-      </c>
-      <c r="K9" s="1" t="inlineStr">
-        <is>
-          <t>Total Loss</t>
-        </is>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>March</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>3575</v>
+      </c>
+      <c r="C9" s="2" t="n">
+        <v>22238.06</v>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>4008</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>January</t>
+          <t>April</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>7113.78</v>
+        <v>15160</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>11377.59</v>
+        <v>19902.05</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>8590</v>
+        <v>5128.23</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>February</t>
+          <t>May</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>0</v>
+        <v>99479.82000000001</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>25311.08</v>
+        <v>7739.21</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>7205.5</v>
+        <v>2350</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>March</t>
+          <t>June</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>3575</v>
+        <v>8705</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>22238.06</v>
+        <v>9820.15</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>4008</v>
+        <v>2155.35</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>April</t>
+          <t>July</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>15160</v>
+        <v>29245.94</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>19902.05</v>
+        <v>13960.55</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>5128.23</v>
+        <v>6482.06</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>May</t>
+          <t>August</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>99479.82000000001</v>
+        <v>40112.38</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>7739.21</v>
+        <v>5191.33</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>2350</v>
+        <v>2658.02</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>June</t>
+          <t>September</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>8705</v>
+        <v>38566.18</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>9820.15</v>
+        <v>5088.45</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>2155.35</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>July</t>
+          <t>October</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>29245.94</v>
+        <v>33110.82</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>13960.55</v>
+        <v>16792.53</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>6482.06</v>
+        <v>7614</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>August</t>
+          <t>November</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>40112.38</v>
+        <v>46059.53</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>5191.33</v>
+        <v>2446.6</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>2658.02</v>
+        <v>210</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>September</t>
+          <t>December</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>38566.18</v>
+        <v>68733.48</v>
       </c>
       <c r="C18" s="2" t="n">
-        <v>5088.45</v>
+        <v>1477.77</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>1400</v>
+        <v>1393.33</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>October</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="n">
-        <v>33110.82</v>
-      </c>
-      <c r="C19" s="2" t="n">
-        <v>16792.53</v>
-      </c>
-      <c r="D19" s="2" t="n">
-        <v>7614</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>November</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="n">
-        <v>46059.53</v>
-      </c>
-      <c r="C20" s="2" t="n">
-        <v>2446.6</v>
-      </c>
-      <c r="D20" s="2" t="n">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>December</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="n">
-        <v>68733.48</v>
-      </c>
-      <c r="C21" s="2" t="n">
-        <v>1477.77</v>
-      </c>
-      <c r="D21" s="2" t="n">
-        <v>1393.33</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="1" t="inlineStr">
+      <c r="A19" s="1" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B22" s="3">
-        <f>SUM(B10:B21)</f>
-        <v/>
-      </c>
-      <c r="C22" s="3">
-        <f>SUM(C10:C21)</f>
-        <v/>
-      </c>
-      <c r="D22" s="3">
-        <f>SUM(D10:D21)</f>
-        <v/>
-      </c>
-      <c r="G22" s="3">
-        <f>B22-C22-D22</f>
-        <v/>
-      </c>
-      <c r="H22" s="3" t="n">
+      <c r="B19" s="3">
+        <f>SUM(B7:B18)</f>
+        <v/>
+      </c>
+      <c r="C19" s="3">
+        <f>SUM(C7:C18)</f>
+        <v/>
+      </c>
+      <c r="D19" s="3">
+        <f>SUM(D7:D18)</f>
+        <v/>
+      </c>
+      <c r="G19" s="3">
+        <f>B19-C19-D19</f>
+        <v/>
+      </c>
+      <c r="H19" s="3" t="n">
         <v>20676.13</v>
       </c>
-      <c r="I22" s="3">
-        <f>G22-H22</f>
-        <v/>
-      </c>
-      <c r="J22" s="3">
-        <f>SUM(B4:B7)</f>
-        <v/>
-      </c>
-      <c r="K22" s="3">
-        <f>I22-J22</f>
+      <c r="I19" s="3">
+        <f>G19-H19</f>
+        <v/>
+      </c>
+      <c r="J19" s="3">
+        <f>B4</f>
+        <v/>
+      </c>
+      <c r="K19" s="3">
+        <f>I19-J19</f>
         <v/>
       </c>
     </row>
@@ -815,6 +786,136 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Year</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Counted Transactions</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Total Credits Counted</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>389861.93</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Total Debits Counted</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>219602.66</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Sum of All Amounts Counted</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>609464.59</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Revenue Group Total</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>369331.93</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>COGS Group Total</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>49832.74</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Expense Group Total</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>140707.12</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Non-Deductible Group Total</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>49592.8</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Net Income (Revenue-COGS-Expense)</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>178792.07</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -11206,7 +11307,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -11224,7 +11325,6 @@
     <col width="16" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
     <col width="28" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
     <col width="70" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
@@ -11274,11 +11374,6 @@
           <t>Override Note</t>
         </is>
       </c>
-      <c r="J1" s="4" t="inlineStr">
-        <is>
-          <t>Contractor</t>
-        </is>
-      </c>
       <c r="L1" s="6" t="inlineStr">
         <is>
           <t>WARNING: Changing Final Group may impact tax reporting. Confirm with tax professional.</t>
@@ -11321,7 +11416,6 @@
         <v/>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="5" t="n">
@@ -11359,7 +11453,6 @@
         <v/>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="5" t="n">
@@ -11397,11 +11490,6 @@
         <v/>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Bryan</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="n">
@@ -11439,11 +11527,6 @@
         <v/>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Casey</t>
-        </is>
-      </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="n">
@@ -11481,7 +11564,6 @@
         <v/>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="5" t="n">
@@ -11519,7 +11601,6 @@
         <v/>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="5" t="n">
@@ -11557,7 +11638,6 @@
         <v/>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="5" t="n">
@@ -11595,7 +11675,6 @@
         <v/>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="5" t="n">
@@ -11633,7 +11712,6 @@
         <v/>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="n">
@@ -11671,7 +11749,6 @@
         <v/>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="5" t="n">
@@ -11709,11 +11786,6 @@
         <v/>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>Bryan</t>
-        </is>
-      </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="n">
@@ -11751,7 +11823,6 @@
         <v/>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="5" t="n">
@@ -11789,7 +11860,6 @@
         <v/>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="5" t="n">
@@ -11827,11 +11897,6 @@
         <v/>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>Bryan</t>
-        </is>
-      </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="n">
@@ -11869,11 +11934,6 @@
         <v/>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>Casey</t>
-        </is>
-      </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="n">
@@ -11911,7 +11971,6 @@
         <v/>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="5" t="n">
@@ -11949,7 +12008,6 @@
         <v/>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="5" t="n">
@@ -11987,7 +12045,6 @@
         <v/>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="5" t="n">
@@ -12025,7 +12082,6 @@
         <v/>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="5" t="n">
@@ -12063,7 +12119,6 @@
         <v/>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="5" t="n">
@@ -12101,7 +12156,6 @@
         <v/>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="5" t="n">
@@ -12139,7 +12193,6 @@
         <v/>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="5" t="n">
@@ -12177,7 +12230,6 @@
         <v/>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="5" t="n">
@@ -12215,7 +12267,6 @@
         <v/>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="5" t="n">
@@ -12253,7 +12304,6 @@
         <v/>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="5" t="n">
@@ -12291,7 +12341,6 @@
         <v/>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="5" t="n">
@@ -12329,7 +12378,6 @@
         <v/>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="5" t="n">
@@ -12367,7 +12415,6 @@
         <v/>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="5" t="n">
@@ -12405,7 +12452,6 @@
         <v/>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="5" t="n">
@@ -12443,7 +12489,6 @@
         <v/>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="5" t="n">
@@ -12481,7 +12526,6 @@
         <v/>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="5" t="n">
@@ -12519,7 +12563,6 @@
         <v/>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="5" t="n">
@@ -12557,7 +12600,6 @@
         <v/>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="5" t="n">
@@ -12595,7 +12637,6 @@
         <v/>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="5" t="n">
@@ -12633,7 +12674,6 @@
         <v/>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="5" t="n">
@@ -12671,7 +12711,6 @@
         <v/>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="5" t="n">
@@ -12709,7 +12748,6 @@
         <v/>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="5" t="n">
@@ -12747,7 +12785,6 @@
         <v/>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="5" t="n">
@@ -12785,11 +12822,6 @@
         <v/>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>Bryan</t>
-        </is>
-      </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="n">
@@ -12827,11 +12859,6 @@
         <v/>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>Casey</t>
-        </is>
-      </c>
     </row>
     <row r="42">
       <c r="A42" s="5" t="n">
@@ -12869,7 +12896,6 @@
         <v/>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="5" t="n">
@@ -12907,7 +12933,6 @@
         <v/>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="5" t="n">
@@ -12945,7 +12970,6 @@
         <v/>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="5" t="n">
@@ -12983,7 +13007,6 @@
         <v/>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="5" t="n">
@@ -13021,7 +13044,6 @@
         <v/>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="5" t="n">
@@ -13059,11 +13081,6 @@
         <v/>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>Bryan</t>
-        </is>
-      </c>
     </row>
     <row r="48">
       <c r="A48" s="5" t="n">
@@ -13101,11 +13118,6 @@
         <v/>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>Casey</t>
-        </is>
-      </c>
     </row>
     <row r="49">
       <c r="A49" s="5" t="n">
@@ -13143,7 +13155,6 @@
         <v/>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="5" t="n">
@@ -13181,7 +13192,6 @@
         <v/>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="5" t="n">
@@ -13219,7 +13229,6 @@
         <v/>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="5" t="n">
@@ -13257,7 +13266,6 @@
         <v/>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="5" t="n">
@@ -13295,7 +13303,6 @@
         <v/>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="5" t="n">
@@ -13333,7 +13340,6 @@
         <v/>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="5" t="n">
@@ -13371,11 +13377,6 @@
         <v/>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>Bryan</t>
-        </is>
-      </c>
     </row>
     <row r="56">
       <c r="A56" s="5" t="n">
@@ -13413,11 +13414,6 @@
         <v/>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>Casey</t>
-        </is>
-      </c>
     </row>
     <row r="57">
       <c r="A57" s="5" t="n">
@@ -13455,7 +13451,6 @@
         <v/>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="5" t="n">
@@ -13493,7 +13488,6 @@
         <v/>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="5" t="n">
@@ -13531,7 +13525,6 @@
         <v/>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="5" t="n">
@@ -13569,7 +13562,6 @@
         <v/>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="5" t="n">
@@ -13607,7 +13599,6 @@
         <v/>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="5" t="n">
@@ -13645,7 +13636,6 @@
         <v/>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="5" t="n">
@@ -13683,7 +13673,6 @@
         <v/>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="5" t="n">
@@ -13721,7 +13710,6 @@
         <v/>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="5" t="n">
@@ -13759,7 +13747,6 @@
         <v/>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="5" t="n">
@@ -13797,7 +13784,6 @@
         <v/>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="5" t="n">
@@ -13835,7 +13821,6 @@
         <v/>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="5" t="n">
@@ -13873,7 +13858,6 @@
         <v/>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="5" t="n">
@@ -13911,7 +13895,6 @@
         <v/>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="5" t="n">
@@ -13949,7 +13932,6 @@
         <v/>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="5" t="n">
@@ -13987,11 +13969,6 @@
         <v/>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>Casey</t>
-        </is>
-      </c>
     </row>
     <row r="72">
       <c r="A72" s="5" t="n">
@@ -14029,7 +14006,6 @@
         <v/>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="5" t="n">
@@ -14067,11 +14043,6 @@
         <v/>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>Bryan</t>
-        </is>
-      </c>
     </row>
     <row r="74">
       <c r="A74" s="5" t="n">
@@ -14109,11 +14080,6 @@
         <v/>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>Casey</t>
-        </is>
-      </c>
     </row>
     <row r="75">
       <c r="A75" s="5" t="n">
@@ -14151,7 +14117,6 @@
         <v/>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="J75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="5" t="n">
@@ -14189,7 +14154,6 @@
         <v/>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="5" t="n">
@@ -14227,7 +14191,6 @@
         <v/>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="5" t="n">
@@ -14265,7 +14228,6 @@
         <v/>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="J78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="5" t="n">
@@ -14303,7 +14265,6 @@
         <v/>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="J79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="5" t="n">
@@ -14341,7 +14302,6 @@
         <v/>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="J80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="5" t="n">
@@ -14379,7 +14339,6 @@
         <v/>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="J81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="5" t="n">
@@ -14417,7 +14376,6 @@
         <v/>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="J82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="5" t="n">
@@ -14455,7 +14413,6 @@
         <v/>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="J83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="5" t="n">
@@ -14493,7 +14450,6 @@
         <v/>
       </c>
       <c r="I84" t="inlineStr"/>
-      <c r="J84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="5" t="n">
@@ -14531,7 +14487,6 @@
         <v/>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="J85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="5" t="n">
@@ -14569,7 +14524,6 @@
         <v/>
       </c>
       <c r="I86" t="inlineStr"/>
-      <c r="J86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="5" t="n">
@@ -14607,7 +14561,6 @@
         <v/>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="J87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="5" t="n">
@@ -14645,7 +14598,6 @@
         <v/>
       </c>
       <c r="I88" t="inlineStr"/>
-      <c r="J88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" s="5" t="n">
@@ -14683,7 +14635,6 @@
         <v/>
       </c>
       <c r="I89" t="inlineStr"/>
-      <c r="J89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="5" t="n">
@@ -14721,7 +14672,6 @@
         <v/>
       </c>
       <c r="I90" t="inlineStr"/>
-      <c r="J90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" s="5" t="n">
@@ -14759,11 +14709,6 @@
         <v/>
       </c>
       <c r="I91" t="inlineStr"/>
-      <c r="J91" t="inlineStr">
-        <is>
-          <t>Bryan</t>
-        </is>
-      </c>
     </row>
     <row r="92">
       <c r="A92" s="5" t="n">
@@ -14801,11 +14746,6 @@
         <v/>
       </c>
       <c r="I92" t="inlineStr"/>
-      <c r="J92" t="inlineStr">
-        <is>
-          <t>Casey</t>
-        </is>
-      </c>
     </row>
     <row r="93">
       <c r="A93" s="5" t="n">
@@ -14843,7 +14783,6 @@
         <v/>
       </c>
       <c r="I93" t="inlineStr"/>
-      <c r="J93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="5" t="n">
@@ -14881,7 +14820,6 @@
         <v/>
       </c>
       <c r="I94" t="inlineStr"/>
-      <c r="J94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="5" t="n">
@@ -14919,7 +14857,6 @@
         <v/>
       </c>
       <c r="I95" t="inlineStr"/>
-      <c r="J95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" s="5" t="n">
@@ -14957,7 +14894,6 @@
         <v/>
       </c>
       <c r="I96" t="inlineStr"/>
-      <c r="J96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" s="5" t="n">
@@ -14995,7 +14931,6 @@
         <v/>
       </c>
       <c r="I97" t="inlineStr"/>
-      <c r="J97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" s="5" t="n">
@@ -15033,7 +14968,6 @@
         <v/>
       </c>
       <c r="I98" t="inlineStr"/>
-      <c r="J98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" s="5" t="n">
@@ -15071,7 +15005,6 @@
         <v/>
       </c>
       <c r="I99" t="inlineStr"/>
-      <c r="J99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" s="5" t="n">
@@ -15109,7 +15042,6 @@
         <v/>
       </c>
       <c r="I100" t="inlineStr"/>
-      <c r="J100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" s="5" t="n">
@@ -15147,11 +15079,6 @@
         <v/>
       </c>
       <c r="I101" t="inlineStr"/>
-      <c r="J101" t="inlineStr">
-        <is>
-          <t>Bryan</t>
-        </is>
-      </c>
     </row>
     <row r="102">
       <c r="A102" s="5" t="n">
@@ -15189,11 +15116,6 @@
         <v/>
       </c>
       <c r="I102" t="inlineStr"/>
-      <c r="J102" t="inlineStr">
-        <is>
-          <t>Casey</t>
-        </is>
-      </c>
     </row>
     <row r="103">
       <c r="A103" s="5" t="n">
@@ -15231,7 +15153,6 @@
         <v/>
       </c>
       <c r="I103" t="inlineStr"/>
-      <c r="J103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" s="5" t="n">
@@ -15269,7 +15190,6 @@
         <v/>
       </c>
       <c r="I104" t="inlineStr"/>
-      <c r="J104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" s="5" t="n">
@@ -15307,7 +15227,6 @@
         <v/>
       </c>
       <c r="I105" t="inlineStr"/>
-      <c r="J105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" s="5" t="n">
@@ -15345,7 +15264,6 @@
         <v/>
       </c>
       <c r="I106" t="inlineStr"/>
-      <c r="J106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" s="5" t="n">
@@ -15383,7 +15301,6 @@
         <v/>
       </c>
       <c r="I107" t="inlineStr"/>
-      <c r="J107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" s="5" t="n">
@@ -15421,11 +15338,6 @@
         <v/>
       </c>
       <c r="I108" t="inlineStr"/>
-      <c r="J108" t="inlineStr">
-        <is>
-          <t>Bryan</t>
-        </is>
-      </c>
     </row>
     <row r="109">
       <c r="A109" s="5" t="n">
@@ -15463,11 +15375,6 @@
         <v/>
       </c>
       <c r="I109" t="inlineStr"/>
-      <c r="J109" t="inlineStr">
-        <is>
-          <t>Casey</t>
-        </is>
-      </c>
     </row>
     <row r="110">
       <c r="A110" s="5" t="n">
@@ -15505,7 +15412,6 @@
         <v/>
       </c>
       <c r="I110" t="inlineStr"/>
-      <c r="J110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" s="5" t="n">
@@ -15543,7 +15449,6 @@
         <v/>
       </c>
       <c r="I111" t="inlineStr"/>
-      <c r="J111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" s="5" t="n">
@@ -15581,7 +15486,6 @@
         <v/>
       </c>
       <c r="I112" t="inlineStr"/>
-      <c r="J112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" s="5" t="n">
@@ -15619,7 +15523,6 @@
         <v/>
       </c>
       <c r="I113" t="inlineStr"/>
-      <c r="J113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" s="5" t="n">
@@ -15657,7 +15560,6 @@
         <v/>
       </c>
       <c r="I114" t="inlineStr"/>
-      <c r="J114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" s="5" t="n">
@@ -15695,7 +15597,6 @@
         <v/>
       </c>
       <c r="I115" t="inlineStr"/>
-      <c r="J115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" s="5" t="n">
@@ -15733,7 +15634,6 @@
         <v/>
       </c>
       <c r="I116" t="inlineStr"/>
-      <c r="J116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" s="5" t="n">
@@ -15771,7 +15671,6 @@
         <v/>
       </c>
       <c r="I117" t="inlineStr"/>
-      <c r="J117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" s="5" t="n">
@@ -15809,7 +15708,6 @@
         <v/>
       </c>
       <c r="I118" t="inlineStr"/>
-      <c r="J118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" s="5" t="n">
@@ -15847,7 +15745,6 @@
         <v/>
       </c>
       <c r="I119" t="inlineStr"/>
-      <c r="J119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" s="5" t="n">
@@ -15885,7 +15782,6 @@
         <v/>
       </c>
       <c r="I120" t="inlineStr"/>
-      <c r="J120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" s="5" t="n">
@@ -15923,7 +15819,6 @@
         <v/>
       </c>
       <c r="I121" t="inlineStr"/>
-      <c r="J121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" s="5" t="n">
@@ -15961,7 +15856,6 @@
         <v/>
       </c>
       <c r="I122" t="inlineStr"/>
-      <c r="J122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" s="5" t="n">
@@ -15999,11 +15893,6 @@
         <v/>
       </c>
       <c r="I123" t="inlineStr"/>
-      <c r="J123" t="inlineStr">
-        <is>
-          <t>Casey</t>
-        </is>
-      </c>
     </row>
     <row r="124">
       <c r="A124" s="5" t="n">
@@ -16041,7 +15930,6 @@
         <v/>
       </c>
       <c r="I124" t="inlineStr"/>
-      <c r="J124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" s="5" t="n">
@@ -16079,7 +15967,6 @@
         <v/>
       </c>
       <c r="I125" t="inlineStr"/>
-      <c r="J125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" s="5" t="n">
@@ -16117,7 +16004,6 @@
         <v/>
       </c>
       <c r="I126" t="inlineStr"/>
-      <c r="J126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" s="5" t="n">
@@ -16155,11 +16041,6 @@
         <v/>
       </c>
       <c r="I127" t="inlineStr"/>
-      <c r="J127" t="inlineStr">
-        <is>
-          <t>Bryan</t>
-        </is>
-      </c>
     </row>
     <row r="128">
       <c r="A128" s="5" t="n">
@@ -16197,11 +16078,6 @@
         <v/>
       </c>
       <c r="I128" t="inlineStr"/>
-      <c r="J128" t="inlineStr">
-        <is>
-          <t>Casey</t>
-        </is>
-      </c>
     </row>
     <row r="129">
       <c r="A129" s="5" t="n">
@@ -16239,7 +16115,6 @@
         <v/>
       </c>
       <c r="I129" t="inlineStr"/>
-      <c r="J129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" s="5" t="n">
@@ -16277,7 +16152,6 @@
         <v/>
       </c>
       <c r="I130" t="inlineStr"/>
-      <c r="J130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" s="5" t="n">
@@ -16315,7 +16189,6 @@
         <v/>
       </c>
       <c r="I131" t="inlineStr"/>
-      <c r="J131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" s="5" t="n">
@@ -16353,7 +16226,6 @@
         <v/>
       </c>
       <c r="I132" t="inlineStr"/>
-      <c r="J132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" s="5" t="n">
@@ -16391,7 +16263,6 @@
         <v/>
       </c>
       <c r="I133" t="inlineStr"/>
-      <c r="J133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" s="5" t="n">
@@ -16429,7 +16300,6 @@
         <v/>
       </c>
       <c r="I134" t="inlineStr"/>
-      <c r="J134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" s="5" t="n">
@@ -16467,7 +16337,6 @@
         <v/>
       </c>
       <c r="I135" t="inlineStr"/>
-      <c r="J135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" s="5" t="n">
@@ -16505,7 +16374,6 @@
         <v/>
       </c>
       <c r="I136" t="inlineStr"/>
-      <c r="J136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" s="5" t="n">
@@ -16543,7 +16411,6 @@
         <v/>
       </c>
       <c r="I137" t="inlineStr"/>
-      <c r="J137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" s="5" t="n">
@@ -16581,7 +16448,6 @@
         <v/>
       </c>
       <c r="I138" t="inlineStr"/>
-      <c r="J138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" s="5" t="n">
@@ -16619,11 +16485,6 @@
         <v/>
       </c>
       <c r="I139" t="inlineStr"/>
-      <c r="J139" t="inlineStr">
-        <is>
-          <t>Casey</t>
-        </is>
-      </c>
     </row>
     <row r="140">
       <c r="A140" s="5" t="n">
@@ -16661,7 +16522,6 @@
         <v/>
       </c>
       <c r="I140" t="inlineStr"/>
-      <c r="J140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" s="5" t="n">
@@ -16699,7 +16559,6 @@
         <v/>
       </c>
       <c r="I141" t="inlineStr"/>
-      <c r="J141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" s="5" t="n">
@@ -16737,7 +16596,6 @@
         <v/>
       </c>
       <c r="I142" t="inlineStr"/>
-      <c r="J142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" s="5" t="n">
@@ -16775,11 +16633,6 @@
         <v/>
       </c>
       <c r="I143" t="inlineStr"/>
-      <c r="J143" t="inlineStr">
-        <is>
-          <t>Bryan</t>
-        </is>
-      </c>
     </row>
     <row r="144">
       <c r="A144" s="5" t="n">
@@ -16817,11 +16670,6 @@
         <v/>
       </c>
       <c r="I144" t="inlineStr"/>
-      <c r="J144" t="inlineStr">
-        <is>
-          <t>Bryan</t>
-        </is>
-      </c>
     </row>
     <row r="145">
       <c r="A145" s="5" t="n">
@@ -16859,11 +16707,6 @@
         <v/>
       </c>
       <c r="I145" t="inlineStr"/>
-      <c r="J145" t="inlineStr">
-        <is>
-          <t>Casey</t>
-        </is>
-      </c>
     </row>
     <row r="146">
       <c r="A146" s="5" t="n">
@@ -16901,7 +16744,6 @@
         <v/>
       </c>
       <c r="I146" t="inlineStr"/>
-      <c r="J146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" s="5" t="n">
@@ -16939,7 +16781,6 @@
         <v/>
       </c>
       <c r="I147" t="inlineStr"/>
-      <c r="J147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" s="5" t="n">
@@ -16977,7 +16818,6 @@
         <v/>
       </c>
       <c r="I148" t="inlineStr"/>
-      <c r="J148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" s="5" t="n">
@@ -17015,7 +16855,6 @@
         <v/>
       </c>
       <c r="I149" t="inlineStr"/>
-      <c r="J149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" s="5" t="n">
@@ -17053,7 +16892,6 @@
         <v/>
       </c>
       <c r="I150" t="inlineStr"/>
-      <c r="J150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" s="5" t="n">
@@ -17091,7 +16929,6 @@
         <v/>
       </c>
       <c r="I151" t="inlineStr"/>
-      <c r="J151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" s="5" t="n">
@@ -17129,7 +16966,6 @@
         <v/>
       </c>
       <c r="I152" t="inlineStr"/>
-      <c r="J152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" s="5" t="n">
@@ -17167,7 +17003,6 @@
         <v/>
       </c>
       <c r="I153" t="inlineStr"/>
-      <c r="J153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" s="5" t="n">
@@ -17205,7 +17040,6 @@
         <v/>
       </c>
       <c r="I154" t="inlineStr"/>
-      <c r="J154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" s="5" t="n">
@@ -17243,7 +17077,6 @@
         <v/>
       </c>
       <c r="I155" t="inlineStr"/>
-      <c r="J155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" s="5" t="n">
@@ -17281,7 +17114,6 @@
         <v/>
       </c>
       <c r="I156" t="inlineStr"/>
-      <c r="J156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" s="5" t="n">
@@ -17319,7 +17151,6 @@
         <v/>
       </c>
       <c r="I157" t="inlineStr"/>
-      <c r="J157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" s="5" t="n">
@@ -17357,7 +17188,6 @@
         <v/>
       </c>
       <c r="I158" t="inlineStr"/>
-      <c r="J158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" s="5" t="n">
@@ -17395,7 +17225,6 @@
         <v/>
       </c>
       <c r="I159" t="inlineStr"/>
-      <c r="J159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" s="5" t="n">
@@ -17433,7 +17262,6 @@
         <v/>
       </c>
       <c r="I160" t="inlineStr"/>
-      <c r="J160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" s="5" t="n">
@@ -17471,11 +17299,6 @@
         <v/>
       </c>
       <c r="I161" t="inlineStr"/>
-      <c r="J161" t="inlineStr">
-        <is>
-          <t>Casey</t>
-        </is>
-      </c>
     </row>
     <row r="162">
       <c r="A162" s="5" t="n">
@@ -17513,7 +17336,6 @@
         <v/>
       </c>
       <c r="I162" t="inlineStr"/>
-      <c r="J162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" s="5" t="n">
@@ -17551,7 +17373,6 @@
         <v/>
       </c>
       <c r="I163" t="inlineStr"/>
-      <c r="J163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" s="5" t="n">
@@ -17589,7 +17410,6 @@
         <v/>
       </c>
       <c r="I164" t="inlineStr"/>
-      <c r="J164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" s="5" t="n">
@@ -17627,7 +17447,6 @@
         <v/>
       </c>
       <c r="I165" t="inlineStr"/>
-      <c r="J165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" s="5" t="n">
@@ -17665,7 +17484,6 @@
         <v/>
       </c>
       <c r="I166" t="inlineStr"/>
-      <c r="J166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" s="5" t="n">
@@ -17703,7 +17521,6 @@
         <v/>
       </c>
       <c r="I167" t="inlineStr"/>
-      <c r="J167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" s="5" t="n">
@@ -17741,7 +17558,6 @@
         <v/>
       </c>
       <c r="I168" t="inlineStr"/>
-      <c r="J168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" s="5" t="n">
@@ -17779,7 +17595,6 @@
         <v/>
       </c>
       <c r="I169" t="inlineStr"/>
-      <c r="J169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" s="5" t="n">
@@ -17817,7 +17632,6 @@
         <v/>
       </c>
       <c r="I170" t="inlineStr"/>
-      <c r="J170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" s="5" t="n">
@@ -17855,7 +17669,6 @@
         <v/>
       </c>
       <c r="I171" t="inlineStr"/>
-      <c r="J171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" s="5" t="n">
@@ -17893,7 +17706,6 @@
         <v/>
       </c>
       <c r="I172" t="inlineStr"/>
-      <c r="J172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" s="5" t="n">
@@ -17931,7 +17743,6 @@
         <v/>
       </c>
       <c r="I173" t="inlineStr"/>
-      <c r="J173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" s="5" t="n">
@@ -17969,7 +17780,6 @@
         <v/>
       </c>
       <c r="I174" t="inlineStr"/>
-      <c r="J174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" s="5" t="n">
@@ -18007,7 +17817,6 @@
         <v/>
       </c>
       <c r="I175" t="inlineStr"/>
-      <c r="J175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" s="5" t="n">
@@ -18045,11 +17854,6 @@
         <v/>
       </c>
       <c r="I176" t="inlineStr"/>
-      <c r="J176" t="inlineStr">
-        <is>
-          <t>Bryan</t>
-        </is>
-      </c>
     </row>
     <row r="177">
       <c r="A177" s="5" t="n">
@@ -18087,11 +17891,6 @@
         <v/>
       </c>
       <c r="I177" t="inlineStr"/>
-      <c r="J177" t="inlineStr">
-        <is>
-          <t>Casey</t>
-        </is>
-      </c>
     </row>
     <row r="178">
       <c r="A178" s="5" t="n">
@@ -18129,7 +17928,6 @@
         <v/>
       </c>
       <c r="I178" t="inlineStr"/>
-      <c r="J178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" s="5" t="n">
@@ -18167,7 +17965,6 @@
         <v/>
       </c>
       <c r="I179" t="inlineStr"/>
-      <c r="J179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" s="5" t="n">
@@ -18205,7 +18002,6 @@
         <v/>
       </c>
       <c r="I180" t="inlineStr"/>
-      <c r="J180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" s="5" t="n">
@@ -18243,7 +18039,6 @@
         <v/>
       </c>
       <c r="I181" t="inlineStr"/>
-      <c r="J181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" s="5" t="n">
@@ -18281,7 +18076,6 @@
         <v/>
       </c>
       <c r="I182" t="inlineStr"/>
-      <c r="J182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" s="5" t="n">
@@ -18319,7 +18113,6 @@
         <v/>
       </c>
       <c r="I183" t="inlineStr"/>
-      <c r="J183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" s="5" t="n">
@@ -18357,7 +18150,6 @@
         <v/>
       </c>
       <c r="I184" t="inlineStr"/>
-      <c r="J184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" s="5" t="n">
@@ -18395,7 +18187,6 @@
         <v/>
       </c>
       <c r="I185" t="inlineStr"/>
-      <c r="J185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" s="5" t="n">
@@ -18433,7 +18224,6 @@
         <v/>
       </c>
       <c r="I186" t="inlineStr"/>
-      <c r="J186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" s="5" t="n">
@@ -18471,7 +18261,6 @@
         <v/>
       </c>
       <c r="I187" t="inlineStr"/>
-      <c r="J187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" s="5" t="n">
@@ -18509,7 +18298,6 @@
         <v/>
       </c>
       <c r="I188" t="inlineStr"/>
-      <c r="J188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" s="5" t="n">
@@ -18547,7 +18335,6 @@
         <v/>
       </c>
       <c r="I189" t="inlineStr"/>
-      <c r="J189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" s="5" t="n">
@@ -18585,7 +18372,6 @@
         <v/>
       </c>
       <c r="I190" t="inlineStr"/>
-      <c r="J190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" s="5" t="n">
@@ -18623,7 +18409,6 @@
         <v/>
       </c>
       <c r="I191" t="inlineStr"/>
-      <c r="J191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" s="5" t="n">
@@ -18661,7 +18446,6 @@
         <v/>
       </c>
       <c r="I192" t="inlineStr"/>
-      <c r="J192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" s="5" t="n">
@@ -18699,11 +18483,6 @@
         <v/>
       </c>
       <c r="I193" t="inlineStr"/>
-      <c r="J193" t="inlineStr">
-        <is>
-          <t>Casey</t>
-        </is>
-      </c>
     </row>
     <row r="194">
       <c r="A194" s="5" t="n">
@@ -18741,7 +18520,6 @@
         <v/>
       </c>
       <c r="I194" t="inlineStr"/>
-      <c r="J194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" s="5" t="n">
@@ -18779,7 +18557,6 @@
         <v/>
       </c>
       <c r="I195" t="inlineStr"/>
-      <c r="J195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" s="5" t="n">
@@ -18817,7 +18594,6 @@
         <v/>
       </c>
       <c r="I196" t="inlineStr"/>
-      <c r="J196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" s="5" t="n">
@@ -18855,11 +18631,6 @@
         <v/>
       </c>
       <c r="I197" t="inlineStr"/>
-      <c r="J197" t="inlineStr">
-        <is>
-          <t>Bryan</t>
-        </is>
-      </c>
     </row>
     <row r="198">
       <c r="A198" s="5" t="n">
@@ -18897,11 +18668,6 @@
         <v/>
       </c>
       <c r="I198" t="inlineStr"/>
-      <c r="J198" t="inlineStr">
-        <is>
-          <t>Casey</t>
-        </is>
-      </c>
     </row>
     <row r="199">
       <c r="A199" s="5" t="n">
@@ -18939,7 +18705,6 @@
         <v/>
       </c>
       <c r="I199" t="inlineStr"/>
-      <c r="J199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" s="5" t="n">
@@ -18977,7 +18742,6 @@
         <v/>
       </c>
       <c r="I200" t="inlineStr"/>
-      <c r="J200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" s="5" t="n">
@@ -19015,7 +18779,6 @@
         <v/>
       </c>
       <c r="I201" t="inlineStr"/>
-      <c r="J201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" s="5" t="n">
@@ -19053,7 +18816,6 @@
         <v/>
       </c>
       <c r="I202" t="inlineStr"/>
-      <c r="J202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" s="5" t="n">
@@ -19091,7 +18853,6 @@
         <v/>
       </c>
       <c r="I203" t="inlineStr"/>
-      <c r="J203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" s="5" t="n">
@@ -19129,7 +18890,6 @@
         <v/>
       </c>
       <c r="I204" t="inlineStr"/>
-      <c r="J204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" s="5" t="n">
@@ -19167,7 +18927,6 @@
         <v/>
       </c>
       <c r="I205" t="inlineStr"/>
-      <c r="J205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" s="5" t="n">
@@ -19205,7 +18964,6 @@
         <v/>
       </c>
       <c r="I206" t="inlineStr"/>
-      <c r="J206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" s="5" t="n">
@@ -19243,11 +19001,6 @@
         <v/>
       </c>
       <c r="I207" t="inlineStr"/>
-      <c r="J207" t="inlineStr">
-        <is>
-          <t>Bryan</t>
-        </is>
-      </c>
     </row>
     <row r="208">
       <c r="A208" s="5" t="n">
@@ -19285,11 +19038,6 @@
         <v/>
       </c>
       <c r="I208" t="inlineStr"/>
-      <c r="J208" t="inlineStr">
-        <is>
-          <t>Casey</t>
-        </is>
-      </c>
     </row>
     <row r="209">
       <c r="A209" s="5" t="n">
@@ -19327,7 +19075,6 @@
         <v/>
       </c>
       <c r="I209" t="inlineStr"/>
-      <c r="J209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" s="5" t="n">
@@ -19365,7 +19112,6 @@
         <v/>
       </c>
       <c r="I210" t="inlineStr"/>
-      <c r="J210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" s="5" t="n">
@@ -19403,7 +19149,6 @@
         <v/>
       </c>
       <c r="I211" t="inlineStr"/>
-      <c r="J211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" s="5" t="n">
@@ -19441,7 +19186,6 @@
         <v/>
       </c>
       <c r="I212" t="inlineStr"/>
-      <c r="J212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" s="5" t="n">
@@ -19479,7 +19223,6 @@
         <v/>
       </c>
       <c r="I213" t="inlineStr"/>
-      <c r="J213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" s="5" t="n">
@@ -19517,7 +19260,6 @@
         <v/>
       </c>
       <c r="I214" t="inlineStr"/>
-      <c r="J214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" s="5" t="n">
@@ -19555,7 +19297,6 @@
         <v/>
       </c>
       <c r="I215" t="inlineStr"/>
-      <c r="J215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" s="5" t="n">
@@ -19593,11 +19334,6 @@
         <v/>
       </c>
       <c r="I216" t="inlineStr"/>
-      <c r="J216" t="inlineStr">
-        <is>
-          <t>Bryan</t>
-        </is>
-      </c>
     </row>
     <row r="217">
       <c r="A217" s="5" t="n">
@@ -19635,11 +19371,6 @@
         <v/>
       </c>
       <c r="I217" t="inlineStr"/>
-      <c r="J217" t="inlineStr">
-        <is>
-          <t>Casey</t>
-        </is>
-      </c>
     </row>
     <row r="218">
       <c r="A218" s="5" t="n">
@@ -19677,7 +19408,6 @@
         <v/>
       </c>
       <c r="I218" t="inlineStr"/>
-      <c r="J218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" s="5" t="n">
@@ -19715,7 +19445,6 @@
         <v/>
       </c>
       <c r="I219" t="inlineStr"/>
-      <c r="J219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" s="5" t="n">
@@ -19753,7 +19482,6 @@
         <v/>
       </c>
       <c r="I220" t="inlineStr"/>
-      <c r="J220" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" s="5" t="n">
@@ -19791,7 +19519,6 @@
         <v/>
       </c>
       <c r="I221" t="inlineStr"/>
-      <c r="J221" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" s="5" t="n">
@@ -19829,7 +19556,6 @@
         <v/>
       </c>
       <c r="I222" t="inlineStr"/>
-      <c r="J222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" s="5" t="n">
@@ -19867,7 +19593,6 @@
         <v/>
       </c>
       <c r="I223" t="inlineStr"/>
-      <c r="J223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" s="5" t="n">
@@ -19905,7 +19630,6 @@
         <v/>
       </c>
       <c r="I224" t="inlineStr"/>
-      <c r="J224" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" s="5" t="n">
@@ -19943,7 +19667,6 @@
         <v/>
       </c>
       <c r="I225" t="inlineStr"/>
-      <c r="J225" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" s="5" t="n">
@@ -19981,7 +19704,6 @@
         <v/>
       </c>
       <c r="I226" t="inlineStr"/>
-      <c r="J226" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" s="5" t="n">
@@ -20019,7 +19741,6 @@
         <v/>
       </c>
       <c r="I227" t="inlineStr"/>
-      <c r="J227" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" s="5" t="n">
@@ -20057,7 +19778,6 @@
         <v/>
       </c>
       <c r="I228" t="inlineStr"/>
-      <c r="J228" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" s="5" t="n">
@@ -20095,7 +19815,6 @@
         <v/>
       </c>
       <c r="I229" t="inlineStr"/>
-      <c r="J229" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" s="5" t="n">
@@ -20133,7 +19852,6 @@
         <v/>
       </c>
       <c r="I230" t="inlineStr"/>
-      <c r="J230" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" s="5" t="n">
@@ -20171,7 +19889,6 @@
         <v/>
       </c>
       <c r="I231" t="inlineStr"/>
-      <c r="J231" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" s="5" t="n">
@@ -20209,7 +19926,6 @@
         <v/>
       </c>
       <c r="I232" t="inlineStr"/>
-      <c r="J232" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" s="5" t="n">
@@ -20247,7 +19963,6 @@
         <v/>
       </c>
       <c r="I233" t="inlineStr"/>
-      <c r="J233" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" s="5" t="n">
@@ -20285,7 +20000,6 @@
         <v/>
       </c>
       <c r="I234" t="inlineStr"/>
-      <c r="J234" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" s="5" t="n">
@@ -20323,7 +20037,6 @@
         <v/>
       </c>
       <c r="I235" t="inlineStr"/>
-      <c r="J235" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" s="5" t="n">
@@ -20361,7 +20074,6 @@
         <v/>
       </c>
       <c r="I236" t="inlineStr"/>
-      <c r="J236" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" s="5" t="n">
@@ -20399,7 +20111,6 @@
         <v/>
       </c>
       <c r="I237" t="inlineStr"/>
-      <c r="J237" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" s="5" t="n">
@@ -20437,7 +20148,6 @@
         <v/>
       </c>
       <c r="I238" t="inlineStr"/>
-      <c r="J238" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" s="5" t="n">
@@ -20475,7 +20185,6 @@
         <v/>
       </c>
       <c r="I239" t="inlineStr"/>
-      <c r="J239" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" s="5" t="n">
@@ -20513,7 +20222,6 @@
         <v/>
       </c>
       <c r="I240" t="inlineStr"/>
-      <c r="J240" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" s="5" t="n">
@@ -20551,7 +20259,6 @@
         <v/>
       </c>
       <c r="I241" t="inlineStr"/>
-      <c r="J241" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" s="5" t="n">
@@ -20589,7 +20296,6 @@
         <v/>
       </c>
       <c r="I242" t="inlineStr"/>
-      <c r="J242" t="inlineStr"/>
     </row>
     <row r="243">
       <c r="A243" s="5" t="n">
@@ -20627,7 +20333,6 @@
         <v/>
       </c>
       <c r="I243" t="inlineStr"/>
-      <c r="J243" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" s="5" t="n">
@@ -20665,7 +20370,6 @@
         <v/>
       </c>
       <c r="I244" t="inlineStr"/>
-      <c r="J244" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="A245" s="5" t="n">
@@ -20703,11 +20407,6 @@
         <v/>
       </c>
       <c r="I245" t="inlineStr"/>
-      <c r="J245" t="inlineStr">
-        <is>
-          <t>Bryan</t>
-        </is>
-      </c>
     </row>
     <row r="246">
       <c r="A246" s="5" t="n">
@@ -20745,11 +20444,6 @@
         <v/>
       </c>
       <c r="I246" t="inlineStr"/>
-      <c r="J246" t="inlineStr">
-        <is>
-          <t>Casey</t>
-        </is>
-      </c>
     </row>
     <row r="247">
       <c r="A247" s="5" t="n">
@@ -20787,7 +20481,6 @@
         <v/>
       </c>
       <c r="I247" t="inlineStr"/>
-      <c r="J247" t="inlineStr"/>
     </row>
     <row r="248">
       <c r="A248" s="5" t="n">
@@ -20825,7 +20518,6 @@
         <v/>
       </c>
       <c r="I248" t="inlineStr"/>
-      <c r="J248" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" s="5" t="n">
@@ -20863,11 +20555,6 @@
         <v/>
       </c>
       <c r="I249" t="inlineStr"/>
-      <c r="J249" t="inlineStr">
-        <is>
-          <t>Casey</t>
-        </is>
-      </c>
     </row>
     <row r="250">
       <c r="A250" s="5" t="n">
@@ -20905,7 +20592,6 @@
         <v/>
       </c>
       <c r="I250" t="inlineStr"/>
-      <c r="J250" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" s="5" t="n">
@@ -20943,7 +20629,6 @@
         <v/>
       </c>
       <c r="I251" t="inlineStr"/>
-      <c r="J251" t="inlineStr"/>
     </row>
     <row r="252">
       <c r="A252" s="5" t="n">
@@ -20981,7 +20666,6 @@
         <v/>
       </c>
       <c r="I252" t="inlineStr"/>
-      <c r="J252" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" s="5" t="n">
@@ -21019,7 +20703,6 @@
         <v/>
       </c>
       <c r="I253" t="inlineStr"/>
-      <c r="J253" t="inlineStr"/>
     </row>
     <row r="254">
       <c r="A254" s="5" t="n">
@@ -21057,7 +20740,6 @@
         <v/>
       </c>
       <c r="I254" t="inlineStr"/>
-      <c r="J254" t="inlineStr"/>
     </row>
     <row r="255">
       <c r="A255" s="5" t="n">
@@ -21095,7 +20777,6 @@
         <v/>
       </c>
       <c r="I255" t="inlineStr"/>
-      <c r="J255" t="inlineStr"/>
     </row>
     <row r="256">
       <c r="A256" s="5" t="n">
@@ -21133,7 +20814,6 @@
         <v/>
       </c>
       <c r="I256" t="inlineStr"/>
-      <c r="J256" t="inlineStr"/>
     </row>
     <row r="257">
       <c r="A257" s="5" t="n">
@@ -21171,7 +20851,6 @@
         <v/>
       </c>
       <c r="I257" t="inlineStr"/>
-      <c r="J257" t="inlineStr"/>
     </row>
     <row r="258">
       <c r="A258" s="5" t="n">
@@ -21209,7 +20888,6 @@
         <v/>
       </c>
       <c r="I258" t="inlineStr"/>
-      <c r="J258" t="inlineStr"/>
     </row>
     <row r="259">
       <c r="A259" s="5" t="n">
@@ -21247,7 +20925,6 @@
         <v/>
       </c>
       <c r="I259" t="inlineStr"/>
-      <c r="J259" t="inlineStr"/>
     </row>
     <row r="260">
       <c r="A260" s="5" t="n">
@@ -21285,7 +20962,6 @@
         <v/>
       </c>
       <c r="I260" t="inlineStr"/>
-      <c r="J260" t="inlineStr"/>
     </row>
     <row r="261">
       <c r="A261" s="5" t="n">
@@ -21323,7 +20999,6 @@
         <v/>
       </c>
       <c r="I261" t="inlineStr"/>
-      <c r="J261" t="inlineStr"/>
     </row>
     <row r="262">
       <c r="A262" s="5" t="n">
@@ -21361,7 +21036,6 @@
         <v/>
       </c>
       <c r="I262" t="inlineStr"/>
-      <c r="J262" t="inlineStr"/>
     </row>
     <row r="263">
       <c r="A263" s="5" t="n">
@@ -21399,7 +21073,6 @@
         <v/>
       </c>
       <c r="I263" t="inlineStr"/>
-      <c r="J263" t="inlineStr"/>
     </row>
     <row r="264">
       <c r="A264" s="5" t="n">
@@ -21437,7 +21110,6 @@
         <v/>
       </c>
       <c r="I264" t="inlineStr"/>
-      <c r="J264" t="inlineStr"/>
     </row>
     <row r="265">
       <c r="A265" s="5" t="n">
@@ -21475,7 +21147,6 @@
         <v/>
       </c>
       <c r="I265" t="inlineStr"/>
-      <c r="J265" t="inlineStr"/>
     </row>
     <row r="266">
       <c r="A266" s="5" t="n">
@@ -21513,7 +21184,6 @@
         <v/>
       </c>
       <c r="I266" t="inlineStr"/>
-      <c r="J266" t="inlineStr"/>
     </row>
     <row r="267">
       <c r="A267" s="5" t="n">
@@ -21551,7 +21221,6 @@
         <v/>
       </c>
       <c r="I267" t="inlineStr"/>
-      <c r="J267" t="inlineStr"/>
     </row>
     <row r="268">
       <c r="A268" s="5" t="n">
@@ -21589,7 +21258,6 @@
         <v/>
       </c>
       <c r="I268" t="inlineStr"/>
-      <c r="J268" t="inlineStr"/>
     </row>
     <row r="269">
       <c r="A269" s="5" t="n">
@@ -21627,7 +21295,6 @@
         <v/>
       </c>
       <c r="I269" t="inlineStr"/>
-      <c r="J269" t="inlineStr"/>
     </row>
     <row r="270">
       <c r="A270" s="5" t="n">
@@ -21665,7 +21332,6 @@
         <v/>
       </c>
       <c r="I270" t="inlineStr"/>
-      <c r="J270" t="inlineStr"/>
     </row>
     <row r="271">
       <c r="A271" s="5" t="n">
@@ -21703,7 +21369,6 @@
         <v/>
       </c>
       <c r="I271" t="inlineStr"/>
-      <c r="J271" t="inlineStr"/>
     </row>
     <row r="272">
       <c r="A272" s="5" t="n">
@@ -21741,7 +21406,6 @@
         <v/>
       </c>
       <c r="I272" t="inlineStr"/>
-      <c r="J272" t="inlineStr"/>
     </row>
     <row r="273">
       <c r="A273" s="5" t="n">
@@ -21779,7 +21443,6 @@
         <v/>
       </c>
       <c r="I273" t="inlineStr"/>
-      <c r="J273" t="inlineStr"/>
     </row>
     <row r="274">
       <c r="A274" s="5" t="n">
@@ -21817,7 +21480,6 @@
         <v/>
       </c>
       <c r="I274" t="inlineStr"/>
-      <c r="J274" t="inlineStr"/>
     </row>
     <row r="275">
       <c r="A275" s="5" t="n">
@@ -21855,11 +21517,6 @@
         <v/>
       </c>
       <c r="I275" t="inlineStr"/>
-      <c r="J275" t="inlineStr">
-        <is>
-          <t>Casey</t>
-        </is>
-      </c>
     </row>
     <row r="276">
       <c r="A276" s="5" t="n">
@@ -21897,7 +21554,6 @@
         <v/>
       </c>
       <c r="I276" t="inlineStr"/>
-      <c r="J276" t="inlineStr"/>
     </row>
     <row r="277">
       <c r="A277" s="5" t="n">
@@ -21935,7 +21591,6 @@
         <v/>
       </c>
       <c r="I277" t="inlineStr"/>
-      <c r="J277" t="inlineStr"/>
     </row>
     <row r="278">
       <c r="A278" s="5" t="n">
@@ -21973,7 +21628,6 @@
         <v/>
       </c>
       <c r="I278" t="inlineStr"/>
-      <c r="J278" t="inlineStr"/>
     </row>
     <row r="279">
       <c r="A279" s="5" t="n">
@@ -22011,7 +21665,6 @@
         <v/>
       </c>
       <c r="I279" t="inlineStr"/>
-      <c r="J279" t="inlineStr"/>
     </row>
     <row r="280">
       <c r="A280" s="5" t="n">
@@ -22049,7 +21702,6 @@
         <v/>
       </c>
       <c r="I280" t="inlineStr"/>
-      <c r="J280" t="inlineStr"/>
     </row>
     <row r="281">
       <c r="A281" s="5" t="n">
@@ -22087,7 +21739,6 @@
         <v/>
       </c>
       <c r="I281" t="inlineStr"/>
-      <c r="J281" t="inlineStr"/>
     </row>
     <row r="282">
       <c r="A282" s="5" t="n">
@@ -22125,7 +21776,6 @@
         <v/>
       </c>
       <c r="I282" t="inlineStr"/>
-      <c r="J282" t="inlineStr"/>
     </row>
     <row r="283">
       <c r="A283" s="5" t="n">
@@ -22163,7 +21813,6 @@
         <v/>
       </c>
       <c r="I283" t="inlineStr"/>
-      <c r="J283" t="inlineStr"/>
     </row>
     <row r="284">
       <c r="A284" s="5" t="n">
@@ -22201,7 +21850,6 @@
         <v/>
       </c>
       <c r="I284" t="inlineStr"/>
-      <c r="J284" t="inlineStr"/>
     </row>
     <row r="285">
       <c r="A285" s="5" t="n">
@@ -22239,7 +21887,6 @@
         <v/>
       </c>
       <c r="I285" t="inlineStr"/>
-      <c r="J285" t="inlineStr"/>
     </row>
     <row r="286">
       <c r="A286" s="5" t="n">
@@ -22277,7 +21924,6 @@
         <v/>
       </c>
       <c r="I286" t="inlineStr"/>
-      <c r="J286" t="inlineStr"/>
     </row>
     <row r="287">
       <c r="A287" s="5" t="n">
@@ -22315,7 +21961,6 @@
         <v/>
       </c>
       <c r="I287" t="inlineStr"/>
-      <c r="J287" t="inlineStr"/>
     </row>
     <row r="288">
       <c r="A288" s="5" t="n">
@@ -22353,7 +21998,6 @@
         <v/>
       </c>
       <c r="I288" t="inlineStr"/>
-      <c r="J288" t="inlineStr"/>
     </row>
     <row r="289">
       <c r="A289" s="5" t="n">
@@ -22391,7 +22035,6 @@
         <v/>
       </c>
       <c r="I289" t="inlineStr"/>
-      <c r="J289" t="inlineStr"/>
     </row>
     <row r="290">
       <c r="A290" s="5" t="n">
@@ -22429,7 +22072,6 @@
         <v/>
       </c>
       <c r="I290" t="inlineStr"/>
-      <c r="J290" t="inlineStr"/>
     </row>
     <row r="291">
       <c r="A291" s="5" t="n">
@@ -22467,7 +22109,6 @@
         <v/>
       </c>
       <c r="I291" t="inlineStr"/>
-      <c r="J291" t="inlineStr"/>
     </row>
     <row r="292">
       <c r="A292" s="5" t="n">
@@ -22505,7 +22146,6 @@
         <v/>
       </c>
       <c r="I292" t="inlineStr"/>
-      <c r="J292" t="inlineStr"/>
     </row>
     <row r="293">
       <c r="A293" s="5" t="n">
@@ -22543,7 +22183,6 @@
         <v/>
       </c>
       <c r="I293" t="inlineStr"/>
-      <c r="J293" t="inlineStr"/>
     </row>
     <row r="294">
       <c r="A294" s="5" t="n">
@@ -22581,7 +22220,6 @@
         <v/>
       </c>
       <c r="I294" t="inlineStr"/>
-      <c r="J294" t="inlineStr"/>
     </row>
     <row r="295">
       <c r="A295" s="5" t="n">
@@ -22619,7 +22257,6 @@
         <v/>
       </c>
       <c r="I295" t="inlineStr"/>
-      <c r="J295" t="inlineStr"/>
     </row>
     <row r="296">
       <c r="A296" s="5" t="n">
@@ -22657,7 +22294,6 @@
         <v/>
       </c>
       <c r="I296" t="inlineStr"/>
-      <c r="J296" t="inlineStr"/>
     </row>
     <row r="297">
       <c r="A297" s="5" t="n">
@@ -22695,7 +22331,6 @@
         <v/>
       </c>
       <c r="I297" t="inlineStr"/>
-      <c r="J297" t="inlineStr"/>
     </row>
     <row r="298">
       <c r="A298" s="5" t="n">
@@ -22733,11 +22368,6 @@
         <v/>
       </c>
       <c r="I298" t="inlineStr"/>
-      <c r="J298" t="inlineStr">
-        <is>
-          <t>Bryan</t>
-        </is>
-      </c>
     </row>
     <row r="299">
       <c r="A299" s="5" t="n">
@@ -22775,11 +22405,6 @@
         <v/>
       </c>
       <c r="I299" t="inlineStr"/>
-      <c r="J299" t="inlineStr">
-        <is>
-          <t>Casey</t>
-        </is>
-      </c>
     </row>
     <row r="300">
       <c r="A300" s="5" t="n">
@@ -22817,7 +22442,6 @@
         <v/>
       </c>
       <c r="I300" t="inlineStr"/>
-      <c r="J300" t="inlineStr"/>
     </row>
     <row r="301">
       <c r="A301" s="5" t="n">
@@ -22855,11 +22479,6 @@
         <v/>
       </c>
       <c r="I301" t="inlineStr"/>
-      <c r="J301" t="inlineStr">
-        <is>
-          <t>Casey</t>
-        </is>
-      </c>
     </row>
     <row r="302">
       <c r="A302" s="5" t="n">
@@ -22897,7 +22516,6 @@
         <v/>
       </c>
       <c r="I302" t="inlineStr"/>
-      <c r="J302" t="inlineStr"/>
     </row>
     <row r="303">
       <c r="A303" s="5" t="n">
@@ -22935,7 +22553,6 @@
         <v/>
       </c>
       <c r="I303" t="inlineStr"/>
-      <c r="J303" t="inlineStr"/>
     </row>
     <row r="304">
       <c r="A304" s="5" t="n">
@@ -22973,7 +22590,6 @@
         <v/>
       </c>
       <c r="I304" t="inlineStr"/>
-      <c r="J304" t="inlineStr"/>
     </row>
     <row r="305">
       <c r="A305" s="5" t="n">
@@ -23011,7 +22627,6 @@
         <v/>
       </c>
       <c r="I305" t="inlineStr"/>
-      <c r="J305" t="inlineStr"/>
     </row>
     <row r="306">
       <c r="A306" s="5" t="n">
@@ -23049,7 +22664,6 @@
         <v/>
       </c>
       <c r="I306" t="inlineStr"/>
-      <c r="J306" t="inlineStr"/>
     </row>
     <row r="307">
       <c r="A307" s="5" t="n">
@@ -23087,7 +22701,6 @@
         <v/>
       </c>
       <c r="I307" t="inlineStr"/>
-      <c r="J307" t="inlineStr"/>
     </row>
     <row r="308">
       <c r="A308" s="5" t="n">
@@ -23125,7 +22738,6 @@
         <v/>
       </c>
       <c r="I308" t="inlineStr"/>
-      <c r="J308" t="inlineStr"/>
     </row>
     <row r="309">
       <c r="A309" s="5" t="n">
@@ -23163,7 +22775,6 @@
         <v/>
       </c>
       <c r="I309" t="inlineStr"/>
-      <c r="J309" t="inlineStr"/>
     </row>
     <row r="310">
       <c r="A310" s="5" t="n">
@@ -23201,7 +22812,6 @@
         <v/>
       </c>
       <c r="I310" t="inlineStr"/>
-      <c r="J310" t="inlineStr"/>
     </row>
     <row r="311">
       <c r="A311" s="5" t="n">
@@ -23239,7 +22849,6 @@
         <v/>
       </c>
       <c r="I311" t="inlineStr"/>
-      <c r="J311" t="inlineStr"/>
     </row>
     <row r="312">
       <c r="A312" s="5" t="n">
@@ -23277,7 +22886,6 @@
         <v/>
       </c>
       <c r="I312" t="inlineStr"/>
-      <c r="J312" t="inlineStr"/>
     </row>
     <row r="313">
       <c r="A313" s="5" t="n">
@@ -23315,7 +22923,6 @@
         <v/>
       </c>
       <c r="I313" t="inlineStr"/>
-      <c r="J313" t="inlineStr"/>
     </row>
     <row r="314">
       <c r="A314" s="5" t="n">
@@ -23353,7 +22960,6 @@
         <v/>
       </c>
       <c r="I314" t="inlineStr"/>
-      <c r="J314" t="inlineStr"/>
     </row>
     <row r="315">
       <c r="A315" s="5" t="n">
@@ -23391,7 +22997,6 @@
         <v/>
       </c>
       <c r="I315" t="inlineStr"/>
-      <c r="J315" t="inlineStr"/>
     </row>
     <row r="316">
       <c r="A316" s="5" t="n">
@@ -23429,7 +23034,6 @@
         <v/>
       </c>
       <c r="I316" t="inlineStr"/>
-      <c r="J316" t="inlineStr"/>
     </row>
     <row r="317">
       <c r="A317" s="5" t="n">
@@ -23467,11 +23071,6 @@
         <v/>
       </c>
       <c r="I317" t="inlineStr"/>
-      <c r="J317" t="inlineStr">
-        <is>
-          <t>Bryan</t>
-        </is>
-      </c>
     </row>
     <row r="318">
       <c r="A318" s="5" t="n">
@@ -23509,11 +23108,6 @@
         <v/>
       </c>
       <c r="I318" t="inlineStr"/>
-      <c r="J318" t="inlineStr">
-        <is>
-          <t>Casey</t>
-        </is>
-      </c>
     </row>
     <row r="319">
       <c r="A319" s="5" t="n">
@@ -23551,7 +23145,6 @@
         <v/>
       </c>
       <c r="I319" t="inlineStr"/>
-      <c r="J319" t="inlineStr"/>
     </row>
     <row r="320">
       <c r="A320" s="5" t="n">
@@ -23589,7 +23182,6 @@
         <v/>
       </c>
       <c r="I320" t="inlineStr"/>
-      <c r="J320" t="inlineStr"/>
     </row>
     <row r="321">
       <c r="A321" s="5" t="n">
@@ -23627,7 +23219,6 @@
         <v/>
       </c>
       <c r="I321" t="inlineStr"/>
-      <c r="J321" t="inlineStr"/>
     </row>
     <row r="322">
       <c r="A322" s="5" t="n">
@@ -23665,7 +23256,6 @@
         <v/>
       </c>
       <c r="I322" t="inlineStr"/>
-      <c r="J322" t="inlineStr"/>
     </row>
     <row r="323">
       <c r="A323" s="5" t="n">
@@ -23703,7 +23293,6 @@
         <v/>
       </c>
       <c r="I323" t="inlineStr"/>
-      <c r="J323" t="inlineStr"/>
     </row>
     <row r="324">
       <c r="A324" s="5" t="n">
@@ -23741,7 +23330,6 @@
         <v/>
       </c>
       <c r="I324" t="inlineStr"/>
-      <c r="J324" t="inlineStr"/>
     </row>
     <row r="325">
       <c r="A325" s="5" t="n">
@@ -23779,7 +23367,6 @@
         <v/>
       </c>
       <c r="I325" t="inlineStr"/>
-      <c r="J325" t="inlineStr"/>
     </row>
     <row r="326">
       <c r="A326" s="5" t="n">
@@ -23817,7 +23404,6 @@
         <v/>
       </c>
       <c r="I326" t="inlineStr"/>
-      <c r="J326" t="inlineStr"/>
     </row>
     <row r="327">
       <c r="A327" s="5" t="n">
@@ -23855,7 +23441,6 @@
         <v/>
       </c>
       <c r="I327" t="inlineStr"/>
-      <c r="J327" t="inlineStr"/>
     </row>
     <row r="328">
       <c r="A328" s="5" t="n">
@@ -23893,7 +23478,6 @@
         <v/>
       </c>
       <c r="I328" t="inlineStr"/>
-      <c r="J328" t="inlineStr"/>
     </row>
     <row r="329">
       <c r="A329" s="5" t="n">
@@ -23931,7 +23515,6 @@
         <v/>
       </c>
       <c r="I329" t="inlineStr"/>
-      <c r="J329" t="inlineStr"/>
     </row>
     <row r="330">
       <c r="A330" s="5" t="n">
@@ -23969,7 +23552,6 @@
         <v/>
       </c>
       <c r="I330" t="inlineStr"/>
-      <c r="J330" t="inlineStr"/>
     </row>
     <row r="331">
       <c r="A331" s="5" t="n">
@@ -24007,7 +23589,6 @@
         <v/>
       </c>
       <c r="I331" t="inlineStr"/>
-      <c r="J331" t="inlineStr"/>
     </row>
     <row r="332">
       <c r="A332" s="5" t="n">
@@ -24045,7 +23626,6 @@
         <v/>
       </c>
       <c r="I332" t="inlineStr"/>
-      <c r="J332" t="inlineStr"/>
     </row>
     <row r="333">
       <c r="A333" s="5" t="n">
@@ -24083,7 +23663,6 @@
         <v/>
       </c>
       <c r="I333" t="inlineStr"/>
-      <c r="J333" t="inlineStr"/>
     </row>
     <row r="334">
       <c r="A334" s="5" t="n">
@@ -24121,7 +23700,6 @@
         <v/>
       </c>
       <c r="I334" t="inlineStr"/>
-      <c r="J334" t="inlineStr"/>
     </row>
     <row r="335">
       <c r="A335" s="5" t="n">
@@ -24159,11 +23737,6 @@
         <v/>
       </c>
       <c r="I335" t="inlineStr"/>
-      <c r="J335" t="inlineStr">
-        <is>
-          <t>Bryan</t>
-        </is>
-      </c>
     </row>
     <row r="336">
       <c r="A336" s="5" t="n">
@@ -24201,11 +23774,6 @@
         <v/>
       </c>
       <c r="I336" t="inlineStr"/>
-      <c r="J336" t="inlineStr">
-        <is>
-          <t>Casey</t>
-        </is>
-      </c>
     </row>
     <row r="337">
       <c r="A337" s="5" t="n">
@@ -24243,7 +23811,6 @@
         <v/>
       </c>
       <c r="I337" t="inlineStr"/>
-      <c r="J337" t="inlineStr"/>
     </row>
     <row r="338">
       <c r="A338" s="5" t="n">
@@ -24281,7 +23848,6 @@
         <v/>
       </c>
       <c r="I338" t="inlineStr"/>
-      <c r="J338" t="inlineStr"/>
     </row>
     <row r="339">
       <c r="A339" s="5" t="n">
@@ -24319,7 +23885,6 @@
         <v/>
       </c>
       <c r="I339" t="inlineStr"/>
-      <c r="J339" t="inlineStr"/>
     </row>
     <row r="340">
       <c r="A340" s="5" t="n">
@@ -24357,7 +23922,6 @@
         <v/>
       </c>
       <c r="I340" t="inlineStr"/>
-      <c r="J340" t="inlineStr"/>
     </row>
     <row r="341">
       <c r="A341" s="5" t="n">
@@ -24395,7 +23959,6 @@
         <v/>
       </c>
       <c r="I341" t="inlineStr"/>
-      <c r="J341" t="inlineStr"/>
     </row>
     <row r="342">
       <c r="A342" s="5" t="n">
@@ -24433,7 +23996,6 @@
         <v/>
       </c>
       <c r="I342" t="inlineStr"/>
-      <c r="J342" t="inlineStr"/>
     </row>
     <row r="343">
       <c r="A343" s="5" t="n">
@@ -24471,7 +24033,6 @@
         <v/>
       </c>
       <c r="I343" t="inlineStr"/>
-      <c r="J343" t="inlineStr"/>
     </row>
     <row r="344">
       <c r="A344" s="5" t="n">
@@ -24509,7 +24070,6 @@
         <v/>
       </c>
       <c r="I344" t="inlineStr"/>
-      <c r="J344" t="inlineStr"/>
     </row>
     <row r="345">
       <c r="A345" s="5" t="n">
@@ -24547,7 +24107,6 @@
         <v/>
       </c>
       <c r="I345" t="inlineStr"/>
-      <c r="J345" t="inlineStr"/>
     </row>
     <row r="346">
       <c r="A346" s="5" t="n">
@@ -24585,7 +24144,6 @@
         <v/>
       </c>
       <c r="I346" t="inlineStr"/>
-      <c r="J346" t="inlineStr"/>
     </row>
     <row r="347">
       <c r="A347" s="5" t="n">
@@ -24623,7 +24181,6 @@
         <v/>
       </c>
       <c r="I347" t="inlineStr"/>
-      <c r="J347" t="inlineStr"/>
     </row>
     <row r="348">
       <c r="A348" s="5" t="n">
@@ -24661,7 +24218,6 @@
         <v/>
       </c>
       <c r="I348" t="inlineStr"/>
-      <c r="J348" t="inlineStr"/>
     </row>
     <row r="349">
       <c r="A349" s="5" t="n">
@@ -24699,7 +24255,6 @@
         <v/>
       </c>
       <c r="I349" t="inlineStr"/>
-      <c r="J349" t="inlineStr"/>
     </row>
     <row r="350">
       <c r="A350" s="5" t="n">
@@ -24737,7 +24292,6 @@
         <v/>
       </c>
       <c r="I350" t="inlineStr"/>
-      <c r="J350" t="inlineStr"/>
     </row>
     <row r="351">
       <c r="A351" s="5" t="n">
@@ -24775,7 +24329,6 @@
         <v/>
       </c>
       <c r="I351" t="inlineStr"/>
-      <c r="J351" t="inlineStr"/>
     </row>
     <row r="352">
       <c r="A352" s="5" t="n">
@@ -24813,7 +24366,6 @@
         <v/>
       </c>
       <c r="I352" t="inlineStr"/>
-      <c r="J352" t="inlineStr"/>
     </row>
     <row r="353">
       <c r="A353" s="5" t="n">
@@ -24851,7 +24403,6 @@
         <v/>
       </c>
       <c r="I353" t="inlineStr"/>
-      <c r="J353" t="inlineStr"/>
     </row>
     <row r="354">
       <c r="A354" s="5" t="n">
@@ -24889,11 +24440,6 @@
         <v/>
       </c>
       <c r="I354" t="inlineStr"/>
-      <c r="J354" t="inlineStr">
-        <is>
-          <t>Casey</t>
-        </is>
-      </c>
     </row>
     <row r="355">
       <c r="A355" s="5" t="n">
@@ -24931,7 +24477,6 @@
         <v/>
       </c>
       <c r="I355" t="inlineStr"/>
-      <c r="J355" t="inlineStr"/>
     </row>
     <row r="356">
       <c r="A356" s="5" t="n">
@@ -24969,7 +24514,6 @@
         <v/>
       </c>
       <c r="I356" t="inlineStr"/>
-      <c r="J356" t="inlineStr"/>
     </row>
     <row r="357">
       <c r="A357" s="5" t="n">
@@ -25007,7 +24551,6 @@
         <v/>
       </c>
       <c r="I357" t="inlineStr"/>
-      <c r="J357" t="inlineStr"/>
     </row>
     <row r="358">
       <c r="A358" s="5" t="n">
@@ -25045,7 +24588,6 @@
         <v/>
       </c>
       <c r="I358" t="inlineStr"/>
-      <c r="J358" t="inlineStr"/>
     </row>
     <row r="359">
       <c r="A359" s="5" t="n">
@@ -25083,7 +24625,6 @@
         <v/>
       </c>
       <c r="I359" t="inlineStr"/>
-      <c r="J359" t="inlineStr"/>
     </row>
     <row r="360">
       <c r="A360" s="5" t="n">
@@ -25121,7 +24662,6 @@
         <v/>
       </c>
       <c r="I360" t="inlineStr"/>
-      <c r="J360" t="inlineStr"/>
     </row>
     <row r="361">
       <c r="A361" s="5" t="n">
@@ -25159,7 +24699,6 @@
         <v/>
       </c>
       <c r="I361" t="inlineStr"/>
-      <c r="J361" t="inlineStr"/>
     </row>
     <row r="362">
       <c r="A362" s="5" t="n">
@@ -25197,7 +24736,6 @@
         <v/>
       </c>
       <c r="I362" t="inlineStr"/>
-      <c r="J362" t="inlineStr"/>
     </row>
     <row r="363">
       <c r="A363" s="5" t="n">
@@ -25235,7 +24773,6 @@
         <v/>
       </c>
       <c r="I363" t="inlineStr"/>
-      <c r="J363" t="inlineStr"/>
     </row>
     <row r="364">
       <c r="A364" s="5" t="n">
@@ -25273,7 +24810,6 @@
         <v/>
       </c>
       <c r="I364" t="inlineStr"/>
-      <c r="J364" t="inlineStr"/>
     </row>
     <row r="365">
       <c r="A365" s="5" t="n">
@@ -25311,7 +24847,6 @@
         <v/>
       </c>
       <c r="I365" t="inlineStr"/>
-      <c r="J365" t="inlineStr"/>
     </row>
     <row r="366">
       <c r="A366" s="5" t="n">
@@ -25349,7 +24884,6 @@
         <v/>
       </c>
       <c r="I366" t="inlineStr"/>
-      <c r="J366" t="inlineStr"/>
     </row>
     <row r="367">
       <c r="A367" s="5" t="n">
@@ -25387,7 +24921,6 @@
         <v/>
       </c>
       <c r="I367" t="inlineStr"/>
-      <c r="J367" t="inlineStr"/>
     </row>
     <row r="368">
       <c r="A368" s="5" t="n">
@@ -25425,7 +24958,6 @@
         <v/>
       </c>
       <c r="I368" t="inlineStr"/>
-      <c r="J368" t="inlineStr"/>
     </row>
     <row r="369">
       <c r="A369" s="5" t="n">
@@ -25463,7 +24995,6 @@
         <v/>
       </c>
       <c r="I369" t="inlineStr"/>
-      <c r="J369" t="inlineStr"/>
     </row>
     <row r="370">
       <c r="A370" s="5" t="n">
@@ -25501,7 +25032,6 @@
         <v/>
       </c>
       <c r="I370" t="inlineStr"/>
-      <c r="J370" t="inlineStr"/>
     </row>
     <row r="371">
       <c r="A371" s="5" t="n">
@@ -25539,7 +25069,6 @@
         <v/>
       </c>
       <c r="I371" t="inlineStr"/>
-      <c r="J371" t="inlineStr"/>
     </row>
     <row r="372">
       <c r="A372" s="5" t="n">
@@ -25577,11 +25106,6 @@
         <v/>
       </c>
       <c r="I372" t="inlineStr"/>
-      <c r="J372" t="inlineStr">
-        <is>
-          <t>Casey</t>
-        </is>
-      </c>
     </row>
     <row r="373">
       <c r="A373" s="5" t="n">
@@ -25619,7 +25143,6 @@
         <v/>
       </c>
       <c r="I373" t="inlineStr"/>
-      <c r="J373" t="inlineStr"/>
     </row>
     <row r="374">
       <c r="A374" s="5" t="n">
@@ -25657,7 +25180,6 @@
         <v/>
       </c>
       <c r="I374" t="inlineStr"/>
-      <c r="J374" t="inlineStr"/>
     </row>
     <row r="375">
       <c r="A375" s="5" t="n">
@@ -25695,7 +25217,6 @@
         <v/>
       </c>
       <c r="I375" t="inlineStr"/>
-      <c r="J375" t="inlineStr"/>
     </row>
     <row r="376">
       <c r="A376" s="5" t="n">
@@ -25733,7 +25254,6 @@
         <v/>
       </c>
       <c r="I376" t="inlineStr"/>
-      <c r="J376" t="inlineStr"/>
     </row>
     <row r="377">
       <c r="A377" s="5" t="n">
@@ -25771,7 +25291,6 @@
         <v/>
       </c>
       <c r="I377" t="inlineStr"/>
-      <c r="J377" t="inlineStr"/>
     </row>
     <row r="378">
       <c r="A378" s="5" t="n">
@@ -25809,7 +25328,6 @@
         <v/>
       </c>
       <c r="I378" t="inlineStr"/>
-      <c r="J378" t="inlineStr"/>
     </row>
     <row r="379">
       <c r="A379" s="5" t="n">
@@ -25847,7 +25365,6 @@
         <v/>
       </c>
       <c r="I379" t="inlineStr"/>
-      <c r="J379" t="inlineStr"/>
     </row>
     <row r="380">
       <c r="A380" s="5" t="n">
@@ -25885,7 +25402,6 @@
         <v/>
       </c>
       <c r="I380" t="inlineStr"/>
-      <c r="J380" t="inlineStr"/>
     </row>
     <row r="381">
       <c r="A381" s="5" t="n">
@@ -25923,7 +25439,6 @@
         <v/>
       </c>
       <c r="I381" t="inlineStr"/>
-      <c r="J381" t="inlineStr"/>
     </row>
     <row r="382">
       <c r="A382" s="5" t="n">
@@ -25961,7 +25476,6 @@
         <v/>
       </c>
       <c r="I382" t="inlineStr"/>
-      <c r="J382" t="inlineStr"/>
     </row>
     <row r="383">
       <c r="A383" s="5" t="n">
@@ -25999,7 +25513,6 @@
         <v/>
       </c>
       <c r="I383" t="inlineStr"/>
-      <c r="J383" t="inlineStr"/>
     </row>
     <row r="384">
       <c r="A384" s="5" t="n">
@@ -26037,7 +25550,6 @@
         <v/>
       </c>
       <c r="I384" t="inlineStr"/>
-      <c r="J384" t="inlineStr"/>
     </row>
     <row r="385">
       <c r="A385" s="5" t="n">
@@ -26075,7 +25587,6 @@
         <v/>
       </c>
       <c r="I385" t="inlineStr"/>
-      <c r="J385" t="inlineStr"/>
     </row>
     <row r="386">
       <c r="A386" s="5" t="n">
@@ -26113,7 +25624,6 @@
         <v/>
       </c>
       <c r="I386" t="inlineStr"/>
-      <c r="J386" t="inlineStr"/>
     </row>
     <row r="387">
       <c r="A387" s="5" t="n">
@@ -26151,7 +25661,6 @@
         <v/>
       </c>
       <c r="I387" t="inlineStr"/>
-      <c r="J387" t="inlineStr"/>
     </row>
     <row r="388">
       <c r="A388" s="5" t="n">
@@ -26189,7 +25698,6 @@
         <v/>
       </c>
       <c r="I388" t="inlineStr"/>
-      <c r="J388" t="inlineStr"/>
     </row>
     <row r="389">
       <c r="A389" s="5" t="n">
@@ -26227,7 +25735,6 @@
         <v/>
       </c>
       <c r="I389" t="inlineStr"/>
-      <c r="J389" t="inlineStr"/>
     </row>
     <row r="390">
       <c r="A390" s="5" t="n">
@@ -26265,7 +25772,6 @@
         <v/>
       </c>
       <c r="I390" t="inlineStr"/>
-      <c r="J390" t="inlineStr"/>
     </row>
     <row r="391">
       <c r="A391" s="5" t="n">
@@ -26303,11 +25809,6 @@
         <v/>
       </c>
       <c r="I391" t="inlineStr"/>
-      <c r="J391" t="inlineStr">
-        <is>
-          <t>Casey</t>
-        </is>
-      </c>
     </row>
     <row r="392">
       <c r="A392" s="5" t="n">
@@ -26345,7 +25846,6 @@
         <v/>
       </c>
       <c r="I392" t="inlineStr"/>
-      <c r="J392" t="inlineStr"/>
     </row>
     <row r="393">
       <c r="A393" s="5" t="n">
@@ -26383,7 +25883,6 @@
         <v/>
       </c>
       <c r="I393" t="inlineStr"/>
-      <c r="J393" t="inlineStr"/>
     </row>
     <row r="394">
       <c r="A394" s="5" t="n">
@@ -26421,7 +25920,6 @@
         <v/>
       </c>
       <c r="I394" t="inlineStr"/>
-      <c r="J394" t="inlineStr"/>
     </row>
     <row r="395">
       <c r="A395" s="5" t="n">
@@ -26459,7 +25957,6 @@
         <v/>
       </c>
       <c r="I395" t="inlineStr"/>
-      <c r="J395" t="inlineStr"/>
     </row>
     <row r="396">
       <c r="A396" s="5" t="n">
@@ -26497,7 +25994,6 @@
         <v/>
       </c>
       <c r="I396" t="inlineStr"/>
-      <c r="J396" t="inlineStr"/>
     </row>
     <row r="397">
       <c r="A397" s="5" t="n">
@@ -26535,7 +26031,6 @@
         <v/>
       </c>
       <c r="I397" t="inlineStr"/>
-      <c r="J397" t="inlineStr"/>
     </row>
     <row r="398">
       <c r="A398" s="5" t="n">
@@ -26573,7 +26068,6 @@
         <v/>
       </c>
       <c r="I398" t="inlineStr"/>
-      <c r="J398" t="inlineStr"/>
     </row>
     <row r="399">
       <c r="A399" s="5" t="n">
@@ -26611,7 +26105,6 @@
         <v/>
       </c>
       <c r="I399" t="inlineStr"/>
-      <c r="J399" t="inlineStr"/>
     </row>
     <row r="400">
       <c r="A400" s="5" t="n">
@@ -26649,7 +26142,6 @@
         <v/>
       </c>
       <c r="I400" t="inlineStr"/>
-      <c r="J400" t="inlineStr"/>
     </row>
     <row r="401">
       <c r="A401" s="5" t="n">
@@ -26687,11 +26179,6 @@
         <v/>
       </c>
       <c r="I401" t="inlineStr"/>
-      <c r="J401" t="inlineStr">
-        <is>
-          <t>Bryan</t>
-        </is>
-      </c>
     </row>
     <row r="402">
       <c r="A402" s="5" t="n">
@@ -26729,11 +26216,6 @@
         <v/>
       </c>
       <c r="I402" t="inlineStr"/>
-      <c r="J402" t="inlineStr">
-        <is>
-          <t>Bryan</t>
-        </is>
-      </c>
     </row>
     <row r="403">
       <c r="A403" s="5" t="n">
@@ -26771,11 +26253,6 @@
         <v/>
       </c>
       <c r="I403" t="inlineStr"/>
-      <c r="J403" t="inlineStr">
-        <is>
-          <t>Casey</t>
-        </is>
-      </c>
     </row>
     <row r="404">
       <c r="A404" s="5" t="n">
@@ -26813,7 +26290,6 @@
         <v/>
       </c>
       <c r="I404" t="inlineStr"/>
-      <c r="J404" t="inlineStr"/>
     </row>
     <row r="405">
       <c r="A405" s="5" t="n">
@@ -26851,7 +26327,6 @@
         <v/>
       </c>
       <c r="I405" t="inlineStr"/>
-      <c r="J405" t="inlineStr"/>
     </row>
     <row r="406">
       <c r="A406" s="5" t="n">
@@ -26889,7 +26364,6 @@
         <v/>
       </c>
       <c r="I406" t="inlineStr"/>
-      <c r="J406" t="inlineStr"/>
     </row>
     <row r="407">
       <c r="A407" s="5" t="n">
@@ -26927,7 +26401,6 @@
         <v/>
       </c>
       <c r="I407" t="inlineStr"/>
-      <c r="J407" t="inlineStr"/>
     </row>
     <row r="408">
       <c r="A408" s="5" t="n">
@@ -26965,7 +26438,6 @@
         <v/>
       </c>
       <c r="I408" t="inlineStr"/>
-      <c r="J408" t="inlineStr"/>
     </row>
     <row r="409">
       <c r="A409" s="5" t="n">
@@ -27003,7 +26475,6 @@
         <v/>
       </c>
       <c r="I409" t="inlineStr"/>
-      <c r="J409" t="inlineStr"/>
     </row>
     <row r="410">
       <c r="A410" s="5" t="n">
@@ -27041,7 +26512,6 @@
         <v/>
       </c>
       <c r="I410" t="inlineStr"/>
-      <c r="J410" t="inlineStr"/>
     </row>
     <row r="411">
       <c r="A411" s="5" t="n">
@@ -27079,7 +26549,6 @@
         <v/>
       </c>
       <c r="I411" t="inlineStr"/>
-      <c r="J411" t="inlineStr"/>
     </row>
     <row r="412">
       <c r="A412" s="5" t="n">
@@ -27117,7 +26586,6 @@
         <v/>
       </c>
       <c r="I412" t="inlineStr"/>
-      <c r="J412" t="inlineStr"/>
     </row>
     <row r="413">
       <c r="A413" s="5" t="n">
@@ -27155,11 +26623,6 @@
         <v/>
       </c>
       <c r="I413" t="inlineStr"/>
-      <c r="J413" t="inlineStr">
-        <is>
-          <t>Bryan</t>
-        </is>
-      </c>
     </row>
     <row r="414">
       <c r="A414" s="5" t="n">
@@ -27197,11 +26660,6 @@
         <v/>
       </c>
       <c r="I414" t="inlineStr"/>
-      <c r="J414" t="inlineStr">
-        <is>
-          <t>Casey</t>
-        </is>
-      </c>
     </row>
     <row r="415">
       <c r="A415" s="5" t="n">
@@ -27239,7 +26697,6 @@
         <v/>
       </c>
       <c r="I415" t="inlineStr"/>
-      <c r="J415" t="inlineStr"/>
     </row>
     <row r="416">
       <c r="A416" s="5" t="n">
@@ -27277,7 +26734,6 @@
         <v/>
       </c>
       <c r="I416" t="inlineStr"/>
-      <c r="J416" t="inlineStr"/>
     </row>
     <row r="417">
       <c r="A417" s="5" t="n">
@@ -27315,7 +26771,6 @@
         <v/>
       </c>
       <c r="I417" t="inlineStr"/>
-      <c r="J417" t="inlineStr"/>
     </row>
     <row r="418">
       <c r="A418" s="5" t="n">
@@ -27353,7 +26808,6 @@
         <v/>
       </c>
       <c r="I418" t="inlineStr"/>
-      <c r="J418" t="inlineStr"/>
     </row>
     <row r="419">
       <c r="A419" s="5" t="n">
@@ -27391,7 +26845,6 @@
         <v/>
       </c>
       <c r="I419" t="inlineStr"/>
-      <c r="J419" t="inlineStr"/>
     </row>
     <row r="420">
       <c r="A420" s="5" t="n">
@@ -27429,7 +26882,6 @@
         <v/>
       </c>
       <c r="I420" t="inlineStr"/>
-      <c r="J420" t="inlineStr"/>
     </row>
     <row r="421">
       <c r="A421" s="5" t="n">
@@ -27467,7 +26919,6 @@
         <v/>
       </c>
       <c r="I421" t="inlineStr"/>
-      <c r="J421" t="inlineStr"/>
     </row>
     <row r="422">
       <c r="A422" s="5" t="n">
@@ -27505,7 +26956,6 @@
         <v/>
       </c>
       <c r="I422" t="inlineStr"/>
-      <c r="J422" t="inlineStr"/>
     </row>
     <row r="423">
       <c r="A423" s="5" t="n">
@@ -27543,7 +26993,6 @@
         <v/>
       </c>
       <c r="I423" t="inlineStr"/>
-      <c r="J423" t="inlineStr"/>
     </row>
     <row r="424">
       <c r="A424" s="5" t="n">
@@ -27581,7 +27030,6 @@
         <v/>
       </c>
       <c r="I424" t="inlineStr"/>
-      <c r="J424" t="inlineStr"/>
     </row>
     <row r="425">
       <c r="A425" s="5" t="n">
@@ -27619,7 +27067,6 @@
         <v/>
       </c>
       <c r="I425" t="inlineStr"/>
-      <c r="J425" t="inlineStr"/>
     </row>
     <row r="426">
       <c r="A426" s="5" t="n">
@@ -27657,7 +27104,6 @@
         <v/>
       </c>
       <c r="I426" t="inlineStr"/>
-      <c r="J426" t="inlineStr"/>
     </row>
     <row r="427">
       <c r="A427" s="5" t="n">
@@ -27695,7 +27141,6 @@
         <v/>
       </c>
       <c r="I427" t="inlineStr"/>
-      <c r="J427" t="inlineStr"/>
     </row>
     <row r="428">
       <c r="A428" s="5" t="n">
@@ -27733,7 +27178,6 @@
         <v/>
       </c>
       <c r="I428" t="inlineStr"/>
-      <c r="J428" t="inlineStr"/>
     </row>
     <row r="429">
       <c r="A429" s="5" t="n">
@@ -27771,7 +27215,6 @@
         <v/>
       </c>
       <c r="I429" t="inlineStr"/>
-      <c r="J429" t="inlineStr"/>
     </row>
     <row r="430">
       <c r="A430" s="5" t="n">
@@ -27809,7 +27252,6 @@
         <v/>
       </c>
       <c r="I430" t="inlineStr"/>
-      <c r="J430" t="inlineStr"/>
     </row>
     <row r="431">
       <c r="A431" s="5" t="n">
@@ -27847,7 +27289,6 @@
         <v/>
       </c>
       <c r="I431" t="inlineStr"/>
-      <c r="J431" t="inlineStr"/>
     </row>
     <row r="432">
       <c r="A432" s="5" t="n">
@@ -27885,7 +27326,6 @@
         <v/>
       </c>
       <c r="I432" t="inlineStr"/>
-      <c r="J432" t="inlineStr"/>
     </row>
     <row r="433">
       <c r="A433" s="5" t="n">
@@ -27923,7 +27363,6 @@
         <v/>
       </c>
       <c r="I433" t="inlineStr"/>
-      <c r="J433" t="inlineStr"/>
     </row>
     <row r="434">
       <c r="A434" s="5" t="n">
@@ -27961,11 +27400,6 @@
         <v/>
       </c>
       <c r="I434" t="inlineStr"/>
-      <c r="J434" t="inlineStr">
-        <is>
-          <t>Bryan</t>
-        </is>
-      </c>
     </row>
     <row r="435">
       <c r="A435" s="5" t="n">
@@ -28003,11 +27437,6 @@
         <v/>
       </c>
       <c r="I435" t="inlineStr"/>
-      <c r="J435" t="inlineStr">
-        <is>
-          <t>Bryan</t>
-        </is>
-      </c>
     </row>
     <row r="436">
       <c r="A436" s="5" t="n">
@@ -28045,11 +27474,6 @@
         <v/>
       </c>
       <c r="I436" t="inlineStr"/>
-      <c r="J436" t="inlineStr">
-        <is>
-          <t>Casey</t>
-        </is>
-      </c>
     </row>
     <row r="437">
       <c r="A437" s="5" t="n">
@@ -28087,7 +27511,6 @@
         <v/>
       </c>
       <c r="I437" t="inlineStr"/>
-      <c r="J437" t="inlineStr"/>
     </row>
     <row r="438">
       <c r="A438" s="5" t="n">
@@ -28125,7 +27548,6 @@
         <v/>
       </c>
       <c r="I438" t="inlineStr"/>
-      <c r="J438" t="inlineStr"/>
     </row>
     <row r="439">
       <c r="A439" s="5" t="n">
@@ -28163,7 +27585,6 @@
         <v/>
       </c>
       <c r="I439" t="inlineStr"/>
-      <c r="J439" t="inlineStr"/>
     </row>
     <row r="440">
       <c r="A440" s="5" t="n">
@@ -28201,7 +27622,6 @@
         <v/>
       </c>
       <c r="I440" t="inlineStr"/>
-      <c r="J440" t="inlineStr"/>
     </row>
     <row r="441">
       <c r="A441" s="5" t="n">
@@ -28239,7 +27659,6 @@
         <v/>
       </c>
       <c r="I441" t="inlineStr"/>
-      <c r="J441" t="inlineStr"/>
     </row>
     <row r="442">
       <c r="A442" s="5" t="n">
@@ -28277,7 +27696,6 @@
         <v/>
       </c>
       <c r="I442" t="inlineStr"/>
-      <c r="J442" t="inlineStr"/>
     </row>
     <row r="443">
       <c r="A443" s="5" t="n">
@@ -28315,7 +27733,6 @@
         <v/>
       </c>
       <c r="I443" t="inlineStr"/>
-      <c r="J443" t="inlineStr"/>
     </row>
     <row r="444">
       <c r="A444" s="5" t="n">
@@ -28353,7 +27770,6 @@
         <v/>
       </c>
       <c r="I444" t="inlineStr"/>
-      <c r="J444" t="inlineStr"/>
     </row>
     <row r="445">
       <c r="A445" s="5" t="n">
@@ -28391,7 +27807,6 @@
         <v/>
       </c>
       <c r="I445" t="inlineStr"/>
-      <c r="J445" t="inlineStr"/>
     </row>
     <row r="446">
       <c r="A446" s="5" t="n">
@@ -28429,7 +27844,6 @@
         <v/>
       </c>
       <c r="I446" t="inlineStr"/>
-      <c r="J446" t="inlineStr"/>
     </row>
     <row r="447">
       <c r="A447" s="5" t="n">
@@ -28467,7 +27881,6 @@
         <v/>
       </c>
       <c r="I447" t="inlineStr"/>
-      <c r="J447" t="inlineStr"/>
     </row>
     <row r="448">
       <c r="A448" s="5" t="n">
@@ -28505,11 +27918,6 @@
         <v/>
       </c>
       <c r="I448" t="inlineStr"/>
-      <c r="J448" t="inlineStr">
-        <is>
-          <t>Bryan</t>
-        </is>
-      </c>
     </row>
     <row r="449">
       <c r="A449" s="5" t="n">
@@ -28547,7 +27955,6 @@
         <v/>
       </c>
       <c r="I449" t="inlineStr"/>
-      <c r="J449" t="inlineStr"/>
     </row>
     <row r="450">
       <c r="A450" s="5" t="n">
@@ -28585,7 +27992,6 @@
         <v/>
       </c>
       <c r="I450" t="inlineStr"/>
-      <c r="J450" t="inlineStr"/>
     </row>
     <row r="451">
       <c r="A451" s="5" t="n">
@@ -28623,7 +28029,6 @@
         <v/>
       </c>
       <c r="I451" t="inlineStr"/>
-      <c r="J451" t="inlineStr"/>
     </row>
     <row r="452">
       <c r="A452" s="5" t="n">
@@ -28661,7 +28066,6 @@
         <v/>
       </c>
       <c r="I452" t="inlineStr"/>
-      <c r="J452" t="inlineStr"/>
     </row>
     <row r="453">
       <c r="A453" s="5" t="n">
@@ -28699,7 +28103,6 @@
         <v/>
       </c>
       <c r="I453" t="inlineStr"/>
-      <c r="J453" t="inlineStr"/>
     </row>
     <row r="454">
       <c r="A454" s="5" t="n">
@@ -28737,7 +28140,6 @@
         <v/>
       </c>
       <c r="I454" t="inlineStr"/>
-      <c r="J454" t="inlineStr"/>
     </row>
     <row r="455">
       <c r="A455" s="5" t="n">
@@ -28775,7 +28177,6 @@
         <v/>
       </c>
       <c r="I455" t="inlineStr"/>
-      <c r="J455" t="inlineStr"/>
     </row>
     <row r="456">
       <c r="A456" s="5" t="n">
@@ -28813,7 +28214,6 @@
         <v/>
       </c>
       <c r="I456" t="inlineStr"/>
-      <c r="J456" t="inlineStr"/>
     </row>
     <row r="457">
       <c r="A457" s="5" t="n">
@@ -28851,7 +28251,6 @@
         <v/>
       </c>
       <c r="I457" t="inlineStr"/>
-      <c r="J457" t="inlineStr"/>
     </row>
     <row r="458">
       <c r="A458" s="5" t="n">
@@ -28889,7 +28288,6 @@
         <v/>
       </c>
       <c r="I458" t="inlineStr"/>
-      <c r="J458" t="inlineStr"/>
     </row>
     <row r="459">
       <c r="A459" s="5" t="n">
@@ -28927,7 +28325,6 @@
         <v/>
       </c>
       <c r="I459" t="inlineStr"/>
-      <c r="J459" t="inlineStr"/>
     </row>
     <row r="460">
       <c r="A460" s="5" t="n">
@@ -28965,7 +28362,6 @@
         <v/>
       </c>
       <c r="I460" t="inlineStr"/>
-      <c r="J460" t="inlineStr"/>
     </row>
     <row r="461">
       <c r="A461" s="5" t="n">
@@ -29003,7 +28399,6 @@
         <v/>
       </c>
       <c r="I461" t="inlineStr"/>
-      <c r="J461" t="inlineStr"/>
     </row>
     <row r="462">
       <c r="A462" s="5" t="n">
@@ -29041,7 +28436,6 @@
         <v/>
       </c>
       <c r="I462" t="inlineStr"/>
-      <c r="J462" t="inlineStr"/>
     </row>
     <row r="463">
       <c r="A463" s="5" t="n">
@@ -29079,7 +28473,6 @@
         <v/>
       </c>
       <c r="I463" t="inlineStr"/>
-      <c r="J463" t="inlineStr"/>
     </row>
     <row r="464">
       <c r="A464" s="5" t="n">
@@ -29117,7 +28510,6 @@
         <v/>
       </c>
       <c r="I464" t="inlineStr"/>
-      <c r="J464" t="inlineStr"/>
     </row>
     <row r="465">
       <c r="A465" s="5" t="n">
@@ -29155,7 +28547,6 @@
         <v/>
       </c>
       <c r="I465" t="inlineStr"/>
-      <c r="J465" t="inlineStr"/>
     </row>
     <row r="466">
       <c r="A466" s="5" t="n">
@@ -29193,7 +28584,6 @@
         <v/>
       </c>
       <c r="I466" t="inlineStr"/>
-      <c r="J466" t="inlineStr"/>
     </row>
     <row r="467">
       <c r="A467" s="5" t="n">
@@ -29231,7 +28621,6 @@
         <v/>
       </c>
       <c r="I467" t="inlineStr"/>
-      <c r="J467" t="inlineStr"/>
     </row>
     <row r="468">
       <c r="A468" s="5" t="n">
@@ -29269,7 +28658,6 @@
         <v/>
       </c>
       <c r="I468" t="inlineStr"/>
-      <c r="J468" t="inlineStr"/>
     </row>
     <row r="469">
       <c r="A469" s="5" t="n">
@@ -29307,7 +28695,6 @@
         <v/>
       </c>
       <c r="I469" t="inlineStr"/>
-      <c r="J469" t="inlineStr"/>
     </row>
     <row r="470">
       <c r="A470" s="5" t="n">
@@ -29345,11 +28732,6 @@
         <v/>
       </c>
       <c r="I470" t="inlineStr"/>
-      <c r="J470" t="inlineStr">
-        <is>
-          <t>Bryan</t>
-        </is>
-      </c>
     </row>
     <row r="471">
       <c r="A471" s="5" t="n">
@@ -29387,11 +28769,6 @@
         <v/>
       </c>
       <c r="I471" t="inlineStr"/>
-      <c r="J471" t="inlineStr">
-        <is>
-          <t>Casey</t>
-        </is>
-      </c>
     </row>
     <row r="472">
       <c r="A472" s="5" t="n">
@@ -29429,7 +28806,6 @@
         <v/>
       </c>
       <c r="I472" t="inlineStr"/>
-      <c r="J472" t="inlineStr"/>
     </row>
     <row r="473">
       <c r="A473" s="5" t="n">
@@ -29467,7 +28843,6 @@
         <v/>
       </c>
       <c r="I473" t="inlineStr"/>
-      <c r="J473" t="inlineStr"/>
     </row>
     <row r="474">
       <c r="A474" s="5" t="n">
@@ -29505,7 +28880,6 @@
         <v/>
       </c>
       <c r="I474" t="inlineStr"/>
-      <c r="J474" t="inlineStr"/>
     </row>
     <row r="475">
       <c r="A475" s="5" t="n">
@@ -29543,7 +28917,6 @@
         <v/>
       </c>
       <c r="I475" t="inlineStr"/>
-      <c r="J475" t="inlineStr"/>
     </row>
     <row r="476">
       <c r="A476" s="5" t="n">
@@ -29581,7 +28954,6 @@
         <v/>
       </c>
       <c r="I476" t="inlineStr"/>
-      <c r="J476" t="inlineStr"/>
     </row>
     <row r="477">
       <c r="A477" s="5" t="n">
@@ -29619,7 +28991,6 @@
         <v/>
       </c>
       <c r="I477" t="inlineStr"/>
-      <c r="J477" t="inlineStr"/>
     </row>
     <row r="478">
       <c r="A478" s="5" t="n">
@@ -29657,11 +29028,6 @@
         <v/>
       </c>
       <c r="I478" t="inlineStr"/>
-      <c r="J478" t="inlineStr">
-        <is>
-          <t>Bryan</t>
-        </is>
-      </c>
     </row>
     <row r="479">
       <c r="A479" s="5" t="n">
@@ -29699,11 +29065,6 @@
         <v/>
       </c>
       <c r="I479" t="inlineStr"/>
-      <c r="J479" t="inlineStr">
-        <is>
-          <t>Casey</t>
-        </is>
-      </c>
     </row>
     <row r="480">
       <c r="A480" s="5" t="n">
@@ -29741,7 +29102,6 @@
         <v/>
       </c>
       <c r="I480" t="inlineStr"/>
-      <c r="J480" t="inlineStr"/>
     </row>
     <row r="481">
       <c r="A481" s="5" t="n">
@@ -29779,7 +29139,6 @@
         <v/>
       </c>
       <c r="I481" t="inlineStr"/>
-      <c r="J481" t="inlineStr"/>
     </row>
     <row r="482">
       <c r="A482" s="5" t="n">
@@ -29817,7 +29176,6 @@
         <v/>
       </c>
       <c r="I482" t="inlineStr"/>
-      <c r="J482" t="inlineStr"/>
     </row>
     <row r="483">
       <c r="A483" s="5" t="n">
@@ -29855,7 +29213,6 @@
         <v/>
       </c>
       <c r="I483" t="inlineStr"/>
-      <c r="J483" t="inlineStr"/>
     </row>
     <row r="484">
       <c r="A484" s="5" t="n">
@@ -29893,7 +29250,6 @@
         <v/>
       </c>
       <c r="I484" t="inlineStr"/>
-      <c r="J484" t="inlineStr"/>
     </row>
     <row r="485">
       <c r="A485" s="5" t="n">
@@ -29931,7 +29287,6 @@
         <v/>
       </c>
       <c r="I485" t="inlineStr"/>
-      <c r="J485" t="inlineStr"/>
     </row>
     <row r="486">
       <c r="A486" s="5" t="n">
@@ -29969,7 +29324,6 @@
         <v/>
       </c>
       <c r="I486" t="inlineStr"/>
-      <c r="J486" t="inlineStr"/>
     </row>
     <row r="487">
       <c r="A487" s="5" t="n">
@@ -30007,7 +29361,6 @@
         <v/>
       </c>
       <c r="I487" t="inlineStr"/>
-      <c r="J487" t="inlineStr"/>
     </row>
     <row r="488">
       <c r="A488" s="5" t="n">
@@ -30045,7 +29398,6 @@
         <v/>
       </c>
       <c r="I488" t="inlineStr"/>
-      <c r="J488" t="inlineStr"/>
     </row>
     <row r="489">
       <c r="A489" s="5" t="n">
@@ -30083,7 +29435,6 @@
         <v/>
       </c>
       <c r="I489" t="inlineStr"/>
-      <c r="J489" t="inlineStr"/>
     </row>
     <row r="490">
       <c r="A490" s="5" t="n">
@@ -30121,7 +29472,6 @@
         <v/>
       </c>
       <c r="I490" t="inlineStr"/>
-      <c r="J490" t="inlineStr"/>
     </row>
     <row r="491">
       <c r="A491" s="5" t="n">
@@ -30159,7 +29509,6 @@
         <v/>
       </c>
       <c r="I491" t="inlineStr"/>
-      <c r="J491" t="inlineStr"/>
     </row>
     <row r="492">
       <c r="A492" s="5" t="n">
@@ -30197,7 +29546,6 @@
         <v/>
       </c>
       <c r="I492" t="inlineStr"/>
-      <c r="J492" t="inlineStr"/>
     </row>
     <row r="493">
       <c r="A493" s="5" t="n">
@@ -30235,7 +29583,6 @@
         <v/>
       </c>
       <c r="I493" t="inlineStr"/>
-      <c r="J493" t="inlineStr"/>
     </row>
     <row r="494">
       <c r="A494" s="5" t="n">
@@ -30273,7 +29620,6 @@
         <v/>
       </c>
       <c r="I494" t="inlineStr"/>
-      <c r="J494" t="inlineStr"/>
     </row>
     <row r="495">
       <c r="A495" s="5" t="n">
@@ -30311,7 +29657,6 @@
         <v/>
       </c>
       <c r="I495" t="inlineStr"/>
-      <c r="J495" t="inlineStr"/>
     </row>
     <row r="496">
       <c r="A496" s="5" t="n">
@@ -30349,7 +29694,6 @@
         <v/>
       </c>
       <c r="I496" t="inlineStr"/>
-      <c r="J496" t="inlineStr"/>
     </row>
     <row r="497">
       <c r="A497" s="5" t="n">
@@ -30387,7 +29731,6 @@
         <v/>
       </c>
       <c r="I497" t="inlineStr"/>
-      <c r="J497" t="inlineStr"/>
     </row>
     <row r="498">
       <c r="A498" s="5" t="n">
@@ -30425,11 +29768,6 @@
         <v/>
       </c>
       <c r="I498" t="inlineStr"/>
-      <c r="J498" t="inlineStr">
-        <is>
-          <t>Bryan</t>
-        </is>
-      </c>
     </row>
     <row r="499">
       <c r="A499" s="5" t="n">
@@ -30467,11 +29805,6 @@
         <v/>
       </c>
       <c r="I499" t="inlineStr"/>
-      <c r="J499" t="inlineStr">
-        <is>
-          <t>Casey</t>
-        </is>
-      </c>
     </row>
     <row r="500">
       <c r="A500" s="5" t="n">
@@ -30509,7 +29842,6 @@
         <v/>
       </c>
       <c r="I500" t="inlineStr"/>
-      <c r="J500" t="inlineStr"/>
     </row>
     <row r="501">
       <c r="A501" s="5" t="n">
@@ -30547,7 +29879,6 @@
         <v/>
       </c>
       <c r="I501" t="inlineStr"/>
-      <c r="J501" t="inlineStr"/>
     </row>
     <row r="502">
       <c r="A502" s="5" t="n">
@@ -30585,7 +29916,6 @@
         <v/>
       </c>
       <c r="I502" t="inlineStr"/>
-      <c r="J502" t="inlineStr"/>
     </row>
     <row r="503">
       <c r="A503" s="5" t="n">
@@ -30623,7 +29953,6 @@
         <v/>
       </c>
       <c r="I503" t="inlineStr"/>
-      <c r="J503" t="inlineStr"/>
     </row>
     <row r="504">
       <c r="A504" s="5" t="n">
@@ -30661,7 +29990,6 @@
         <v/>
       </c>
       <c r="I504" t="inlineStr"/>
-      <c r="J504" t="inlineStr"/>
     </row>
     <row r="505">
       <c r="A505" s="5" t="n">
@@ -30699,7 +30027,6 @@
         <v/>
       </c>
       <c r="I505" t="inlineStr"/>
-      <c r="J505" t="inlineStr"/>
     </row>
     <row r="506">
       <c r="A506" s="5" t="n">
@@ -30737,7 +30064,6 @@
         <v/>
       </c>
       <c r="I506" t="inlineStr"/>
-      <c r="J506" t="inlineStr"/>
     </row>
     <row r="507">
       <c r="A507" s="5" t="n">
@@ -30775,7 +30101,6 @@
         <v/>
       </c>
       <c r="I507" t="inlineStr"/>
-      <c r="J507" t="inlineStr"/>
     </row>
     <row r="508">
       <c r="A508" s="5" t="n">
@@ -30813,7 +30138,6 @@
         <v/>
       </c>
       <c r="I508" t="inlineStr"/>
-      <c r="J508" t="inlineStr"/>
     </row>
     <row r="509">
       <c r="A509" s="5" t="n">
@@ -30851,11 +30175,6 @@
         <v/>
       </c>
       <c r="I509" t="inlineStr"/>
-      <c r="J509" t="inlineStr">
-        <is>
-          <t>Bryan</t>
-        </is>
-      </c>
     </row>
     <row r="510">
       <c r="A510" s="5" t="n">
@@ -30893,11 +30212,6 @@
         <v/>
       </c>
       <c r="I510" t="inlineStr"/>
-      <c r="J510" t="inlineStr">
-        <is>
-          <t>Casey</t>
-        </is>
-      </c>
     </row>
     <row r="511">
       <c r="A511" s="5" t="n">
@@ -30935,7 +30249,6 @@
         <v/>
       </c>
       <c r="I511" t="inlineStr"/>
-      <c r="J511" t="inlineStr"/>
     </row>
     <row r="512">
       <c r="A512" s="5" t="n">
@@ -30973,7 +30286,6 @@
         <v/>
       </c>
       <c r="I512" t="inlineStr"/>
-      <c r="J512" t="inlineStr"/>
     </row>
     <row r="513">
       <c r="A513" s="5" t="n">
@@ -31011,7 +30323,6 @@
         <v/>
       </c>
       <c r="I513" t="inlineStr"/>
-      <c r="J513" t="inlineStr"/>
     </row>
     <row r="514">
       <c r="A514" s="5" t="n">
@@ -31049,7 +30360,6 @@
         <v/>
       </c>
       <c r="I514" t="inlineStr"/>
-      <c r="J514" t="inlineStr"/>
     </row>
     <row r="515">
       <c r="A515" s="5" t="n">
@@ -31087,7 +30397,6 @@
         <v/>
       </c>
       <c r="I515" t="inlineStr"/>
-      <c r="J515" t="inlineStr"/>
     </row>
     <row r="516">
       <c r="A516" s="5" t="n">
@@ -31125,7 +30434,6 @@
         <v/>
       </c>
       <c r="I516" t="inlineStr"/>
-      <c r="J516" t="inlineStr"/>
     </row>
     <row r="517">
       <c r="A517" s="5" t="n">
@@ -31163,7 +30471,6 @@
         <v/>
       </c>
       <c r="I517" t="inlineStr"/>
-      <c r="J517" t="inlineStr"/>
     </row>
     <row r="518">
       <c r="A518" s="5" t="n">
@@ -31201,7 +30508,6 @@
         <v/>
       </c>
       <c r="I518" t="inlineStr"/>
-      <c r="J518" t="inlineStr"/>
     </row>
     <row r="519">
       <c r="A519" s="5" t="n">
@@ -31239,7 +30545,6 @@
         <v/>
       </c>
       <c r="I519" t="inlineStr"/>
-      <c r="J519" t="inlineStr"/>
     </row>
     <row r="520">
       <c r="A520" s="5" t="n">
@@ -31277,7 +30582,6 @@
         <v/>
       </c>
       <c r="I520" t="inlineStr"/>
-      <c r="J520" t="inlineStr"/>
     </row>
     <row r="521">
       <c r="A521" s="5" t="n">
@@ -31315,7 +30619,6 @@
         <v/>
       </c>
       <c r="I521" t="inlineStr"/>
-      <c r="J521" t="inlineStr"/>
     </row>
     <row r="522">
       <c r="A522" s="5" t="n">
@@ -31353,7 +30656,6 @@
         <v/>
       </c>
       <c r="I522" t="inlineStr"/>
-      <c r="J522" t="inlineStr"/>
     </row>
     <row r="523">
       <c r="A523" s="5" t="n">
@@ -31391,7 +30693,6 @@
         <v/>
       </c>
       <c r="I523" t="inlineStr"/>
-      <c r="J523" t="inlineStr"/>
     </row>
     <row r="524">
       <c r="A524" s="5" t="n">
@@ -31429,7 +30730,6 @@
         <v/>
       </c>
       <c r="I524" t="inlineStr"/>
-      <c r="J524" t="inlineStr"/>
     </row>
     <row r="525">
       <c r="A525" s="5" t="n">
@@ -31467,7 +30767,6 @@
         <v/>
       </c>
       <c r="I525" t="inlineStr"/>
-      <c r="J525" t="inlineStr"/>
     </row>
     <row r="526">
       <c r="A526" s="5" t="n">
@@ -31505,7 +30804,6 @@
         <v/>
       </c>
       <c r="I526" t="inlineStr"/>
-      <c r="J526" t="inlineStr"/>
     </row>
     <row r="527">
       <c r="A527" s="5" t="n">
@@ -31543,7 +30841,6 @@
         <v/>
       </c>
       <c r="I527" t="inlineStr"/>
-      <c r="J527" t="inlineStr"/>
     </row>
     <row r="528">
       <c r="A528" s="5" t="n">
@@ -31581,7 +30878,6 @@
         <v/>
       </c>
       <c r="I528" t="inlineStr"/>
-      <c r="J528" t="inlineStr"/>
     </row>
     <row r="529">
       <c r="A529" s="5" t="n">
@@ -31619,7 +30915,6 @@
         <v/>
       </c>
       <c r="I529" t="inlineStr"/>
-      <c r="J529" t="inlineStr"/>
     </row>
     <row r="530">
       <c r="A530" s="5" t="n">
@@ -31657,7 +30952,6 @@
         <v/>
       </c>
       <c r="I530" t="inlineStr"/>
-      <c r="J530" t="inlineStr"/>
     </row>
     <row r="531">
       <c r="A531" s="5" t="n">
@@ -31695,7 +30989,6 @@
         <v/>
       </c>
       <c r="I531" t="inlineStr"/>
-      <c r="J531" t="inlineStr"/>
     </row>
     <row r="532">
       <c r="A532" s="5" t="n">
@@ -31733,7 +31026,6 @@
         <v/>
       </c>
       <c r="I532" t="inlineStr"/>
-      <c r="J532" t="inlineStr"/>
     </row>
     <row r="533">
       <c r="A533" s="5" t="n">
@@ -31771,7 +31063,6 @@
         <v/>
       </c>
       <c r="I533" t="inlineStr"/>
-      <c r="J533" t="inlineStr"/>
     </row>
     <row r="534">
       <c r="A534" s="5" t="n">
@@ -31809,7 +31100,6 @@
         <v/>
       </c>
       <c r="I534" t="inlineStr"/>
-      <c r="J534" t="inlineStr"/>
     </row>
     <row r="535">
       <c r="A535" s="5" t="n">
@@ -31847,7 +31137,6 @@
         <v/>
       </c>
       <c r="I535" t="inlineStr"/>
-      <c r="J535" t="inlineStr"/>
     </row>
     <row r="536">
       <c r="A536" s="5" t="n">
@@ -31885,7 +31174,6 @@
         <v/>
       </c>
       <c r="I536" t="inlineStr"/>
-      <c r="J536" t="inlineStr"/>
     </row>
     <row r="537">
       <c r="A537" s="5" t="n">
@@ -31923,7 +31211,6 @@
         <v/>
       </c>
       <c r="I537" t="inlineStr"/>
-      <c r="J537" t="inlineStr"/>
     </row>
     <row r="538">
       <c r="A538" s="5" t="n">
@@ -31961,7 +31248,6 @@
         <v/>
       </c>
       <c r="I538" t="inlineStr"/>
-      <c r="J538" t="inlineStr"/>
     </row>
     <row r="539">
       <c r="A539" s="5" t="n">
@@ -31999,11 +31285,6 @@
         <v/>
       </c>
       <c r="I539" t="inlineStr"/>
-      <c r="J539" t="inlineStr">
-        <is>
-          <t>Bryan</t>
-        </is>
-      </c>
     </row>
     <row r="540">
       <c r="A540" s="5" t="n">
@@ -32041,7 +31322,6 @@
         <v/>
       </c>
       <c r="I540" t="inlineStr"/>
-      <c r="J540" t="inlineStr"/>
     </row>
     <row r="541">
       <c r="A541" s="5" t="n">
@@ -32079,7 +31359,6 @@
         <v/>
       </c>
       <c r="I541" t="inlineStr"/>
-      <c r="J541" t="inlineStr"/>
     </row>
     <row r="542">
       <c r="A542" s="5" t="n">
@@ -32117,7 +31396,6 @@
         <v/>
       </c>
       <c r="I542" t="inlineStr"/>
-      <c r="J542" t="inlineStr"/>
     </row>
     <row r="543">
       <c r="A543" s="5" t="n">
@@ -32155,7 +31433,6 @@
         <v/>
       </c>
       <c r="I543" t="inlineStr"/>
-      <c r="J543" t="inlineStr"/>
     </row>
     <row r="544">
       <c r="A544" s="5" t="n">
@@ -32193,7 +31470,6 @@
         <v/>
       </c>
       <c r="I544" t="inlineStr"/>
-      <c r="J544" t="inlineStr"/>
     </row>
     <row r="545">
       <c r="A545" s="5" t="n">
@@ -32231,7 +31507,6 @@
         <v/>
       </c>
       <c r="I545" t="inlineStr"/>
-      <c r="J545" t="inlineStr"/>
     </row>
     <row r="546">
       <c r="A546" s="5" t="n">
@@ -32269,7 +31544,6 @@
         <v/>
       </c>
       <c r="I546" t="inlineStr"/>
-      <c r="J546" t="inlineStr"/>
     </row>
     <row r="547">
       <c r="A547" s="5" t="n">
@@ -32307,7 +31581,6 @@
         <v/>
       </c>
       <c r="I547" t="inlineStr"/>
-      <c r="J547" t="inlineStr"/>
     </row>
     <row r="548">
       <c r="A548" s="5" t="n">
@@ -32345,7 +31618,6 @@
         <v/>
       </c>
       <c r="I548" t="inlineStr"/>
-      <c r="J548" t="inlineStr"/>
     </row>
     <row r="549">
       <c r="A549" s="5" t="n">
@@ -32383,7 +31655,6 @@
         <v/>
       </c>
       <c r="I549" t="inlineStr"/>
-      <c r="J549" t="inlineStr"/>
     </row>
     <row r="550">
       <c r="A550" s="5" t="n">
@@ -32421,7 +31692,6 @@
         <v/>
       </c>
       <c r="I550" t="inlineStr"/>
-      <c r="J550" t="inlineStr"/>
     </row>
     <row r="551">
       <c r="A551" s="5" t="n">
@@ -32459,7 +31729,6 @@
         <v/>
       </c>
       <c r="I551" t="inlineStr"/>
-      <c r="J551" t="inlineStr"/>
     </row>
     <row r="552">
       <c r="A552" s="5" t="n">
@@ -32497,7 +31766,6 @@
         <v/>
       </c>
       <c r="I552" t="inlineStr"/>
-      <c r="J552" t="inlineStr"/>
     </row>
     <row r="553">
       <c r="A553" s="5" t="n">
@@ -32535,7 +31803,6 @@
         <v/>
       </c>
       <c r="I553" t="inlineStr"/>
-      <c r="J553" t="inlineStr"/>
     </row>
     <row r="554">
       <c r="A554" s="5" t="n">
@@ -32573,7 +31840,6 @@
         <v/>
       </c>
       <c r="I554" t="inlineStr"/>
-      <c r="J554" t="inlineStr"/>
     </row>
     <row r="555">
       <c r="A555" s="5" t="n">
@@ -32611,7 +31877,6 @@
         <v/>
       </c>
       <c r="I555" t="inlineStr"/>
-      <c r="J555" t="inlineStr"/>
     </row>
     <row r="556">
       <c r="A556" s="5" t="n">
@@ -32649,7 +31914,6 @@
         <v/>
       </c>
       <c r="I556" t="inlineStr"/>
-      <c r="J556" t="inlineStr"/>
     </row>
     <row r="557">
       <c r="A557" s="5" t="n">
@@ -32687,7 +31951,6 @@
         <v/>
       </c>
       <c r="I557" t="inlineStr"/>
-      <c r="J557" t="inlineStr"/>
     </row>
     <row r="558">
       <c r="A558" s="5" t="n">
@@ -32725,7 +31988,6 @@
         <v/>
       </c>
       <c r="I558" t="inlineStr"/>
-      <c r="J558" t="inlineStr"/>
     </row>
     <row r="559">
       <c r="A559" s="5" t="n">
@@ -32763,11 +32025,6 @@
         <v/>
       </c>
       <c r="I559" t="inlineStr"/>
-      <c r="J559" t="inlineStr">
-        <is>
-          <t>Casey</t>
-        </is>
-      </c>
     </row>
     <row r="560">
       <c r="A560" s="5" t="n">
@@ -32805,7 +32062,6 @@
         <v/>
       </c>
       <c r="I560" t="inlineStr"/>
-      <c r="J560" t="inlineStr"/>
     </row>
     <row r="561">
       <c r="A561" s="5" t="n">
@@ -32843,7 +32099,6 @@
         <v/>
       </c>
       <c r="I561" t="inlineStr"/>
-      <c r="J561" t="inlineStr"/>
     </row>
     <row r="562">
       <c r="A562" s="5" t="n">
@@ -32881,7 +32136,6 @@
         <v/>
       </c>
       <c r="I562" t="inlineStr"/>
-      <c r="J562" t="inlineStr"/>
     </row>
     <row r="563">
       <c r="A563" s="5" t="n">
@@ -32919,7 +32173,6 @@
         <v/>
       </c>
       <c r="I563" t="inlineStr"/>
-      <c r="J563" t="inlineStr"/>
     </row>
     <row r="564">
       <c r="A564" s="5" t="n">
@@ -32957,11 +32210,6 @@
         <v/>
       </c>
       <c r="I564" t="inlineStr"/>
-      <c r="J564" t="inlineStr">
-        <is>
-          <t>Bryan</t>
-        </is>
-      </c>
     </row>
     <row r="565">
       <c r="A565" s="5" t="n">
@@ -32999,11 +32247,6 @@
         <v/>
       </c>
       <c r="I565" t="inlineStr"/>
-      <c r="J565" t="inlineStr">
-        <is>
-          <t>Casey</t>
-        </is>
-      </c>
     </row>
     <row r="566">
       <c r="A566" s="5" t="n">
@@ -33041,7 +32284,6 @@
         <v/>
       </c>
       <c r="I566" t="inlineStr"/>
-      <c r="J566" t="inlineStr"/>
     </row>
     <row r="567">
       <c r="A567" s="5" t="n">
@@ -33079,7 +32321,6 @@
         <v/>
       </c>
       <c r="I567" t="inlineStr"/>
-      <c r="J567" t="inlineStr"/>
     </row>
     <row r="568">
       <c r="A568" s="5" t="n">
@@ -33117,7 +32358,6 @@
         <v/>
       </c>
       <c r="I568" t="inlineStr"/>
-      <c r="J568" t="inlineStr"/>
     </row>
     <row r="569">
       <c r="A569" s="5" t="n">
@@ -33155,7 +32395,6 @@
         <v/>
       </c>
       <c r="I569" t="inlineStr"/>
-      <c r="J569" t="inlineStr"/>
     </row>
     <row r="570">
       <c r="A570" s="5" t="n">
@@ -33193,7 +32432,6 @@
         <v/>
       </c>
       <c r="I570" t="inlineStr"/>
-      <c r="J570" t="inlineStr"/>
     </row>
     <row r="571">
       <c r="A571" s="5" t="n">
@@ -33231,7 +32469,6 @@
         <v/>
       </c>
       <c r="I571" t="inlineStr"/>
-      <c r="J571" t="inlineStr"/>
     </row>
     <row r="572">
       <c r="A572" s="5" t="n">
@@ -33269,7 +32506,6 @@
         <v/>
       </c>
       <c r="I572" t="inlineStr"/>
-      <c r="J572" t="inlineStr"/>
     </row>
     <row r="573">
       <c r="A573" s="5" t="n">
@@ -33307,7 +32543,6 @@
         <v/>
       </c>
       <c r="I573" t="inlineStr"/>
-      <c r="J573" t="inlineStr"/>
     </row>
     <row r="574">
       <c r="A574" s="5" t="n">
@@ -33345,7 +32580,6 @@
         <v/>
       </c>
       <c r="I574" t="inlineStr"/>
-      <c r="J574" t="inlineStr"/>
     </row>
     <row r="575">
       <c r="A575" s="5" t="n">
@@ -33383,7 +32617,6 @@
         <v/>
       </c>
       <c r="I575" t="inlineStr"/>
-      <c r="J575" t="inlineStr"/>
     </row>
     <row r="576">
       <c r="A576" s="5" t="n">
@@ -33421,2893 +32654,2889 @@
         <v/>
       </c>
       <c r="I576" t="inlineStr"/>
-      <c r="J576" t="inlineStr"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:J2">
+  <conditionalFormatting sqref="A2:I2">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$H2="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A3:J3">
+  <conditionalFormatting sqref="A3:I3">
     <cfRule type="expression" priority="2" dxfId="0">
       <formula>$H3="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A4:J4">
+  <conditionalFormatting sqref="A4:I4">
     <cfRule type="expression" priority="3" dxfId="0">
       <formula>$H4="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A5:J5">
+  <conditionalFormatting sqref="A5:I5">
     <cfRule type="expression" priority="4" dxfId="0">
       <formula>$H5="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A6:J6">
+  <conditionalFormatting sqref="A6:I6">
     <cfRule type="expression" priority="5" dxfId="0">
       <formula>$H6="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A7:J7">
+  <conditionalFormatting sqref="A7:I7">
     <cfRule type="expression" priority="6" dxfId="0">
       <formula>$H7="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A8:J8">
+  <conditionalFormatting sqref="A8:I8">
     <cfRule type="expression" priority="7" dxfId="0">
       <formula>$H8="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A9:J9">
+  <conditionalFormatting sqref="A9:I9">
     <cfRule type="expression" priority="8" dxfId="0">
       <formula>$H9="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A10:J10">
+  <conditionalFormatting sqref="A10:I10">
     <cfRule type="expression" priority="9" dxfId="0">
       <formula>$H10="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A11:J11">
+  <conditionalFormatting sqref="A11:I11">
     <cfRule type="expression" priority="10" dxfId="0">
       <formula>$H11="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A12:J12">
+  <conditionalFormatting sqref="A12:I12">
     <cfRule type="expression" priority="11" dxfId="0">
       <formula>$H12="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A13:J13">
+  <conditionalFormatting sqref="A13:I13">
     <cfRule type="expression" priority="12" dxfId="0">
       <formula>$H13="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A14:J14">
+  <conditionalFormatting sqref="A14:I14">
     <cfRule type="expression" priority="13" dxfId="0">
       <formula>$H14="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A15:J15">
+  <conditionalFormatting sqref="A15:I15">
     <cfRule type="expression" priority="14" dxfId="0">
       <formula>$H15="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A16:J16">
+  <conditionalFormatting sqref="A16:I16">
     <cfRule type="expression" priority="15" dxfId="0">
       <formula>$H16="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A17:J17">
+  <conditionalFormatting sqref="A17:I17">
     <cfRule type="expression" priority="16" dxfId="0">
       <formula>$H17="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A18:J18">
+  <conditionalFormatting sqref="A18:I18">
     <cfRule type="expression" priority="17" dxfId="0">
       <formula>$H18="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A19:J19">
+  <conditionalFormatting sqref="A19:I19">
     <cfRule type="expression" priority="18" dxfId="0">
       <formula>$H19="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A20:J20">
+  <conditionalFormatting sqref="A20:I20">
     <cfRule type="expression" priority="19" dxfId="0">
       <formula>$H20="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A21:J21">
+  <conditionalFormatting sqref="A21:I21">
     <cfRule type="expression" priority="20" dxfId="0">
       <formula>$H21="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A22:J22">
+  <conditionalFormatting sqref="A22:I22">
     <cfRule type="expression" priority="21" dxfId="0">
       <formula>$H22="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A23:J23">
+  <conditionalFormatting sqref="A23:I23">
     <cfRule type="expression" priority="22" dxfId="0">
       <formula>$H23="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A24:J24">
+  <conditionalFormatting sqref="A24:I24">
     <cfRule type="expression" priority="23" dxfId="0">
       <formula>$H24="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A25:J25">
+  <conditionalFormatting sqref="A25:I25">
     <cfRule type="expression" priority="24" dxfId="0">
       <formula>$H25="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A26:J26">
+  <conditionalFormatting sqref="A26:I26">
     <cfRule type="expression" priority="25" dxfId="0">
       <formula>$H26="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A27:J27">
+  <conditionalFormatting sqref="A27:I27">
     <cfRule type="expression" priority="26" dxfId="0">
       <formula>$H27="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A28:J28">
+  <conditionalFormatting sqref="A28:I28">
     <cfRule type="expression" priority="27" dxfId="0">
       <formula>$H28="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A29:J29">
+  <conditionalFormatting sqref="A29:I29">
     <cfRule type="expression" priority="28" dxfId="0">
       <formula>$H29="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A30:J30">
+  <conditionalFormatting sqref="A30:I30">
     <cfRule type="expression" priority="29" dxfId="0">
       <formula>$H30="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A31:J31">
+  <conditionalFormatting sqref="A31:I31">
     <cfRule type="expression" priority="30" dxfId="0">
       <formula>$H31="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A32:J32">
+  <conditionalFormatting sqref="A32:I32">
     <cfRule type="expression" priority="31" dxfId="0">
       <formula>$H32="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A33:J33">
+  <conditionalFormatting sqref="A33:I33">
     <cfRule type="expression" priority="32" dxfId="0">
       <formula>$H33="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A34:J34">
+  <conditionalFormatting sqref="A34:I34">
     <cfRule type="expression" priority="33" dxfId="0">
       <formula>$H34="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A35:J35">
+  <conditionalFormatting sqref="A35:I35">
     <cfRule type="expression" priority="34" dxfId="0">
       <formula>$H35="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A36:J36">
+  <conditionalFormatting sqref="A36:I36">
     <cfRule type="expression" priority="35" dxfId="0">
       <formula>$H36="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A37:J37">
+  <conditionalFormatting sqref="A37:I37">
     <cfRule type="expression" priority="36" dxfId="0">
       <formula>$H37="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A38:J38">
+  <conditionalFormatting sqref="A38:I38">
     <cfRule type="expression" priority="37" dxfId="0">
       <formula>$H38="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A39:J39">
+  <conditionalFormatting sqref="A39:I39">
     <cfRule type="expression" priority="38" dxfId="0">
       <formula>$H39="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A40:J40">
+  <conditionalFormatting sqref="A40:I40">
     <cfRule type="expression" priority="39" dxfId="0">
       <formula>$H40="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A41:J41">
+  <conditionalFormatting sqref="A41:I41">
     <cfRule type="expression" priority="40" dxfId="0">
       <formula>$H41="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A42:J42">
+  <conditionalFormatting sqref="A42:I42">
     <cfRule type="expression" priority="41" dxfId="0">
       <formula>$H42="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A43:J43">
+  <conditionalFormatting sqref="A43:I43">
     <cfRule type="expression" priority="42" dxfId="0">
       <formula>$H43="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A44:J44">
+  <conditionalFormatting sqref="A44:I44">
     <cfRule type="expression" priority="43" dxfId="0">
       <formula>$H44="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A45:J45">
+  <conditionalFormatting sqref="A45:I45">
     <cfRule type="expression" priority="44" dxfId="0">
       <formula>$H45="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A46:J46">
+  <conditionalFormatting sqref="A46:I46">
     <cfRule type="expression" priority="45" dxfId="0">
       <formula>$H46="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A47:J47">
+  <conditionalFormatting sqref="A47:I47">
     <cfRule type="expression" priority="46" dxfId="0">
       <formula>$H47="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A48:J48">
+  <conditionalFormatting sqref="A48:I48">
     <cfRule type="expression" priority="47" dxfId="0">
       <formula>$H48="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A49:J49">
+  <conditionalFormatting sqref="A49:I49">
     <cfRule type="expression" priority="48" dxfId="0">
       <formula>$H49="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A50:J50">
+  <conditionalFormatting sqref="A50:I50">
     <cfRule type="expression" priority="49" dxfId="0">
       <formula>$H50="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A51:J51">
+  <conditionalFormatting sqref="A51:I51">
     <cfRule type="expression" priority="50" dxfId="0">
       <formula>$H51="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A52:J52">
+  <conditionalFormatting sqref="A52:I52">
     <cfRule type="expression" priority="51" dxfId="0">
       <formula>$H52="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A53:J53">
+  <conditionalFormatting sqref="A53:I53">
     <cfRule type="expression" priority="52" dxfId="0">
       <formula>$H53="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A54:J54">
+  <conditionalFormatting sqref="A54:I54">
     <cfRule type="expression" priority="53" dxfId="0">
       <formula>$H54="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A55:J55">
+  <conditionalFormatting sqref="A55:I55">
     <cfRule type="expression" priority="54" dxfId="0">
       <formula>$H55="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A56:J56">
+  <conditionalFormatting sqref="A56:I56">
     <cfRule type="expression" priority="55" dxfId="0">
       <formula>$H56="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A57:J57">
+  <conditionalFormatting sqref="A57:I57">
     <cfRule type="expression" priority="56" dxfId="0">
       <formula>$H57="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A58:J58">
+  <conditionalFormatting sqref="A58:I58">
     <cfRule type="expression" priority="57" dxfId="0">
       <formula>$H58="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A59:J59">
+  <conditionalFormatting sqref="A59:I59">
     <cfRule type="expression" priority="58" dxfId="0">
       <formula>$H59="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A60:J60">
+  <conditionalFormatting sqref="A60:I60">
     <cfRule type="expression" priority="59" dxfId="0">
       <formula>$H60="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A61:J61">
+  <conditionalFormatting sqref="A61:I61">
     <cfRule type="expression" priority="60" dxfId="0">
       <formula>$H61="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A62:J62">
+  <conditionalFormatting sqref="A62:I62">
     <cfRule type="expression" priority="61" dxfId="0">
       <formula>$H62="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A63:J63">
+  <conditionalFormatting sqref="A63:I63">
     <cfRule type="expression" priority="62" dxfId="0">
       <formula>$H63="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A64:J64">
+  <conditionalFormatting sqref="A64:I64">
     <cfRule type="expression" priority="63" dxfId="0">
       <formula>$H64="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A65:J65">
+  <conditionalFormatting sqref="A65:I65">
     <cfRule type="expression" priority="64" dxfId="0">
       <formula>$H65="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A66:J66">
+  <conditionalFormatting sqref="A66:I66">
     <cfRule type="expression" priority="65" dxfId="0">
       <formula>$H66="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A67:J67">
+  <conditionalFormatting sqref="A67:I67">
     <cfRule type="expression" priority="66" dxfId="0">
       <formula>$H67="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A68:J68">
+  <conditionalFormatting sqref="A68:I68">
     <cfRule type="expression" priority="67" dxfId="0">
       <formula>$H68="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A69:J69">
+  <conditionalFormatting sqref="A69:I69">
     <cfRule type="expression" priority="68" dxfId="0">
       <formula>$H69="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A70:J70">
+  <conditionalFormatting sqref="A70:I70">
     <cfRule type="expression" priority="69" dxfId="0">
       <formula>$H70="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A71:J71">
+  <conditionalFormatting sqref="A71:I71">
     <cfRule type="expression" priority="70" dxfId="0">
       <formula>$H71="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A72:J72">
+  <conditionalFormatting sqref="A72:I72">
     <cfRule type="expression" priority="71" dxfId="0">
       <formula>$H72="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A73:J73">
+  <conditionalFormatting sqref="A73:I73">
     <cfRule type="expression" priority="72" dxfId="0">
       <formula>$H73="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A74:J74">
+  <conditionalFormatting sqref="A74:I74">
     <cfRule type="expression" priority="73" dxfId="0">
       <formula>$H74="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A75:J75">
+  <conditionalFormatting sqref="A75:I75">
     <cfRule type="expression" priority="74" dxfId="0">
       <formula>$H75="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A76:J76">
+  <conditionalFormatting sqref="A76:I76">
     <cfRule type="expression" priority="75" dxfId="0">
       <formula>$H76="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A77:J77">
+  <conditionalFormatting sqref="A77:I77">
     <cfRule type="expression" priority="76" dxfId="0">
       <formula>$H77="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A78:J78">
+  <conditionalFormatting sqref="A78:I78">
     <cfRule type="expression" priority="77" dxfId="0">
       <formula>$H78="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A79:J79">
+  <conditionalFormatting sqref="A79:I79">
     <cfRule type="expression" priority="78" dxfId="0">
       <formula>$H79="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A80:J80">
+  <conditionalFormatting sqref="A80:I80">
     <cfRule type="expression" priority="79" dxfId="0">
       <formula>$H80="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A81:J81">
+  <conditionalFormatting sqref="A81:I81">
     <cfRule type="expression" priority="80" dxfId="0">
       <formula>$H81="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A82:J82">
+  <conditionalFormatting sqref="A82:I82">
     <cfRule type="expression" priority="81" dxfId="0">
       <formula>$H82="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A83:J83">
+  <conditionalFormatting sqref="A83:I83">
     <cfRule type="expression" priority="82" dxfId="0">
       <formula>$H83="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A84:J84">
+  <conditionalFormatting sqref="A84:I84">
     <cfRule type="expression" priority="83" dxfId="0">
       <formula>$H84="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A85:J85">
+  <conditionalFormatting sqref="A85:I85">
     <cfRule type="expression" priority="84" dxfId="0">
       <formula>$H85="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A86:J86">
+  <conditionalFormatting sqref="A86:I86">
     <cfRule type="expression" priority="85" dxfId="0">
       <formula>$H86="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A87:J87">
+  <conditionalFormatting sqref="A87:I87">
     <cfRule type="expression" priority="86" dxfId="0">
       <formula>$H87="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A88:J88">
+  <conditionalFormatting sqref="A88:I88">
     <cfRule type="expression" priority="87" dxfId="0">
       <formula>$H88="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A89:J89">
+  <conditionalFormatting sqref="A89:I89">
     <cfRule type="expression" priority="88" dxfId="0">
       <formula>$H89="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A90:J90">
+  <conditionalFormatting sqref="A90:I90">
     <cfRule type="expression" priority="89" dxfId="0">
       <formula>$H90="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A91:J91">
+  <conditionalFormatting sqref="A91:I91">
     <cfRule type="expression" priority="90" dxfId="0">
       <formula>$H91="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A92:J92">
+  <conditionalFormatting sqref="A92:I92">
     <cfRule type="expression" priority="91" dxfId="0">
       <formula>$H92="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A93:J93">
+  <conditionalFormatting sqref="A93:I93">
     <cfRule type="expression" priority="92" dxfId="0">
       <formula>$H93="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A94:J94">
+  <conditionalFormatting sqref="A94:I94">
     <cfRule type="expression" priority="93" dxfId="0">
       <formula>$H94="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A95:J95">
+  <conditionalFormatting sqref="A95:I95">
     <cfRule type="expression" priority="94" dxfId="0">
       <formula>$H95="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A96:J96">
+  <conditionalFormatting sqref="A96:I96">
     <cfRule type="expression" priority="95" dxfId="0">
       <formula>$H96="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A97:J97">
+  <conditionalFormatting sqref="A97:I97">
     <cfRule type="expression" priority="96" dxfId="0">
       <formula>$H97="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A98:J98">
+  <conditionalFormatting sqref="A98:I98">
     <cfRule type="expression" priority="97" dxfId="0">
       <formula>$H98="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A99:J99">
+  <conditionalFormatting sqref="A99:I99">
     <cfRule type="expression" priority="98" dxfId="0">
       <formula>$H99="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A100:J100">
+  <conditionalFormatting sqref="A100:I100">
     <cfRule type="expression" priority="99" dxfId="0">
       <formula>$H100="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A101:J101">
+  <conditionalFormatting sqref="A101:I101">
     <cfRule type="expression" priority="100" dxfId="0">
       <formula>$H101="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A102:J102">
+  <conditionalFormatting sqref="A102:I102">
     <cfRule type="expression" priority="101" dxfId="0">
       <formula>$H102="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A103:J103">
+  <conditionalFormatting sqref="A103:I103">
     <cfRule type="expression" priority="102" dxfId="0">
       <formula>$H103="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A104:J104">
+  <conditionalFormatting sqref="A104:I104">
     <cfRule type="expression" priority="103" dxfId="0">
       <formula>$H104="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A105:J105">
+  <conditionalFormatting sqref="A105:I105">
     <cfRule type="expression" priority="104" dxfId="0">
       <formula>$H105="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A106:J106">
+  <conditionalFormatting sqref="A106:I106">
     <cfRule type="expression" priority="105" dxfId="0">
       <formula>$H106="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A107:J107">
+  <conditionalFormatting sqref="A107:I107">
     <cfRule type="expression" priority="106" dxfId="0">
       <formula>$H107="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A108:J108">
+  <conditionalFormatting sqref="A108:I108">
     <cfRule type="expression" priority="107" dxfId="0">
       <formula>$H108="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A109:J109">
+  <conditionalFormatting sqref="A109:I109">
     <cfRule type="expression" priority="108" dxfId="0">
       <formula>$H109="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A110:J110">
+  <conditionalFormatting sqref="A110:I110">
     <cfRule type="expression" priority="109" dxfId="0">
       <formula>$H110="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A111:J111">
+  <conditionalFormatting sqref="A111:I111">
     <cfRule type="expression" priority="110" dxfId="0">
       <formula>$H111="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A112:J112">
+  <conditionalFormatting sqref="A112:I112">
     <cfRule type="expression" priority="111" dxfId="0">
       <formula>$H112="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A113:J113">
+  <conditionalFormatting sqref="A113:I113">
     <cfRule type="expression" priority="112" dxfId="0">
       <formula>$H113="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A114:J114">
+  <conditionalFormatting sqref="A114:I114">
     <cfRule type="expression" priority="113" dxfId="0">
       <formula>$H114="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A115:J115">
+  <conditionalFormatting sqref="A115:I115">
     <cfRule type="expression" priority="114" dxfId="0">
       <formula>$H115="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A116:J116">
+  <conditionalFormatting sqref="A116:I116">
     <cfRule type="expression" priority="115" dxfId="0">
       <formula>$H116="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A117:J117">
+  <conditionalFormatting sqref="A117:I117">
     <cfRule type="expression" priority="116" dxfId="0">
       <formula>$H117="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A118:J118">
+  <conditionalFormatting sqref="A118:I118">
     <cfRule type="expression" priority="117" dxfId="0">
       <formula>$H118="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A119:J119">
+  <conditionalFormatting sqref="A119:I119">
     <cfRule type="expression" priority="118" dxfId="0">
       <formula>$H119="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A120:J120">
+  <conditionalFormatting sqref="A120:I120">
     <cfRule type="expression" priority="119" dxfId="0">
       <formula>$H120="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A121:J121">
+  <conditionalFormatting sqref="A121:I121">
     <cfRule type="expression" priority="120" dxfId="0">
       <formula>$H121="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A122:J122">
+  <conditionalFormatting sqref="A122:I122">
     <cfRule type="expression" priority="121" dxfId="0">
       <formula>$H122="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A123:J123">
+  <conditionalFormatting sqref="A123:I123">
     <cfRule type="expression" priority="122" dxfId="0">
       <formula>$H123="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A124:J124">
+  <conditionalFormatting sqref="A124:I124">
     <cfRule type="expression" priority="123" dxfId="0">
       <formula>$H124="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A125:J125">
+  <conditionalFormatting sqref="A125:I125">
     <cfRule type="expression" priority="124" dxfId="0">
       <formula>$H125="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A126:J126">
+  <conditionalFormatting sqref="A126:I126">
     <cfRule type="expression" priority="125" dxfId="0">
       <formula>$H126="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A127:J127">
+  <conditionalFormatting sqref="A127:I127">
     <cfRule type="expression" priority="126" dxfId="0">
       <formula>$H127="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A128:J128">
+  <conditionalFormatting sqref="A128:I128">
     <cfRule type="expression" priority="127" dxfId="0">
       <formula>$H128="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A129:J129">
+  <conditionalFormatting sqref="A129:I129">
     <cfRule type="expression" priority="128" dxfId="0">
       <formula>$H129="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A130:J130">
+  <conditionalFormatting sqref="A130:I130">
     <cfRule type="expression" priority="129" dxfId="0">
       <formula>$H130="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A131:J131">
+  <conditionalFormatting sqref="A131:I131">
     <cfRule type="expression" priority="130" dxfId="0">
       <formula>$H131="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A132:J132">
+  <conditionalFormatting sqref="A132:I132">
     <cfRule type="expression" priority="131" dxfId="0">
       <formula>$H132="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A133:J133">
+  <conditionalFormatting sqref="A133:I133">
     <cfRule type="expression" priority="132" dxfId="0">
       <formula>$H133="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A134:J134">
+  <conditionalFormatting sqref="A134:I134">
     <cfRule type="expression" priority="133" dxfId="0">
       <formula>$H134="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A135:J135">
+  <conditionalFormatting sqref="A135:I135">
     <cfRule type="expression" priority="134" dxfId="0">
       <formula>$H135="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A136:J136">
+  <conditionalFormatting sqref="A136:I136">
     <cfRule type="expression" priority="135" dxfId="0">
       <formula>$H136="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A137:J137">
+  <conditionalFormatting sqref="A137:I137">
     <cfRule type="expression" priority="136" dxfId="0">
       <formula>$H137="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A138:J138">
+  <conditionalFormatting sqref="A138:I138">
     <cfRule type="expression" priority="137" dxfId="0">
       <formula>$H138="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A139:J139">
+  <conditionalFormatting sqref="A139:I139">
     <cfRule type="expression" priority="138" dxfId="0">
       <formula>$H139="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A140:J140">
+  <conditionalFormatting sqref="A140:I140">
     <cfRule type="expression" priority="139" dxfId="0">
       <formula>$H140="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A141:J141">
+  <conditionalFormatting sqref="A141:I141">
     <cfRule type="expression" priority="140" dxfId="0">
       <formula>$H141="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A142:J142">
+  <conditionalFormatting sqref="A142:I142">
     <cfRule type="expression" priority="141" dxfId="0">
       <formula>$H142="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A143:J143">
+  <conditionalFormatting sqref="A143:I143">
     <cfRule type="expression" priority="142" dxfId="0">
       <formula>$H143="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A144:J144">
+  <conditionalFormatting sqref="A144:I144">
     <cfRule type="expression" priority="143" dxfId="0">
       <formula>$H144="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A145:J145">
+  <conditionalFormatting sqref="A145:I145">
     <cfRule type="expression" priority="144" dxfId="0">
       <formula>$H145="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A146:J146">
+  <conditionalFormatting sqref="A146:I146">
     <cfRule type="expression" priority="145" dxfId="0">
       <formula>$H146="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A147:J147">
+  <conditionalFormatting sqref="A147:I147">
     <cfRule type="expression" priority="146" dxfId="0">
       <formula>$H147="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A148:J148">
+  <conditionalFormatting sqref="A148:I148">
     <cfRule type="expression" priority="147" dxfId="0">
       <formula>$H148="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A149:J149">
+  <conditionalFormatting sqref="A149:I149">
     <cfRule type="expression" priority="148" dxfId="0">
       <formula>$H149="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A150:J150">
+  <conditionalFormatting sqref="A150:I150">
     <cfRule type="expression" priority="149" dxfId="0">
       <formula>$H150="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A151:J151">
+  <conditionalFormatting sqref="A151:I151">
     <cfRule type="expression" priority="150" dxfId="0">
       <formula>$H151="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A152:J152">
+  <conditionalFormatting sqref="A152:I152">
     <cfRule type="expression" priority="151" dxfId="0">
       <formula>$H152="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A153:J153">
+  <conditionalFormatting sqref="A153:I153">
     <cfRule type="expression" priority="152" dxfId="0">
       <formula>$H153="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A154:J154">
+  <conditionalFormatting sqref="A154:I154">
     <cfRule type="expression" priority="153" dxfId="0">
       <formula>$H154="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A155:J155">
+  <conditionalFormatting sqref="A155:I155">
     <cfRule type="expression" priority="154" dxfId="0">
       <formula>$H155="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A156:J156">
+  <conditionalFormatting sqref="A156:I156">
     <cfRule type="expression" priority="155" dxfId="0">
       <formula>$H156="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A157:J157">
+  <conditionalFormatting sqref="A157:I157">
     <cfRule type="expression" priority="156" dxfId="0">
       <formula>$H157="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A158:J158">
+  <conditionalFormatting sqref="A158:I158">
     <cfRule type="expression" priority="157" dxfId="0">
       <formula>$H158="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A159:J159">
+  <conditionalFormatting sqref="A159:I159">
     <cfRule type="expression" priority="158" dxfId="0">
       <formula>$H159="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A160:J160">
+  <conditionalFormatting sqref="A160:I160">
     <cfRule type="expression" priority="159" dxfId="0">
       <formula>$H160="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A161:J161">
+  <conditionalFormatting sqref="A161:I161">
     <cfRule type="expression" priority="160" dxfId="0">
       <formula>$H161="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A162:J162">
+  <conditionalFormatting sqref="A162:I162">
     <cfRule type="expression" priority="161" dxfId="0">
       <formula>$H162="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A163:J163">
+  <conditionalFormatting sqref="A163:I163">
     <cfRule type="expression" priority="162" dxfId="0">
       <formula>$H163="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A164:J164">
+  <conditionalFormatting sqref="A164:I164">
     <cfRule type="expression" priority="163" dxfId="0">
       <formula>$H164="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A165:J165">
+  <conditionalFormatting sqref="A165:I165">
     <cfRule type="expression" priority="164" dxfId="0">
       <formula>$H165="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A166:J166">
+  <conditionalFormatting sqref="A166:I166">
     <cfRule type="expression" priority="165" dxfId="0">
       <formula>$H166="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A167:J167">
+  <conditionalFormatting sqref="A167:I167">
     <cfRule type="expression" priority="166" dxfId="0">
       <formula>$H167="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A168:J168">
+  <conditionalFormatting sqref="A168:I168">
     <cfRule type="expression" priority="167" dxfId="0">
       <formula>$H168="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A169:J169">
+  <conditionalFormatting sqref="A169:I169">
     <cfRule type="expression" priority="168" dxfId="0">
       <formula>$H169="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A170:J170">
+  <conditionalFormatting sqref="A170:I170">
     <cfRule type="expression" priority="169" dxfId="0">
       <formula>$H170="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A171:J171">
+  <conditionalFormatting sqref="A171:I171">
     <cfRule type="expression" priority="170" dxfId="0">
       <formula>$H171="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A172:J172">
+  <conditionalFormatting sqref="A172:I172">
     <cfRule type="expression" priority="171" dxfId="0">
       <formula>$H172="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A173:J173">
+  <conditionalFormatting sqref="A173:I173">
     <cfRule type="expression" priority="172" dxfId="0">
       <formula>$H173="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A174:J174">
+  <conditionalFormatting sqref="A174:I174">
     <cfRule type="expression" priority="173" dxfId="0">
       <formula>$H174="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A175:J175">
+  <conditionalFormatting sqref="A175:I175">
     <cfRule type="expression" priority="174" dxfId="0">
       <formula>$H175="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A176:J176">
+  <conditionalFormatting sqref="A176:I176">
     <cfRule type="expression" priority="175" dxfId="0">
       <formula>$H176="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A177:J177">
+  <conditionalFormatting sqref="A177:I177">
     <cfRule type="expression" priority="176" dxfId="0">
       <formula>$H177="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A178:J178">
+  <conditionalFormatting sqref="A178:I178">
     <cfRule type="expression" priority="177" dxfId="0">
       <formula>$H178="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A179:J179">
+  <conditionalFormatting sqref="A179:I179">
     <cfRule type="expression" priority="178" dxfId="0">
       <formula>$H179="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A180:J180">
+  <conditionalFormatting sqref="A180:I180">
     <cfRule type="expression" priority="179" dxfId="0">
       <formula>$H180="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A181:J181">
+  <conditionalFormatting sqref="A181:I181">
     <cfRule type="expression" priority="180" dxfId="0">
       <formula>$H181="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A182:J182">
+  <conditionalFormatting sqref="A182:I182">
     <cfRule type="expression" priority="181" dxfId="0">
       <formula>$H182="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A183:J183">
+  <conditionalFormatting sqref="A183:I183">
     <cfRule type="expression" priority="182" dxfId="0">
       <formula>$H183="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A184:J184">
+  <conditionalFormatting sqref="A184:I184">
     <cfRule type="expression" priority="183" dxfId="0">
       <formula>$H184="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A185:J185">
+  <conditionalFormatting sqref="A185:I185">
     <cfRule type="expression" priority="184" dxfId="0">
       <formula>$H185="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A186:J186">
+  <conditionalFormatting sqref="A186:I186">
     <cfRule type="expression" priority="185" dxfId="0">
       <formula>$H186="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A187:J187">
+  <conditionalFormatting sqref="A187:I187">
     <cfRule type="expression" priority="186" dxfId="0">
       <formula>$H187="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A188:J188">
+  <conditionalFormatting sqref="A188:I188">
     <cfRule type="expression" priority="187" dxfId="0">
       <formula>$H188="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A189:J189">
+  <conditionalFormatting sqref="A189:I189">
     <cfRule type="expression" priority="188" dxfId="0">
       <formula>$H189="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A190:J190">
+  <conditionalFormatting sqref="A190:I190">
     <cfRule type="expression" priority="189" dxfId="0">
       <formula>$H190="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A191:J191">
+  <conditionalFormatting sqref="A191:I191">
     <cfRule type="expression" priority="190" dxfId="0">
       <formula>$H191="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A192:J192">
+  <conditionalFormatting sqref="A192:I192">
     <cfRule type="expression" priority="191" dxfId="0">
       <formula>$H192="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A193:J193">
+  <conditionalFormatting sqref="A193:I193">
     <cfRule type="expression" priority="192" dxfId="0">
       <formula>$H193="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A194:J194">
+  <conditionalFormatting sqref="A194:I194">
     <cfRule type="expression" priority="193" dxfId="0">
       <formula>$H194="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A195:J195">
+  <conditionalFormatting sqref="A195:I195">
     <cfRule type="expression" priority="194" dxfId="0">
       <formula>$H195="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A196:J196">
+  <conditionalFormatting sqref="A196:I196">
     <cfRule type="expression" priority="195" dxfId="0">
       <formula>$H196="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A197:J197">
+  <conditionalFormatting sqref="A197:I197">
     <cfRule type="expression" priority="196" dxfId="0">
       <formula>$H197="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A198:J198">
+  <conditionalFormatting sqref="A198:I198">
     <cfRule type="expression" priority="197" dxfId="0">
       <formula>$H198="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A199:J199">
+  <conditionalFormatting sqref="A199:I199">
     <cfRule type="expression" priority="198" dxfId="0">
       <formula>$H199="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A200:J200">
+  <conditionalFormatting sqref="A200:I200">
     <cfRule type="expression" priority="199" dxfId="0">
       <formula>$H200="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A201:J201">
+  <conditionalFormatting sqref="A201:I201">
     <cfRule type="expression" priority="200" dxfId="0">
       <formula>$H201="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A202:J202">
+  <conditionalFormatting sqref="A202:I202">
     <cfRule type="expression" priority="201" dxfId="0">
       <formula>$H202="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A203:J203">
+  <conditionalFormatting sqref="A203:I203">
     <cfRule type="expression" priority="202" dxfId="0">
       <formula>$H203="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A204:J204">
+  <conditionalFormatting sqref="A204:I204">
     <cfRule type="expression" priority="203" dxfId="0">
       <formula>$H204="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A205:J205">
+  <conditionalFormatting sqref="A205:I205">
     <cfRule type="expression" priority="204" dxfId="0">
       <formula>$H205="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A206:J206">
+  <conditionalFormatting sqref="A206:I206">
     <cfRule type="expression" priority="205" dxfId="0">
       <formula>$H206="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A207:J207">
+  <conditionalFormatting sqref="A207:I207">
     <cfRule type="expression" priority="206" dxfId="0">
       <formula>$H207="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A208:J208">
+  <conditionalFormatting sqref="A208:I208">
     <cfRule type="expression" priority="207" dxfId="0">
       <formula>$H208="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A209:J209">
+  <conditionalFormatting sqref="A209:I209">
     <cfRule type="expression" priority="208" dxfId="0">
       <formula>$H209="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A210:J210">
+  <conditionalFormatting sqref="A210:I210">
     <cfRule type="expression" priority="209" dxfId="0">
       <formula>$H210="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A211:J211">
+  <conditionalFormatting sqref="A211:I211">
     <cfRule type="expression" priority="210" dxfId="0">
       <formula>$H211="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A212:J212">
+  <conditionalFormatting sqref="A212:I212">
     <cfRule type="expression" priority="211" dxfId="0">
       <formula>$H212="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A213:J213">
+  <conditionalFormatting sqref="A213:I213">
     <cfRule type="expression" priority="212" dxfId="0">
       <formula>$H213="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A214:J214">
+  <conditionalFormatting sqref="A214:I214">
     <cfRule type="expression" priority="213" dxfId="0">
       <formula>$H214="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A215:J215">
+  <conditionalFormatting sqref="A215:I215">
     <cfRule type="expression" priority="214" dxfId="0">
       <formula>$H215="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A216:J216">
+  <conditionalFormatting sqref="A216:I216">
     <cfRule type="expression" priority="215" dxfId="0">
       <formula>$H216="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A217:J217">
+  <conditionalFormatting sqref="A217:I217">
     <cfRule type="expression" priority="216" dxfId="0">
       <formula>$H217="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A218:J218">
+  <conditionalFormatting sqref="A218:I218">
     <cfRule type="expression" priority="217" dxfId="0">
       <formula>$H218="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A219:J219">
+  <conditionalFormatting sqref="A219:I219">
     <cfRule type="expression" priority="218" dxfId="0">
       <formula>$H219="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A220:J220">
+  <conditionalFormatting sqref="A220:I220">
     <cfRule type="expression" priority="219" dxfId="0">
       <formula>$H220="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A221:J221">
+  <conditionalFormatting sqref="A221:I221">
     <cfRule type="expression" priority="220" dxfId="0">
       <formula>$H221="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A222:J222">
+  <conditionalFormatting sqref="A222:I222">
     <cfRule type="expression" priority="221" dxfId="0">
       <formula>$H222="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A223:J223">
+  <conditionalFormatting sqref="A223:I223">
     <cfRule type="expression" priority="222" dxfId="0">
       <formula>$H223="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A224:J224">
+  <conditionalFormatting sqref="A224:I224">
     <cfRule type="expression" priority="223" dxfId="0">
       <formula>$H224="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A225:J225">
+  <conditionalFormatting sqref="A225:I225">
     <cfRule type="expression" priority="224" dxfId="0">
       <formula>$H225="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A226:J226">
+  <conditionalFormatting sqref="A226:I226">
     <cfRule type="expression" priority="225" dxfId="0">
       <formula>$H226="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A227:J227">
+  <conditionalFormatting sqref="A227:I227">
     <cfRule type="expression" priority="226" dxfId="0">
       <formula>$H227="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A228:J228">
+  <conditionalFormatting sqref="A228:I228">
     <cfRule type="expression" priority="227" dxfId="0">
       <formula>$H228="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A229:J229">
+  <conditionalFormatting sqref="A229:I229">
     <cfRule type="expression" priority="228" dxfId="0">
       <formula>$H229="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A230:J230">
+  <conditionalFormatting sqref="A230:I230">
     <cfRule type="expression" priority="229" dxfId="0">
       <formula>$H230="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A231:J231">
+  <conditionalFormatting sqref="A231:I231">
     <cfRule type="expression" priority="230" dxfId="0">
       <formula>$H231="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A232:J232">
+  <conditionalFormatting sqref="A232:I232">
     <cfRule type="expression" priority="231" dxfId="0">
       <formula>$H232="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A233:J233">
+  <conditionalFormatting sqref="A233:I233">
     <cfRule type="expression" priority="232" dxfId="0">
       <formula>$H233="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A234:J234">
+  <conditionalFormatting sqref="A234:I234">
     <cfRule type="expression" priority="233" dxfId="0">
       <formula>$H234="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A235:J235">
+  <conditionalFormatting sqref="A235:I235">
     <cfRule type="expression" priority="234" dxfId="0">
       <formula>$H235="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A236:J236">
+  <conditionalFormatting sqref="A236:I236">
     <cfRule type="expression" priority="235" dxfId="0">
       <formula>$H236="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A237:J237">
+  <conditionalFormatting sqref="A237:I237">
     <cfRule type="expression" priority="236" dxfId="0">
       <formula>$H237="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A238:J238">
+  <conditionalFormatting sqref="A238:I238">
     <cfRule type="expression" priority="237" dxfId="0">
       <formula>$H238="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A239:J239">
+  <conditionalFormatting sqref="A239:I239">
     <cfRule type="expression" priority="238" dxfId="0">
       <formula>$H239="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A240:J240">
+  <conditionalFormatting sqref="A240:I240">
     <cfRule type="expression" priority="239" dxfId="0">
       <formula>$H240="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A241:J241">
+  <conditionalFormatting sqref="A241:I241">
     <cfRule type="expression" priority="240" dxfId="0">
       <formula>$H241="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A242:J242">
+  <conditionalFormatting sqref="A242:I242">
     <cfRule type="expression" priority="241" dxfId="0">
       <formula>$H242="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A243:J243">
+  <conditionalFormatting sqref="A243:I243">
     <cfRule type="expression" priority="242" dxfId="0">
       <formula>$H243="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A244:J244">
+  <conditionalFormatting sqref="A244:I244">
     <cfRule type="expression" priority="243" dxfId="0">
       <formula>$H244="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A245:J245">
+  <conditionalFormatting sqref="A245:I245">
     <cfRule type="expression" priority="244" dxfId="0">
       <formula>$H245="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A246:J246">
+  <conditionalFormatting sqref="A246:I246">
     <cfRule type="expression" priority="245" dxfId="0">
       <formula>$H246="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A247:J247">
+  <conditionalFormatting sqref="A247:I247">
     <cfRule type="expression" priority="246" dxfId="0">
       <formula>$H247="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A248:J248">
+  <conditionalFormatting sqref="A248:I248">
     <cfRule type="expression" priority="247" dxfId="0">
       <formula>$H248="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A249:J249">
+  <conditionalFormatting sqref="A249:I249">
     <cfRule type="expression" priority="248" dxfId="0">
       <formula>$H249="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A250:J250">
+  <conditionalFormatting sqref="A250:I250">
     <cfRule type="expression" priority="249" dxfId="0">
       <formula>$H250="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A251:J251">
+  <conditionalFormatting sqref="A251:I251">
     <cfRule type="expression" priority="250" dxfId="0">
       <formula>$H251="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A252:J252">
+  <conditionalFormatting sqref="A252:I252">
     <cfRule type="expression" priority="251" dxfId="0">
       <formula>$H252="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A253:J253">
+  <conditionalFormatting sqref="A253:I253">
     <cfRule type="expression" priority="252" dxfId="0">
       <formula>$H253="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A254:J254">
+  <conditionalFormatting sqref="A254:I254">
     <cfRule type="expression" priority="253" dxfId="0">
       <formula>$H254="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A255:J255">
+  <conditionalFormatting sqref="A255:I255">
     <cfRule type="expression" priority="254" dxfId="0">
       <formula>$H255="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A256:J256">
+  <conditionalFormatting sqref="A256:I256">
     <cfRule type="expression" priority="255" dxfId="0">
       <formula>$H256="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A257:J257">
+  <conditionalFormatting sqref="A257:I257">
     <cfRule type="expression" priority="256" dxfId="0">
       <formula>$H257="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A258:J258">
+  <conditionalFormatting sqref="A258:I258">
     <cfRule type="expression" priority="257" dxfId="0">
       <formula>$H258="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A259:J259">
+  <conditionalFormatting sqref="A259:I259">
     <cfRule type="expression" priority="258" dxfId="0">
       <formula>$H259="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A260:J260">
+  <conditionalFormatting sqref="A260:I260">
     <cfRule type="expression" priority="259" dxfId="0">
       <formula>$H260="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A261:J261">
+  <conditionalFormatting sqref="A261:I261">
     <cfRule type="expression" priority="260" dxfId="0">
       <formula>$H261="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A262:J262">
+  <conditionalFormatting sqref="A262:I262">
     <cfRule type="expression" priority="261" dxfId="0">
       <formula>$H262="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A263:J263">
+  <conditionalFormatting sqref="A263:I263">
     <cfRule type="expression" priority="262" dxfId="0">
       <formula>$H263="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A264:J264">
+  <conditionalFormatting sqref="A264:I264">
     <cfRule type="expression" priority="263" dxfId="0">
       <formula>$H264="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A265:J265">
+  <conditionalFormatting sqref="A265:I265">
     <cfRule type="expression" priority="264" dxfId="0">
       <formula>$H265="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A266:J266">
+  <conditionalFormatting sqref="A266:I266">
     <cfRule type="expression" priority="265" dxfId="0">
       <formula>$H266="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A267:J267">
+  <conditionalFormatting sqref="A267:I267">
     <cfRule type="expression" priority="266" dxfId="0">
       <formula>$H267="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A268:J268">
+  <conditionalFormatting sqref="A268:I268">
     <cfRule type="expression" priority="267" dxfId="0">
       <formula>$H268="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A269:J269">
+  <conditionalFormatting sqref="A269:I269">
     <cfRule type="expression" priority="268" dxfId="0">
       <formula>$H269="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A270:J270">
+  <conditionalFormatting sqref="A270:I270">
     <cfRule type="expression" priority="269" dxfId="0">
       <formula>$H270="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A271:J271">
+  <conditionalFormatting sqref="A271:I271">
     <cfRule type="expression" priority="270" dxfId="0">
       <formula>$H271="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A272:J272">
+  <conditionalFormatting sqref="A272:I272">
     <cfRule type="expression" priority="271" dxfId="0">
       <formula>$H272="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A273:J273">
+  <conditionalFormatting sqref="A273:I273">
     <cfRule type="expression" priority="272" dxfId="0">
       <formula>$H273="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A274:J274">
+  <conditionalFormatting sqref="A274:I274">
     <cfRule type="expression" priority="273" dxfId="0">
       <formula>$H274="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A275:J275">
+  <conditionalFormatting sqref="A275:I275">
     <cfRule type="expression" priority="274" dxfId="0">
       <formula>$H275="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A276:J276">
+  <conditionalFormatting sqref="A276:I276">
     <cfRule type="expression" priority="275" dxfId="0">
       <formula>$H276="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A277:J277">
+  <conditionalFormatting sqref="A277:I277">
     <cfRule type="expression" priority="276" dxfId="0">
       <formula>$H277="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A278:J278">
+  <conditionalFormatting sqref="A278:I278">
     <cfRule type="expression" priority="277" dxfId="0">
       <formula>$H278="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A279:J279">
+  <conditionalFormatting sqref="A279:I279">
     <cfRule type="expression" priority="278" dxfId="0">
       <formula>$H279="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A280:J280">
+  <conditionalFormatting sqref="A280:I280">
     <cfRule type="expression" priority="279" dxfId="0">
       <formula>$H280="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A281:J281">
+  <conditionalFormatting sqref="A281:I281">
     <cfRule type="expression" priority="280" dxfId="0">
       <formula>$H281="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A282:J282">
+  <conditionalFormatting sqref="A282:I282">
     <cfRule type="expression" priority="281" dxfId="0">
       <formula>$H282="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A283:J283">
+  <conditionalFormatting sqref="A283:I283">
     <cfRule type="expression" priority="282" dxfId="0">
       <formula>$H283="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A284:J284">
+  <conditionalFormatting sqref="A284:I284">
     <cfRule type="expression" priority="283" dxfId="0">
       <formula>$H284="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A285:J285">
+  <conditionalFormatting sqref="A285:I285">
     <cfRule type="expression" priority="284" dxfId="0">
       <formula>$H285="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A286:J286">
+  <conditionalFormatting sqref="A286:I286">
     <cfRule type="expression" priority="285" dxfId="0">
       <formula>$H286="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A287:J287">
+  <conditionalFormatting sqref="A287:I287">
     <cfRule type="expression" priority="286" dxfId="0">
       <formula>$H287="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A288:J288">
+  <conditionalFormatting sqref="A288:I288">
     <cfRule type="expression" priority="287" dxfId="0">
       <formula>$H288="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A289:J289">
+  <conditionalFormatting sqref="A289:I289">
     <cfRule type="expression" priority="288" dxfId="0">
       <formula>$H289="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A290:J290">
+  <conditionalFormatting sqref="A290:I290">
     <cfRule type="expression" priority="289" dxfId="0">
       <formula>$H290="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A291:J291">
+  <conditionalFormatting sqref="A291:I291">
     <cfRule type="expression" priority="290" dxfId="0">
       <formula>$H291="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A292:J292">
+  <conditionalFormatting sqref="A292:I292">
     <cfRule type="expression" priority="291" dxfId="0">
       <formula>$H292="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A293:J293">
+  <conditionalFormatting sqref="A293:I293">
     <cfRule type="expression" priority="292" dxfId="0">
       <formula>$H293="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A294:J294">
+  <conditionalFormatting sqref="A294:I294">
     <cfRule type="expression" priority="293" dxfId="0">
       <formula>$H294="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A295:J295">
+  <conditionalFormatting sqref="A295:I295">
     <cfRule type="expression" priority="294" dxfId="0">
       <formula>$H295="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A296:J296">
+  <conditionalFormatting sqref="A296:I296">
     <cfRule type="expression" priority="295" dxfId="0">
       <formula>$H296="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A297:J297">
+  <conditionalFormatting sqref="A297:I297">
     <cfRule type="expression" priority="296" dxfId="0">
       <formula>$H297="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A298:J298">
+  <conditionalFormatting sqref="A298:I298">
     <cfRule type="expression" priority="297" dxfId="0">
       <formula>$H298="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A299:J299">
+  <conditionalFormatting sqref="A299:I299">
     <cfRule type="expression" priority="298" dxfId="0">
       <formula>$H299="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A300:J300">
+  <conditionalFormatting sqref="A300:I300">
     <cfRule type="expression" priority="299" dxfId="0">
       <formula>$H300="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A301:J301">
+  <conditionalFormatting sqref="A301:I301">
     <cfRule type="expression" priority="300" dxfId="0">
       <formula>$H301="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A302:J302">
+  <conditionalFormatting sqref="A302:I302">
     <cfRule type="expression" priority="301" dxfId="0">
       <formula>$H302="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A303:J303">
+  <conditionalFormatting sqref="A303:I303">
     <cfRule type="expression" priority="302" dxfId="0">
       <formula>$H303="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A304:J304">
+  <conditionalFormatting sqref="A304:I304">
     <cfRule type="expression" priority="303" dxfId="0">
       <formula>$H304="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A305:J305">
+  <conditionalFormatting sqref="A305:I305">
     <cfRule type="expression" priority="304" dxfId="0">
       <formula>$H305="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A306:J306">
+  <conditionalFormatting sqref="A306:I306">
     <cfRule type="expression" priority="305" dxfId="0">
       <formula>$H306="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A307:J307">
+  <conditionalFormatting sqref="A307:I307">
     <cfRule type="expression" priority="306" dxfId="0">
       <formula>$H307="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A308:J308">
+  <conditionalFormatting sqref="A308:I308">
     <cfRule type="expression" priority="307" dxfId="0">
       <formula>$H308="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A309:J309">
+  <conditionalFormatting sqref="A309:I309">
     <cfRule type="expression" priority="308" dxfId="0">
       <formula>$H309="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A310:J310">
+  <conditionalFormatting sqref="A310:I310">
     <cfRule type="expression" priority="309" dxfId="0">
       <formula>$H310="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A311:J311">
+  <conditionalFormatting sqref="A311:I311">
     <cfRule type="expression" priority="310" dxfId="0">
       <formula>$H311="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A312:J312">
+  <conditionalFormatting sqref="A312:I312">
     <cfRule type="expression" priority="311" dxfId="0">
       <formula>$H312="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A313:J313">
+  <conditionalFormatting sqref="A313:I313">
     <cfRule type="expression" priority="312" dxfId="0">
       <formula>$H313="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A314:J314">
+  <conditionalFormatting sqref="A314:I314">
     <cfRule type="expression" priority="313" dxfId="0">
       <formula>$H314="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A315:J315">
+  <conditionalFormatting sqref="A315:I315">
     <cfRule type="expression" priority="314" dxfId="0">
       <formula>$H315="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A316:J316">
+  <conditionalFormatting sqref="A316:I316">
     <cfRule type="expression" priority="315" dxfId="0">
       <formula>$H316="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A317:J317">
+  <conditionalFormatting sqref="A317:I317">
     <cfRule type="expression" priority="316" dxfId="0">
       <formula>$H317="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A318:J318">
+  <conditionalFormatting sqref="A318:I318">
     <cfRule type="expression" priority="317" dxfId="0">
       <formula>$H318="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A319:J319">
+  <conditionalFormatting sqref="A319:I319">
     <cfRule type="expression" priority="318" dxfId="0">
       <formula>$H319="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A320:J320">
+  <conditionalFormatting sqref="A320:I320">
     <cfRule type="expression" priority="319" dxfId="0">
       <formula>$H320="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A321:J321">
+  <conditionalFormatting sqref="A321:I321">
     <cfRule type="expression" priority="320" dxfId="0">
       <formula>$H321="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A322:J322">
+  <conditionalFormatting sqref="A322:I322">
     <cfRule type="expression" priority="321" dxfId="0">
       <formula>$H322="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A323:J323">
+  <conditionalFormatting sqref="A323:I323">
     <cfRule type="expression" priority="322" dxfId="0">
       <formula>$H323="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A324:J324">
+  <conditionalFormatting sqref="A324:I324">
     <cfRule type="expression" priority="323" dxfId="0">
       <formula>$H324="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A325:J325">
+  <conditionalFormatting sqref="A325:I325">
     <cfRule type="expression" priority="324" dxfId="0">
       <formula>$H325="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A326:J326">
+  <conditionalFormatting sqref="A326:I326">
     <cfRule type="expression" priority="325" dxfId="0">
       <formula>$H326="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A327:J327">
+  <conditionalFormatting sqref="A327:I327">
     <cfRule type="expression" priority="326" dxfId="0">
       <formula>$H327="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A328:J328">
+  <conditionalFormatting sqref="A328:I328">
     <cfRule type="expression" priority="327" dxfId="0">
       <formula>$H328="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A329:J329">
+  <conditionalFormatting sqref="A329:I329">
     <cfRule type="expression" priority="328" dxfId="0">
       <formula>$H329="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A330:J330">
+  <conditionalFormatting sqref="A330:I330">
     <cfRule type="expression" priority="329" dxfId="0">
       <formula>$H330="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A331:J331">
+  <conditionalFormatting sqref="A331:I331">
     <cfRule type="expression" priority="330" dxfId="0">
       <formula>$H331="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A332:J332">
+  <conditionalFormatting sqref="A332:I332">
     <cfRule type="expression" priority="331" dxfId="0">
       <formula>$H332="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A333:J333">
+  <conditionalFormatting sqref="A333:I333">
     <cfRule type="expression" priority="332" dxfId="0">
       <formula>$H333="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A334:J334">
+  <conditionalFormatting sqref="A334:I334">
     <cfRule type="expression" priority="333" dxfId="0">
       <formula>$H334="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A335:J335">
+  <conditionalFormatting sqref="A335:I335">
     <cfRule type="expression" priority="334" dxfId="0">
       <formula>$H335="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A336:J336">
+  <conditionalFormatting sqref="A336:I336">
     <cfRule type="expression" priority="335" dxfId="0">
       <formula>$H336="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A337:J337">
+  <conditionalFormatting sqref="A337:I337">
     <cfRule type="expression" priority="336" dxfId="0">
       <formula>$H337="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A338:J338">
+  <conditionalFormatting sqref="A338:I338">
     <cfRule type="expression" priority="337" dxfId="0">
       <formula>$H338="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A339:J339">
+  <conditionalFormatting sqref="A339:I339">
     <cfRule type="expression" priority="338" dxfId="0">
       <formula>$H339="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A340:J340">
+  <conditionalFormatting sqref="A340:I340">
     <cfRule type="expression" priority="339" dxfId="0">
       <formula>$H340="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A341:J341">
+  <conditionalFormatting sqref="A341:I341">
     <cfRule type="expression" priority="340" dxfId="0">
       <formula>$H341="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A342:J342">
+  <conditionalFormatting sqref="A342:I342">
     <cfRule type="expression" priority="341" dxfId="0">
       <formula>$H342="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A343:J343">
+  <conditionalFormatting sqref="A343:I343">
     <cfRule type="expression" priority="342" dxfId="0">
       <formula>$H343="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A344:J344">
+  <conditionalFormatting sqref="A344:I344">
     <cfRule type="expression" priority="343" dxfId="0">
       <formula>$H344="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A345:J345">
+  <conditionalFormatting sqref="A345:I345">
     <cfRule type="expression" priority="344" dxfId="0">
       <formula>$H345="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A346:J346">
+  <conditionalFormatting sqref="A346:I346">
     <cfRule type="expression" priority="345" dxfId="0">
       <formula>$H346="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A347:J347">
+  <conditionalFormatting sqref="A347:I347">
     <cfRule type="expression" priority="346" dxfId="0">
       <formula>$H347="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A348:J348">
+  <conditionalFormatting sqref="A348:I348">
     <cfRule type="expression" priority="347" dxfId="0">
       <formula>$H348="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A349:J349">
+  <conditionalFormatting sqref="A349:I349">
     <cfRule type="expression" priority="348" dxfId="0">
       <formula>$H349="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A350:J350">
+  <conditionalFormatting sqref="A350:I350">
     <cfRule type="expression" priority="349" dxfId="0">
       <formula>$H350="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A351:J351">
+  <conditionalFormatting sqref="A351:I351">
     <cfRule type="expression" priority="350" dxfId="0">
       <formula>$H351="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A352:J352">
+  <conditionalFormatting sqref="A352:I352">
     <cfRule type="expression" priority="351" dxfId="0">
       <formula>$H352="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A353:J353">
+  <conditionalFormatting sqref="A353:I353">
     <cfRule type="expression" priority="352" dxfId="0">
       <formula>$H353="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A354:J354">
+  <conditionalFormatting sqref="A354:I354">
     <cfRule type="expression" priority="353" dxfId="0">
       <formula>$H354="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A355:J355">
+  <conditionalFormatting sqref="A355:I355">
     <cfRule type="expression" priority="354" dxfId="0">
       <formula>$H355="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A356:J356">
+  <conditionalFormatting sqref="A356:I356">
     <cfRule type="expression" priority="355" dxfId="0">
       <formula>$H356="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A357:J357">
+  <conditionalFormatting sqref="A357:I357">
     <cfRule type="expression" priority="356" dxfId="0">
       <formula>$H357="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A358:J358">
+  <conditionalFormatting sqref="A358:I358">
     <cfRule type="expression" priority="357" dxfId="0">
       <formula>$H358="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A359:J359">
+  <conditionalFormatting sqref="A359:I359">
     <cfRule type="expression" priority="358" dxfId="0">
       <formula>$H359="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A360:J360">
+  <conditionalFormatting sqref="A360:I360">
     <cfRule type="expression" priority="359" dxfId="0">
       <formula>$H360="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A361:J361">
+  <conditionalFormatting sqref="A361:I361">
     <cfRule type="expression" priority="360" dxfId="0">
       <formula>$H361="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A362:J362">
+  <conditionalFormatting sqref="A362:I362">
     <cfRule type="expression" priority="361" dxfId="0">
       <formula>$H362="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A363:J363">
+  <conditionalFormatting sqref="A363:I363">
     <cfRule type="expression" priority="362" dxfId="0">
       <formula>$H363="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A364:J364">
+  <conditionalFormatting sqref="A364:I364">
     <cfRule type="expression" priority="363" dxfId="0">
       <formula>$H364="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A365:J365">
+  <conditionalFormatting sqref="A365:I365">
     <cfRule type="expression" priority="364" dxfId="0">
       <formula>$H365="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A366:J366">
+  <conditionalFormatting sqref="A366:I366">
     <cfRule type="expression" priority="365" dxfId="0">
       <formula>$H366="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A367:J367">
+  <conditionalFormatting sqref="A367:I367">
     <cfRule type="expression" priority="366" dxfId="0">
       <formula>$H367="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A368:J368">
+  <conditionalFormatting sqref="A368:I368">
     <cfRule type="expression" priority="367" dxfId="0">
       <formula>$H368="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A369:J369">
+  <conditionalFormatting sqref="A369:I369">
     <cfRule type="expression" priority="368" dxfId="0">
       <formula>$H369="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A370:J370">
+  <conditionalFormatting sqref="A370:I370">
     <cfRule type="expression" priority="369" dxfId="0">
       <formula>$H370="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A371:J371">
+  <conditionalFormatting sqref="A371:I371">
     <cfRule type="expression" priority="370" dxfId="0">
       <formula>$H371="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A372:J372">
+  <conditionalFormatting sqref="A372:I372">
     <cfRule type="expression" priority="371" dxfId="0">
       <formula>$H372="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A373:J373">
+  <conditionalFormatting sqref="A373:I373">
     <cfRule type="expression" priority="372" dxfId="0">
       <formula>$H373="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A374:J374">
+  <conditionalFormatting sqref="A374:I374">
     <cfRule type="expression" priority="373" dxfId="0">
       <formula>$H374="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A375:J375">
+  <conditionalFormatting sqref="A375:I375">
     <cfRule type="expression" priority="374" dxfId="0">
       <formula>$H375="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A376:J376">
+  <conditionalFormatting sqref="A376:I376">
     <cfRule type="expression" priority="375" dxfId="0">
       <formula>$H376="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A377:J377">
+  <conditionalFormatting sqref="A377:I377">
     <cfRule type="expression" priority="376" dxfId="0">
       <formula>$H377="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A378:J378">
+  <conditionalFormatting sqref="A378:I378">
     <cfRule type="expression" priority="377" dxfId="0">
       <formula>$H378="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A379:J379">
+  <conditionalFormatting sqref="A379:I379">
     <cfRule type="expression" priority="378" dxfId="0">
       <formula>$H379="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A380:J380">
+  <conditionalFormatting sqref="A380:I380">
     <cfRule type="expression" priority="379" dxfId="0">
       <formula>$H380="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A381:J381">
+  <conditionalFormatting sqref="A381:I381">
     <cfRule type="expression" priority="380" dxfId="0">
       <formula>$H381="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A382:J382">
+  <conditionalFormatting sqref="A382:I382">
     <cfRule type="expression" priority="381" dxfId="0">
       <formula>$H382="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A383:J383">
+  <conditionalFormatting sqref="A383:I383">
     <cfRule type="expression" priority="382" dxfId="0">
       <formula>$H383="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A384:J384">
+  <conditionalFormatting sqref="A384:I384">
     <cfRule type="expression" priority="383" dxfId="0">
       <formula>$H384="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A385:J385">
+  <conditionalFormatting sqref="A385:I385">
     <cfRule type="expression" priority="384" dxfId="0">
       <formula>$H385="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A386:J386">
+  <conditionalFormatting sqref="A386:I386">
     <cfRule type="expression" priority="385" dxfId="0">
       <formula>$H386="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A387:J387">
+  <conditionalFormatting sqref="A387:I387">
     <cfRule type="expression" priority="386" dxfId="0">
       <formula>$H387="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A388:J388">
+  <conditionalFormatting sqref="A388:I388">
     <cfRule type="expression" priority="387" dxfId="0">
       <formula>$H388="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A389:J389">
+  <conditionalFormatting sqref="A389:I389">
     <cfRule type="expression" priority="388" dxfId="0">
       <formula>$H389="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A390:J390">
+  <conditionalFormatting sqref="A390:I390">
     <cfRule type="expression" priority="389" dxfId="0">
       <formula>$H390="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A391:J391">
+  <conditionalFormatting sqref="A391:I391">
     <cfRule type="expression" priority="390" dxfId="0">
       <formula>$H391="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A392:J392">
+  <conditionalFormatting sqref="A392:I392">
     <cfRule type="expression" priority="391" dxfId="0">
       <formula>$H392="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A393:J393">
+  <conditionalFormatting sqref="A393:I393">
     <cfRule type="expression" priority="392" dxfId="0">
       <formula>$H393="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A394:J394">
+  <conditionalFormatting sqref="A394:I394">
     <cfRule type="expression" priority="393" dxfId="0">
       <formula>$H394="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A395:J395">
+  <conditionalFormatting sqref="A395:I395">
     <cfRule type="expression" priority="394" dxfId="0">
       <formula>$H395="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A396:J396">
+  <conditionalFormatting sqref="A396:I396">
     <cfRule type="expression" priority="395" dxfId="0">
       <formula>$H396="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A397:J397">
+  <conditionalFormatting sqref="A397:I397">
     <cfRule type="expression" priority="396" dxfId="0">
       <formula>$H397="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A398:J398">
+  <conditionalFormatting sqref="A398:I398">
     <cfRule type="expression" priority="397" dxfId="0">
       <formula>$H398="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A399:J399">
+  <conditionalFormatting sqref="A399:I399">
     <cfRule type="expression" priority="398" dxfId="0">
       <formula>$H399="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A400:J400">
+  <conditionalFormatting sqref="A400:I400">
     <cfRule type="expression" priority="399" dxfId="0">
       <formula>$H400="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A401:J401">
+  <conditionalFormatting sqref="A401:I401">
     <cfRule type="expression" priority="400" dxfId="0">
       <formula>$H401="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A402:J402">
+  <conditionalFormatting sqref="A402:I402">
     <cfRule type="expression" priority="401" dxfId="0">
       <formula>$H402="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A403:J403">
+  <conditionalFormatting sqref="A403:I403">
     <cfRule type="expression" priority="402" dxfId="0">
       <formula>$H403="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A404:J404">
+  <conditionalFormatting sqref="A404:I404">
     <cfRule type="expression" priority="403" dxfId="0">
       <formula>$H404="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A405:J405">
+  <conditionalFormatting sqref="A405:I405">
     <cfRule type="expression" priority="404" dxfId="0">
       <formula>$H405="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A406:J406">
+  <conditionalFormatting sqref="A406:I406">
     <cfRule type="expression" priority="405" dxfId="0">
       <formula>$H406="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A407:J407">
+  <conditionalFormatting sqref="A407:I407">
     <cfRule type="expression" priority="406" dxfId="0">
       <formula>$H407="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A408:J408">
+  <conditionalFormatting sqref="A408:I408">
     <cfRule type="expression" priority="407" dxfId="0">
       <formula>$H408="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A409:J409">
+  <conditionalFormatting sqref="A409:I409">
     <cfRule type="expression" priority="408" dxfId="0">
       <formula>$H409="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A410:J410">
+  <conditionalFormatting sqref="A410:I410">
     <cfRule type="expression" priority="409" dxfId="0">
       <formula>$H410="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A411:J411">
+  <conditionalFormatting sqref="A411:I411">
     <cfRule type="expression" priority="410" dxfId="0">
       <formula>$H411="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A412:J412">
+  <conditionalFormatting sqref="A412:I412">
     <cfRule type="expression" priority="411" dxfId="0">
       <formula>$H412="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A413:J413">
+  <conditionalFormatting sqref="A413:I413">
     <cfRule type="expression" priority="412" dxfId="0">
       <formula>$H413="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A414:J414">
+  <conditionalFormatting sqref="A414:I414">
     <cfRule type="expression" priority="413" dxfId="0">
       <formula>$H414="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A415:J415">
+  <conditionalFormatting sqref="A415:I415">
     <cfRule type="expression" priority="414" dxfId="0">
       <formula>$H415="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A416:J416">
+  <conditionalFormatting sqref="A416:I416">
     <cfRule type="expression" priority="415" dxfId="0">
       <formula>$H416="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A417:J417">
+  <conditionalFormatting sqref="A417:I417">
     <cfRule type="expression" priority="416" dxfId="0">
       <formula>$H417="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A418:J418">
+  <conditionalFormatting sqref="A418:I418">
     <cfRule type="expression" priority="417" dxfId="0">
       <formula>$H418="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A419:J419">
+  <conditionalFormatting sqref="A419:I419">
     <cfRule type="expression" priority="418" dxfId="0">
       <formula>$H419="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A420:J420">
+  <conditionalFormatting sqref="A420:I420">
     <cfRule type="expression" priority="419" dxfId="0">
       <formula>$H420="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A421:J421">
+  <conditionalFormatting sqref="A421:I421">
     <cfRule type="expression" priority="420" dxfId="0">
       <formula>$H421="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A422:J422">
+  <conditionalFormatting sqref="A422:I422">
     <cfRule type="expression" priority="421" dxfId="0">
       <formula>$H422="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A423:J423">
+  <conditionalFormatting sqref="A423:I423">
     <cfRule type="expression" priority="422" dxfId="0">
       <formula>$H423="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A424:J424">
+  <conditionalFormatting sqref="A424:I424">
     <cfRule type="expression" priority="423" dxfId="0">
       <formula>$H424="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A425:J425">
+  <conditionalFormatting sqref="A425:I425">
     <cfRule type="expression" priority="424" dxfId="0">
       <formula>$H425="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A426:J426">
+  <conditionalFormatting sqref="A426:I426">
     <cfRule type="expression" priority="425" dxfId="0">
       <formula>$H426="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A427:J427">
+  <conditionalFormatting sqref="A427:I427">
     <cfRule type="expression" priority="426" dxfId="0">
       <formula>$H427="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A428:J428">
+  <conditionalFormatting sqref="A428:I428">
     <cfRule type="expression" priority="427" dxfId="0">
       <formula>$H428="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A429:J429">
+  <conditionalFormatting sqref="A429:I429">
     <cfRule type="expression" priority="428" dxfId="0">
       <formula>$H429="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A430:J430">
+  <conditionalFormatting sqref="A430:I430">
     <cfRule type="expression" priority="429" dxfId="0">
       <formula>$H430="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A431:J431">
+  <conditionalFormatting sqref="A431:I431">
     <cfRule type="expression" priority="430" dxfId="0">
       <formula>$H431="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A432:J432">
+  <conditionalFormatting sqref="A432:I432">
     <cfRule type="expression" priority="431" dxfId="0">
       <formula>$H432="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A433:J433">
+  <conditionalFormatting sqref="A433:I433">
     <cfRule type="expression" priority="432" dxfId="0">
       <formula>$H433="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A434:J434">
+  <conditionalFormatting sqref="A434:I434">
     <cfRule type="expression" priority="433" dxfId="0">
       <formula>$H434="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A435:J435">
+  <conditionalFormatting sqref="A435:I435">
     <cfRule type="expression" priority="434" dxfId="0">
       <formula>$H435="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A436:J436">
+  <conditionalFormatting sqref="A436:I436">
     <cfRule type="expression" priority="435" dxfId="0">
       <formula>$H436="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A437:J437">
+  <conditionalFormatting sqref="A437:I437">
     <cfRule type="expression" priority="436" dxfId="0">
       <formula>$H437="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A438:J438">
+  <conditionalFormatting sqref="A438:I438">
     <cfRule type="expression" priority="437" dxfId="0">
       <formula>$H438="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A439:J439">
+  <conditionalFormatting sqref="A439:I439">
     <cfRule type="expression" priority="438" dxfId="0">
       <formula>$H439="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A440:J440">
+  <conditionalFormatting sqref="A440:I440">
     <cfRule type="expression" priority="439" dxfId="0">
       <formula>$H440="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A441:J441">
+  <conditionalFormatting sqref="A441:I441">
     <cfRule type="expression" priority="440" dxfId="0">
       <formula>$H441="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A442:J442">
+  <conditionalFormatting sqref="A442:I442">
     <cfRule type="expression" priority="441" dxfId="0">
       <formula>$H442="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A443:J443">
+  <conditionalFormatting sqref="A443:I443">
     <cfRule type="expression" priority="442" dxfId="0">
       <formula>$H443="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A444:J444">
+  <conditionalFormatting sqref="A444:I444">
     <cfRule type="expression" priority="443" dxfId="0">
       <formula>$H444="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A445:J445">
+  <conditionalFormatting sqref="A445:I445">
     <cfRule type="expression" priority="444" dxfId="0">
       <formula>$H445="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A446:J446">
+  <conditionalFormatting sqref="A446:I446">
     <cfRule type="expression" priority="445" dxfId="0">
       <formula>$H446="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A447:J447">
+  <conditionalFormatting sqref="A447:I447">
     <cfRule type="expression" priority="446" dxfId="0">
       <formula>$H447="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A448:J448">
+  <conditionalFormatting sqref="A448:I448">
     <cfRule type="expression" priority="447" dxfId="0">
       <formula>$H448="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A449:J449">
+  <conditionalFormatting sqref="A449:I449">
     <cfRule type="expression" priority="448" dxfId="0">
       <formula>$H449="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A450:J450">
+  <conditionalFormatting sqref="A450:I450">
     <cfRule type="expression" priority="449" dxfId="0">
       <formula>$H450="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A451:J451">
+  <conditionalFormatting sqref="A451:I451">
     <cfRule type="expression" priority="450" dxfId="0">
       <formula>$H451="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A452:J452">
+  <conditionalFormatting sqref="A452:I452">
     <cfRule type="expression" priority="451" dxfId="0">
       <formula>$H452="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A453:J453">
+  <conditionalFormatting sqref="A453:I453">
     <cfRule type="expression" priority="452" dxfId="0">
       <formula>$H453="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A454:J454">
+  <conditionalFormatting sqref="A454:I454">
     <cfRule type="expression" priority="453" dxfId="0">
       <formula>$H454="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A455:J455">
+  <conditionalFormatting sqref="A455:I455">
     <cfRule type="expression" priority="454" dxfId="0">
       <formula>$H455="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A456:J456">
+  <conditionalFormatting sqref="A456:I456">
     <cfRule type="expression" priority="455" dxfId="0">
       <formula>$H456="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A457:J457">
+  <conditionalFormatting sqref="A457:I457">
     <cfRule type="expression" priority="456" dxfId="0">
       <formula>$H457="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A458:J458">
+  <conditionalFormatting sqref="A458:I458">
     <cfRule type="expression" priority="457" dxfId="0">
       <formula>$H458="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A459:J459">
+  <conditionalFormatting sqref="A459:I459">
     <cfRule type="expression" priority="458" dxfId="0">
       <formula>$H459="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A460:J460">
+  <conditionalFormatting sqref="A460:I460">
     <cfRule type="expression" priority="459" dxfId="0">
       <formula>$H460="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A461:J461">
+  <conditionalFormatting sqref="A461:I461">
     <cfRule type="expression" priority="460" dxfId="0">
       <formula>$H461="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A462:J462">
+  <conditionalFormatting sqref="A462:I462">
     <cfRule type="expression" priority="461" dxfId="0">
       <formula>$H462="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A463:J463">
+  <conditionalFormatting sqref="A463:I463">
     <cfRule type="expression" priority="462" dxfId="0">
       <formula>$H463="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A464:J464">
+  <conditionalFormatting sqref="A464:I464">
     <cfRule type="expression" priority="463" dxfId="0">
       <formula>$H464="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A465:J465">
+  <conditionalFormatting sqref="A465:I465">
     <cfRule type="expression" priority="464" dxfId="0">
       <formula>$H465="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A466:J466">
+  <conditionalFormatting sqref="A466:I466">
     <cfRule type="expression" priority="465" dxfId="0">
       <formula>$H466="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A467:J467">
+  <conditionalFormatting sqref="A467:I467">
     <cfRule type="expression" priority="466" dxfId="0">
       <formula>$H467="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A468:J468">
+  <conditionalFormatting sqref="A468:I468">
     <cfRule type="expression" priority="467" dxfId="0">
       <formula>$H468="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A469:J469">
+  <conditionalFormatting sqref="A469:I469">
     <cfRule type="expression" priority="468" dxfId="0">
       <formula>$H469="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A470:J470">
+  <conditionalFormatting sqref="A470:I470">
     <cfRule type="expression" priority="469" dxfId="0">
       <formula>$H470="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A471:J471">
+  <conditionalFormatting sqref="A471:I471">
     <cfRule type="expression" priority="470" dxfId="0">
       <formula>$H471="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A472:J472">
+  <conditionalFormatting sqref="A472:I472">
     <cfRule type="expression" priority="471" dxfId="0">
       <formula>$H472="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A473:J473">
+  <conditionalFormatting sqref="A473:I473">
     <cfRule type="expression" priority="472" dxfId="0">
       <formula>$H473="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A474:J474">
+  <conditionalFormatting sqref="A474:I474">
     <cfRule type="expression" priority="473" dxfId="0">
       <formula>$H474="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A475:J475">
+  <conditionalFormatting sqref="A475:I475">
     <cfRule type="expression" priority="474" dxfId="0">
       <formula>$H475="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A476:J476">
+  <conditionalFormatting sqref="A476:I476">
     <cfRule type="expression" priority="475" dxfId="0">
       <formula>$H476="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A477:J477">
+  <conditionalFormatting sqref="A477:I477">
     <cfRule type="expression" priority="476" dxfId="0">
       <formula>$H477="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A478:J478">
+  <conditionalFormatting sqref="A478:I478">
     <cfRule type="expression" priority="477" dxfId="0">
       <formula>$H478="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A479:J479">
+  <conditionalFormatting sqref="A479:I479">
     <cfRule type="expression" priority="478" dxfId="0">
       <formula>$H479="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A480:J480">
+  <conditionalFormatting sqref="A480:I480">
     <cfRule type="expression" priority="479" dxfId="0">
       <formula>$H480="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A481:J481">
+  <conditionalFormatting sqref="A481:I481">
     <cfRule type="expression" priority="480" dxfId="0">
       <formula>$H481="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A482:J482">
+  <conditionalFormatting sqref="A482:I482">
     <cfRule type="expression" priority="481" dxfId="0">
       <formula>$H482="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A483:J483">
+  <conditionalFormatting sqref="A483:I483">
     <cfRule type="expression" priority="482" dxfId="0">
       <formula>$H483="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A484:J484">
+  <conditionalFormatting sqref="A484:I484">
     <cfRule type="expression" priority="483" dxfId="0">
       <formula>$H484="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A485:J485">
+  <conditionalFormatting sqref="A485:I485">
     <cfRule type="expression" priority="484" dxfId="0">
       <formula>$H485="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A486:J486">
+  <conditionalFormatting sqref="A486:I486">
     <cfRule type="expression" priority="485" dxfId="0">
       <formula>$H486="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A487:J487">
+  <conditionalFormatting sqref="A487:I487">
     <cfRule type="expression" priority="486" dxfId="0">
       <formula>$H487="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A488:J488">
+  <conditionalFormatting sqref="A488:I488">
     <cfRule type="expression" priority="487" dxfId="0">
       <formula>$H488="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A489:J489">
+  <conditionalFormatting sqref="A489:I489">
     <cfRule type="expression" priority="488" dxfId="0">
       <formula>$H489="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A490:J490">
+  <conditionalFormatting sqref="A490:I490">
     <cfRule type="expression" priority="489" dxfId="0">
       <formula>$H490="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A491:J491">
+  <conditionalFormatting sqref="A491:I491">
     <cfRule type="expression" priority="490" dxfId="0">
       <formula>$H491="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A492:J492">
+  <conditionalFormatting sqref="A492:I492">
     <cfRule type="expression" priority="491" dxfId="0">
       <formula>$H492="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A493:J493">
+  <conditionalFormatting sqref="A493:I493">
     <cfRule type="expression" priority="492" dxfId="0">
       <formula>$H493="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A494:J494">
+  <conditionalFormatting sqref="A494:I494">
     <cfRule type="expression" priority="493" dxfId="0">
       <formula>$H494="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A495:J495">
+  <conditionalFormatting sqref="A495:I495">
     <cfRule type="expression" priority="494" dxfId="0">
       <formula>$H495="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A496:J496">
+  <conditionalFormatting sqref="A496:I496">
     <cfRule type="expression" priority="495" dxfId="0">
       <formula>$H496="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A497:J497">
+  <conditionalFormatting sqref="A497:I497">
     <cfRule type="expression" priority="496" dxfId="0">
       <formula>$H497="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A498:J498">
+  <conditionalFormatting sqref="A498:I498">
     <cfRule type="expression" priority="497" dxfId="0">
       <formula>$H498="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A499:J499">
+  <conditionalFormatting sqref="A499:I499">
     <cfRule type="expression" priority="498" dxfId="0">
       <formula>$H499="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A500:J500">
+  <conditionalFormatting sqref="A500:I500">
     <cfRule type="expression" priority="499" dxfId="0">
       <formula>$H500="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A501:J501">
+  <conditionalFormatting sqref="A501:I501">
     <cfRule type="expression" priority="500" dxfId="0">
       <formula>$H501="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A502:J502">
+  <conditionalFormatting sqref="A502:I502">
     <cfRule type="expression" priority="501" dxfId="0">
       <formula>$H502="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A503:J503">
+  <conditionalFormatting sqref="A503:I503">
     <cfRule type="expression" priority="502" dxfId="0">
       <formula>$H503="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A504:J504">
+  <conditionalFormatting sqref="A504:I504">
     <cfRule type="expression" priority="503" dxfId="0">
       <formula>$H504="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A505:J505">
+  <conditionalFormatting sqref="A505:I505">
     <cfRule type="expression" priority="504" dxfId="0">
       <formula>$H505="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A506:J506">
+  <conditionalFormatting sqref="A506:I506">
     <cfRule type="expression" priority="505" dxfId="0">
       <formula>$H506="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A507:J507">
+  <conditionalFormatting sqref="A507:I507">
     <cfRule type="expression" priority="506" dxfId="0">
       <formula>$H507="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A508:J508">
+  <conditionalFormatting sqref="A508:I508">
     <cfRule type="expression" priority="507" dxfId="0">
       <formula>$H508="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A509:J509">
+  <conditionalFormatting sqref="A509:I509">
     <cfRule type="expression" priority="508" dxfId="0">
       <formula>$H509="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A510:J510">
+  <conditionalFormatting sqref="A510:I510">
     <cfRule type="expression" priority="509" dxfId="0">
       <formula>$H510="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A511:J511">
+  <conditionalFormatting sqref="A511:I511">
     <cfRule type="expression" priority="510" dxfId="0">
       <formula>$H511="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A512:J512">
+  <conditionalFormatting sqref="A512:I512">
     <cfRule type="expression" priority="511" dxfId="0">
       <formula>$H512="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A513:J513">
+  <conditionalFormatting sqref="A513:I513">
     <cfRule type="expression" priority="512" dxfId="0">
       <formula>$H513="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A514:J514">
+  <conditionalFormatting sqref="A514:I514">
     <cfRule type="expression" priority="513" dxfId="0">
       <formula>$H514="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A515:J515">
+  <conditionalFormatting sqref="A515:I515">
     <cfRule type="expression" priority="514" dxfId="0">
       <formula>$H515="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A516:J516">
+  <conditionalFormatting sqref="A516:I516">
     <cfRule type="expression" priority="515" dxfId="0">
       <formula>$H516="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A517:J517">
+  <conditionalFormatting sqref="A517:I517">
     <cfRule type="expression" priority="516" dxfId="0">
       <formula>$H517="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A518:J518">
+  <conditionalFormatting sqref="A518:I518">
     <cfRule type="expression" priority="517" dxfId="0">
       <formula>$H518="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A519:J519">
+  <conditionalFormatting sqref="A519:I519">
     <cfRule type="expression" priority="518" dxfId="0">
       <formula>$H519="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A520:J520">
+  <conditionalFormatting sqref="A520:I520">
     <cfRule type="expression" priority="519" dxfId="0">
       <formula>$H520="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A521:J521">
+  <conditionalFormatting sqref="A521:I521">
     <cfRule type="expression" priority="520" dxfId="0">
       <formula>$H521="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A522:J522">
+  <conditionalFormatting sqref="A522:I522">
     <cfRule type="expression" priority="521" dxfId="0">
       <formula>$H522="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A523:J523">
+  <conditionalFormatting sqref="A523:I523">
     <cfRule type="expression" priority="522" dxfId="0">
       <formula>$H523="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A524:J524">
+  <conditionalFormatting sqref="A524:I524">
     <cfRule type="expression" priority="523" dxfId="0">
       <formula>$H524="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A525:J525">
+  <conditionalFormatting sqref="A525:I525">
     <cfRule type="expression" priority="524" dxfId="0">
       <formula>$H525="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A526:J526">
+  <conditionalFormatting sqref="A526:I526">
     <cfRule type="expression" priority="525" dxfId="0">
       <formula>$H526="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A527:J527">
+  <conditionalFormatting sqref="A527:I527">
     <cfRule type="expression" priority="526" dxfId="0">
       <formula>$H527="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A528:J528">
+  <conditionalFormatting sqref="A528:I528">
     <cfRule type="expression" priority="527" dxfId="0">
       <formula>$H528="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A529:J529">
+  <conditionalFormatting sqref="A529:I529">
     <cfRule type="expression" priority="528" dxfId="0">
       <formula>$H529="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A530:J530">
+  <conditionalFormatting sqref="A530:I530">
     <cfRule type="expression" priority="529" dxfId="0">
       <formula>$H530="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A531:J531">
+  <conditionalFormatting sqref="A531:I531">
     <cfRule type="expression" priority="530" dxfId="0">
       <formula>$H531="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A532:J532">
+  <conditionalFormatting sqref="A532:I532">
     <cfRule type="expression" priority="531" dxfId="0">
       <formula>$H532="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A533:J533">
+  <conditionalFormatting sqref="A533:I533">
     <cfRule type="expression" priority="532" dxfId="0">
       <formula>$H533="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A534:J534">
+  <conditionalFormatting sqref="A534:I534">
     <cfRule type="expression" priority="533" dxfId="0">
       <formula>$H534="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A535:J535">
+  <conditionalFormatting sqref="A535:I535">
     <cfRule type="expression" priority="534" dxfId="0">
       <formula>$H535="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A536:J536">
+  <conditionalFormatting sqref="A536:I536">
     <cfRule type="expression" priority="535" dxfId="0">
       <formula>$H536="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A537:J537">
+  <conditionalFormatting sqref="A537:I537">
     <cfRule type="expression" priority="536" dxfId="0">
       <formula>$H537="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A538:J538">
+  <conditionalFormatting sqref="A538:I538">
     <cfRule type="expression" priority="537" dxfId="0">
       <formula>$H538="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A539:J539">
+  <conditionalFormatting sqref="A539:I539">
     <cfRule type="expression" priority="538" dxfId="0">
       <formula>$H539="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A540:J540">
+  <conditionalFormatting sqref="A540:I540">
     <cfRule type="expression" priority="539" dxfId="0">
       <formula>$H540="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A541:J541">
+  <conditionalFormatting sqref="A541:I541">
     <cfRule type="expression" priority="540" dxfId="0">
       <formula>$H541="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A542:J542">
+  <conditionalFormatting sqref="A542:I542">
     <cfRule type="expression" priority="541" dxfId="0">
       <formula>$H542="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A543:J543">
+  <conditionalFormatting sqref="A543:I543">
     <cfRule type="expression" priority="542" dxfId="0">
       <formula>$H543="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A544:J544">
+  <conditionalFormatting sqref="A544:I544">
     <cfRule type="expression" priority="543" dxfId="0">
       <formula>$H544="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A545:J545">
+  <conditionalFormatting sqref="A545:I545">
     <cfRule type="expression" priority="544" dxfId="0">
       <formula>$H545="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A546:J546">
+  <conditionalFormatting sqref="A546:I546">
     <cfRule type="expression" priority="545" dxfId="0">
       <formula>$H546="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A547:J547">
+  <conditionalFormatting sqref="A547:I547">
     <cfRule type="expression" priority="546" dxfId="0">
       <formula>$H547="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A548:J548">
+  <conditionalFormatting sqref="A548:I548">
     <cfRule type="expression" priority="547" dxfId="0">
       <formula>$H548="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A549:J549">
+  <conditionalFormatting sqref="A549:I549">
     <cfRule type="expression" priority="548" dxfId="0">
       <formula>$H549="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A550:J550">
+  <conditionalFormatting sqref="A550:I550">
     <cfRule type="expression" priority="549" dxfId="0">
       <formula>$H550="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A551:J551">
+  <conditionalFormatting sqref="A551:I551">
     <cfRule type="expression" priority="550" dxfId="0">
       <formula>$H551="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A552:J552">
+  <conditionalFormatting sqref="A552:I552">
     <cfRule type="expression" priority="551" dxfId="0">
       <formula>$H552="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A553:J553">
+  <conditionalFormatting sqref="A553:I553">
     <cfRule type="expression" priority="552" dxfId="0">
       <formula>$H553="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A554:J554">
+  <conditionalFormatting sqref="A554:I554">
     <cfRule type="expression" priority="553" dxfId="0">
       <formula>$H554="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A555:J555">
+  <conditionalFormatting sqref="A555:I555">
     <cfRule type="expression" priority="554" dxfId="0">
       <formula>$H555="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A556:J556">
+  <conditionalFormatting sqref="A556:I556">
     <cfRule type="expression" priority="555" dxfId="0">
       <formula>$H556="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A557:J557">
+  <conditionalFormatting sqref="A557:I557">
     <cfRule type="expression" priority="556" dxfId="0">
       <formula>$H557="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A558:J558">
+  <conditionalFormatting sqref="A558:I558">
     <cfRule type="expression" priority="557" dxfId="0">
       <formula>$H558="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A559:J559">
+  <conditionalFormatting sqref="A559:I559">
     <cfRule type="expression" priority="558" dxfId="0">
       <formula>$H559="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A560:J560">
+  <conditionalFormatting sqref="A560:I560">
     <cfRule type="expression" priority="559" dxfId="0">
       <formula>$H560="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A561:J561">
+  <conditionalFormatting sqref="A561:I561">
     <cfRule type="expression" priority="560" dxfId="0">
       <formula>$H561="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A562:J562">
+  <conditionalFormatting sqref="A562:I562">
     <cfRule type="expression" priority="561" dxfId="0">
       <formula>$H562="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A563:J563">
+  <conditionalFormatting sqref="A563:I563">
     <cfRule type="expression" priority="562" dxfId="0">
       <formula>$H563="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A564:J564">
+  <conditionalFormatting sqref="A564:I564">
     <cfRule type="expression" priority="563" dxfId="0">
       <formula>$H564="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A565:J565">
+  <conditionalFormatting sqref="A565:I565">
     <cfRule type="expression" priority="564" dxfId="0">
       <formula>$H565="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A566:J566">
+  <conditionalFormatting sqref="A566:I566">
     <cfRule type="expression" priority="565" dxfId="0">
       <formula>$H566="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A567:J567">
+  <conditionalFormatting sqref="A567:I567">
     <cfRule type="expression" priority="566" dxfId="0">
       <formula>$H567="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A568:J568">
+  <conditionalFormatting sqref="A568:I568">
     <cfRule type="expression" priority="567" dxfId="0">
       <formula>$H568="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A569:J569">
+  <conditionalFormatting sqref="A569:I569">
     <cfRule type="expression" priority="568" dxfId="0">
       <formula>$H569="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A570:J570">
+  <conditionalFormatting sqref="A570:I570">
     <cfRule type="expression" priority="569" dxfId="0">
       <formula>$H570="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A571:J571">
+  <conditionalFormatting sqref="A571:I571">
     <cfRule type="expression" priority="570" dxfId="0">
       <formula>$H571="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A572:J572">
+  <conditionalFormatting sqref="A572:I572">
     <cfRule type="expression" priority="571" dxfId="0">
       <formula>$H572="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A573:J573">
+  <conditionalFormatting sqref="A573:I573">
     <cfRule type="expression" priority="572" dxfId="0">
       <formula>$H573="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A574:J574">
+  <conditionalFormatting sqref="A574:I574">
     <cfRule type="expression" priority="573" dxfId="0">
       <formula>$H574="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A575:J575">
+  <conditionalFormatting sqref="A575:I575">
     <cfRule type="expression" priority="574" dxfId="0">
       <formula>$H575="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A576:J576">
+  <conditionalFormatting sqref="A576:I576">
     <cfRule type="expression" priority="575" dxfId="0">
       <formula>$H576="YES"</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="4">
+  <dataValidations count="3">
     <dataValidation sqref="E2:E576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Income,Materials,Labor,Dump Fees,Fuel,Insurance,Tools,Repairs,Utilities,Owner Draw,Transfer"</formula1>
     </dataValidation>
     <dataValidation sqref="G2:G576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"Revenue,COGS,Expense,Non-Deductible"</formula1>
-    </dataValidation>
-    <dataValidation sqref="J2:J576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>",Bryan,Jameson,Casey,Tony,Unassigned Labor"</formula1>
     </dataValidation>
     <dataValidation sqref="I2:I576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Override note required" error="Override note required when manual override is YES." type="custom">
       <formula1>=OR(H2="NO",LEN(I2)&gt;0)</formula1>
@@ -36317,7 +35546,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -36413,7 +35642,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -36737,13 +35966,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -36753,7 +35982,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Contractor</t>
+          <t>Payroll</t>
         </is>
       </c>
       <c r="B1" s="4" t="inlineStr">
@@ -36765,44 +35994,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Bryan</t>
+          <t>Payroll Total</t>
         </is>
       </c>
       <c r="B2" s="2">
-        <f>SUMIFS(CATEGORIZED_2025!$C:$C,CATEGORIZED_2025!$E:$E,"Labor",CATEGORIZED_2025!$J:$J,A2)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Jameson</t>
-        </is>
-      </c>
-      <c r="B3" s="2">
-        <f>SUMIFS(CATEGORIZED_2025!$C:$C,CATEGORIZED_2025!$E:$E,"Labor",CATEGORIZED_2025!$J:$J,A3)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Casey</t>
-        </is>
-      </c>
-      <c r="B4" s="2">
-        <f>SUMIFS(CATEGORIZED_2025!$C:$C,CATEGORIZED_2025!$E:$E,"Labor",CATEGORIZED_2025!$J:$J,A4)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Tony</t>
-        </is>
-      </c>
-      <c r="B5" s="2">
-        <f>SUMIFS(CATEGORIZED_2025!$C:$C,CATEGORIZED_2025!$E:$E,"Labor",CATEGORIZED_2025!$J:$J,A5)</f>
+        <f>SUMIFS(CATEGORIZED_2025!$C:$C,CATEGORIZED_2025!$E:$E,"Labor")</f>
         <v/>
       </c>
     </row>

--- a/bill-docs-k7m2v9/AllPro_Tax_2025.xlsx
+++ b/bill-docs-k7m2v9/AllPro_Tax_2025.xlsx
@@ -14,6 +14,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="P&amp;L_2025" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MONTHLY_2025" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LABOR_2025" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OVERRIDE_LOG_2025" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TIEOUT_2025" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -26,7 +28,7 @@
     <numFmt numFmtId="164" formatCode="$#,##0.00"/>
     <numFmt numFmtId="165" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -48,6 +50,10 @@
     <font>
       <b val="1"/>
       <sz val="13"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="007A0000"/>
     </font>
   </fonts>
   <fills count="3">
@@ -75,7 +81,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -86,6 +92,7 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -36005,4 +36012,748 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="46" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="28" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>Manual Override Log - 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>Warning: Changing classification may impact tax reporting. Confirm with tax professional.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Manual Override Count</t>
+        </is>
+      </c>
+      <c r="B5">
+        <f>COUNTIF(CATEGORIZED_2025!$H:$H,"YES")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Total Amount in Overridden Transactions</t>
+        </is>
+      </c>
+      <c r="B6" s="2">
+        <f>SUMIFS(CATEGORIZED_2025!$C:$C,CATEGORIZED_2025!$H:$H,"YES")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>Amount</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>Original Group</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>Final Group</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>Manual Override</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>Override Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <f>IFERROR(FILTER(CATEGORIZED_2025!A:I,CATEGORIZED_2025!H:H="YES"),"No manual overrides")</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="19" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Month</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Beginning Balance (Stmt)</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Credits (Stmt)</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Debits (Stmt)</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Expected Ending (Stmt Calc)</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Ending Balance (Stmt)</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Statement Variance</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Credits Counted (Workbook)</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Debits Counted (Workbook)</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Credits Variance</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Debits Variance</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>7932.6</v>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>46338.58</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>22448.59</v>
+      </c>
+      <c r="E2" s="2">
+        <f>B2+C2-D2</f>
+        <v/>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>31822.59</v>
+      </c>
+      <c r="G2" s="2">
+        <f>F2-E2</f>
+        <v/>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>7113.78</v>
+      </c>
+      <c r="I2" s="2" t="n">
+        <v>22448.59</v>
+      </c>
+      <c r="J2" s="2">
+        <f>H2-C2</f>
+        <v/>
+      </c>
+      <c r="K2" s="2">
+        <f>I2-D2</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2025-02</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>31822.59</v>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>17843.24</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>34655.38</v>
+      </c>
+      <c r="E3" s="2">
+        <f>B3+C3-D3</f>
+        <v/>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>13510.45</v>
+      </c>
+      <c r="G3" s="2">
+        <f>F3-E3</f>
+        <v/>
+      </c>
+      <c r="H3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" s="2" t="n">
+        <v>34655.38</v>
+      </c>
+      <c r="J3" s="2">
+        <f>H3-C3</f>
+        <v/>
+      </c>
+      <c r="K3" s="2">
+        <f>I3-D3</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="2">
+        <f>B4+C4-D4</f>
+        <v/>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="2">
+        <f>F4-E4</f>
+        <v/>
+      </c>
+      <c r="H4" s="2" t="n">
+        <v>3575</v>
+      </c>
+      <c r="I4" s="2" t="n">
+        <v>26681.06</v>
+      </c>
+      <c r="J4" s="2">
+        <f>H4-C4</f>
+        <v/>
+      </c>
+      <c r="K4" s="2">
+        <f>I4-D4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2025-04</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="2">
+        <f>B5+C5-D5</f>
+        <v/>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="2">
+        <f>F5-E5</f>
+        <v/>
+      </c>
+      <c r="H5" s="2" t="n">
+        <v>15160</v>
+      </c>
+      <c r="I5" s="2" t="n">
+        <v>30344.28</v>
+      </c>
+      <c r="J5" s="2">
+        <f>H5-C5</f>
+        <v/>
+      </c>
+      <c r="K5" s="2">
+        <f>I5-D5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2025-05</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>10293</v>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>23294.39</v>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>21764.96</v>
+      </c>
+      <c r="E6" s="2">
+        <f>B6+C6-D6</f>
+        <v/>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>11822.43</v>
+      </c>
+      <c r="G6" s="2">
+        <f>F6-E6</f>
+        <v/>
+      </c>
+      <c r="H6" s="2" t="n">
+        <v>99479.81999999999</v>
+      </c>
+      <c r="I6" s="2" t="n">
+        <v>12027.21</v>
+      </c>
+      <c r="J6" s="2">
+        <f>H6-C6</f>
+        <v/>
+      </c>
+      <c r="K6" s="2">
+        <f>I6-D6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="2">
+        <f>B7+C7-D7</f>
+        <v/>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="2">
+        <f>F7-E7</f>
+        <v/>
+      </c>
+      <c r="H7" s="2" t="n">
+        <v>8705</v>
+      </c>
+      <c r="I7" s="2" t="n">
+        <v>14185.5</v>
+      </c>
+      <c r="J7" s="2">
+        <f>H7-C7</f>
+        <v/>
+      </c>
+      <c r="K7" s="2">
+        <f>I7-D7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2025-07</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="2">
+        <f>B8+C8-D8</f>
+        <v/>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="2">
+        <f>F8-E8</f>
+        <v/>
+      </c>
+      <c r="H8" s="2" t="n">
+        <v>29245.94</v>
+      </c>
+      <c r="I8" s="2" t="n">
+        <v>23326.61</v>
+      </c>
+      <c r="J8" s="2">
+        <f>H8-C8</f>
+        <v/>
+      </c>
+      <c r="K8" s="2">
+        <f>I8-D8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2025-08</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>19836.26</v>
+      </c>
+      <c r="C9" s="2" t="n">
+        <v>24595.03</v>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>28677.15</v>
+      </c>
+      <c r="E9" s="2">
+        <f>B9+C9-D9</f>
+        <v/>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>15754.14</v>
+      </c>
+      <c r="G9" s="2">
+        <f>F9-E9</f>
+        <v/>
+      </c>
+      <c r="H9" s="2" t="n">
+        <v>40112.38</v>
+      </c>
+      <c r="I9" s="2" t="n">
+        <v>9298.349999999999</v>
+      </c>
+      <c r="J9" s="2">
+        <f>H9-C9</f>
+        <v/>
+      </c>
+      <c r="K9" s="2">
+        <f>I9-D9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2025-09</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>15754.14</v>
+      </c>
+      <c r="C10" s="2" t="n">
+        <v>19582.1</v>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>23049.64</v>
+      </c>
+      <c r="E10" s="2">
+        <f>B10+C10-D10</f>
+        <v/>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>12286.6</v>
+      </c>
+      <c r="G10" s="2">
+        <f>F10-E10</f>
+        <v/>
+      </c>
+      <c r="H10" s="2" t="n">
+        <v>38566.18</v>
+      </c>
+      <c r="I10" s="2" t="n">
+        <v>11688.45</v>
+      </c>
+      <c r="J10" s="2">
+        <f>H10-C10</f>
+        <v/>
+      </c>
+      <c r="K10" s="2">
+        <f>I10-D10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>12286.6</v>
+      </c>
+      <c r="C11" s="2" t="n">
+        <v>33110.82</v>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>28694.53</v>
+      </c>
+      <c r="E11" s="2">
+        <f>B11+C11-D11</f>
+        <v/>
+      </c>
+      <c r="F11" s="2" t="n">
+        <v>16702.89</v>
+      </c>
+      <c r="G11" s="2">
+        <f>F11-E11</f>
+        <v/>
+      </c>
+      <c r="H11" s="2" t="n">
+        <v>33110.82</v>
+      </c>
+      <c r="I11" s="2" t="n">
+        <v>28694.53</v>
+      </c>
+      <c r="J11" s="2">
+        <f>H11-C11</f>
+        <v/>
+      </c>
+      <c r="K11" s="2">
+        <f>I11-D11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="2">
+        <f>B12+C12-D12</f>
+        <v/>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="2">
+        <f>F12-E12</f>
+        <v/>
+      </c>
+      <c r="H12" s="2" t="n">
+        <v>46059.53</v>
+      </c>
+      <c r="I12" s="2" t="n">
+        <v>3156.6</v>
+      </c>
+      <c r="J12" s="2">
+        <f>H12-C12</f>
+        <v/>
+      </c>
+      <c r="K12" s="2">
+        <f>I12-D12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="2">
+        <f>B13+C13-D13</f>
+        <v/>
+      </c>
+      <c r="F13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="2">
+        <f>F13-E13</f>
+        <v/>
+      </c>
+      <c r="H13" s="2" t="n">
+        <v>68733.48</v>
+      </c>
+      <c r="I13" s="2" t="n">
+        <v>3096.099999999999</v>
+      </c>
+      <c r="J13" s="2">
+        <f>H13-C13</f>
+        <v/>
+      </c>
+      <c r="K13" s="2">
+        <f>I13-D13</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B14" s="3">
+        <f>SUM(B2:B13)</f>
+        <v/>
+      </c>
+      <c r="C14" s="3">
+        <f>SUM(C2:C13)</f>
+        <v/>
+      </c>
+      <c r="D14" s="3">
+        <f>SUM(D2:D13)</f>
+        <v/>
+      </c>
+      <c r="E14" s="3">
+        <f>SUM(E2:E13)</f>
+        <v/>
+      </c>
+      <c r="F14" s="3">
+        <f>SUM(F2:F13)</f>
+        <v/>
+      </c>
+      <c r="G14" s="3">
+        <f>SUM(G2:G13)</f>
+        <v/>
+      </c>
+      <c r="H14" s="3">
+        <f>SUM(H2:H13)</f>
+        <v/>
+      </c>
+      <c r="I14" s="3">
+        <f>SUM(I2:I13)</f>
+        <v/>
+      </c>
+      <c r="J14" s="3">
+        <f>SUM(J2:J13)</f>
+        <v/>
+      </c>
+      <c r="K14" s="3">
+        <f>SUM(K2:K13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>Interpretation: Statement variance and credit/debit variances should be near zero after full reconciliation.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/bill-docs-k7m2v9/AllPro_Tax_2025.xlsx
+++ b/bill-docs-k7m2v9/AllPro_Tax_2025.xlsx
@@ -493,6 +493,7 @@
         <v>20676.13</v>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
@@ -510,6 +511,7 @@
         <v>49194.49</v>
       </c>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
@@ -11422,7 +11424,6 @@
         <f>IF(G2&lt;&gt;F2,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="5" t="n">
@@ -11459,7 +11460,6 @@
         <f>IF(G3&lt;&gt;F3,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="5" t="n">
@@ -11496,7 +11496,6 @@
         <f>IF(G4&lt;&gt;F4,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="5" t="n">
@@ -11533,7 +11532,6 @@
         <f>IF(G5&lt;&gt;F5,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="5" t="n">
@@ -11570,7 +11568,6 @@
         <f>IF(G6&lt;&gt;F6,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="5" t="n">
@@ -11607,7 +11604,6 @@
         <f>IF(G7&lt;&gt;F7,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="5" t="n">
@@ -11644,7 +11640,6 @@
         <f>IF(G8&lt;&gt;F8,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="5" t="n">
@@ -11681,7 +11676,6 @@
         <f>IF(G9&lt;&gt;F9,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="5" t="n">
@@ -11718,7 +11712,6 @@
         <f>IF(G10&lt;&gt;F10,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="n">
@@ -11755,7 +11748,6 @@
         <f>IF(G11&lt;&gt;F11,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="5" t="n">
@@ -11792,7 +11784,6 @@
         <f>IF(G12&lt;&gt;F12,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="5" t="n">
@@ -11829,7 +11820,6 @@
         <f>IF(G13&lt;&gt;F13,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="5" t="n">
@@ -11866,7 +11856,6 @@
         <f>IF(G14&lt;&gt;F14,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="5" t="n">
@@ -11903,7 +11892,6 @@
         <f>IF(G15&lt;&gt;F15,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="5" t="n">
@@ -11940,7 +11928,6 @@
         <f>IF(G16&lt;&gt;F16,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="5" t="n">
@@ -11977,7 +11964,6 @@
         <f>IF(G17&lt;&gt;F17,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="5" t="n">
@@ -12014,7 +12000,6 @@
         <f>IF(G18&lt;&gt;F18,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="5" t="n">
@@ -12051,7 +12036,6 @@
         <f>IF(G19&lt;&gt;F19,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="5" t="n">
@@ -12088,7 +12072,6 @@
         <f>IF(G20&lt;&gt;F20,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="5" t="n">
@@ -12125,7 +12108,6 @@
         <f>IF(G21&lt;&gt;F21,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="5" t="n">
@@ -12162,7 +12144,6 @@
         <f>IF(G22&lt;&gt;F22,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="5" t="n">
@@ -12199,7 +12180,6 @@
         <f>IF(G23&lt;&gt;F23,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="5" t="n">
@@ -12236,7 +12216,6 @@
         <f>IF(G24&lt;&gt;F24,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="5" t="n">
@@ -12273,7 +12252,6 @@
         <f>IF(G25&lt;&gt;F25,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="5" t="n">
@@ -12310,7 +12288,6 @@
         <f>IF(G26&lt;&gt;F26,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="5" t="n">
@@ -12347,7 +12324,6 @@
         <f>IF(G27&lt;&gt;F27,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="5" t="n">
@@ -12384,7 +12360,6 @@
         <f>IF(G28&lt;&gt;F28,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="5" t="n">
@@ -12421,7 +12396,6 @@
         <f>IF(G29&lt;&gt;F29,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="5" t="n">
@@ -12458,7 +12432,6 @@
         <f>IF(G30&lt;&gt;F30,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="5" t="n">
@@ -12495,7 +12468,6 @@
         <f>IF(G31&lt;&gt;F31,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="5" t="n">
@@ -12532,7 +12504,6 @@
         <f>IF(G32&lt;&gt;F32,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="5" t="n">
@@ -12569,7 +12540,6 @@
         <f>IF(G33&lt;&gt;F33,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="5" t="n">
@@ -12606,7 +12576,6 @@
         <f>IF(G34&lt;&gt;F34,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="5" t="n">
@@ -12643,7 +12612,6 @@
         <f>IF(G35&lt;&gt;F35,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="5" t="n">
@@ -12680,7 +12648,6 @@
         <f>IF(G36&lt;&gt;F36,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="5" t="n">
@@ -12717,7 +12684,6 @@
         <f>IF(G37&lt;&gt;F37,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="5" t="n">
@@ -12754,7 +12720,6 @@
         <f>IF(G38&lt;&gt;F38,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="5" t="n">
@@ -12791,7 +12756,6 @@
         <f>IF(G39&lt;&gt;F39,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="5" t="n">
@@ -12828,7 +12792,6 @@
         <f>IF(G40&lt;&gt;F40,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="5" t="n">
@@ -12865,7 +12828,6 @@
         <f>IF(G41&lt;&gt;F41,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="5" t="n">
@@ -12902,7 +12864,6 @@
         <f>IF(G42&lt;&gt;F42,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="5" t="n">
@@ -12939,7 +12900,6 @@
         <f>IF(G43&lt;&gt;F43,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="5" t="n">
@@ -12976,7 +12936,6 @@
         <f>IF(G44&lt;&gt;F44,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="5" t="n">
@@ -13013,7 +12972,6 @@
         <f>IF(G45&lt;&gt;F45,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="5" t="n">
@@ -13050,7 +13008,6 @@
         <f>IF(G46&lt;&gt;F46,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="5" t="n">
@@ -13087,7 +13044,6 @@
         <f>IF(G47&lt;&gt;F47,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="5" t="n">
@@ -13124,7 +13080,6 @@
         <f>IF(G48&lt;&gt;F48,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="5" t="n">
@@ -13161,7 +13116,6 @@
         <f>IF(G49&lt;&gt;F49,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="5" t="n">
@@ -13198,7 +13152,6 @@
         <f>IF(G50&lt;&gt;F50,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="5" t="n">
@@ -13235,7 +13188,6 @@
         <f>IF(G51&lt;&gt;F51,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="5" t="n">
@@ -13272,7 +13224,6 @@
         <f>IF(G52&lt;&gt;F52,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="5" t="n">
@@ -13309,7 +13260,6 @@
         <f>IF(G53&lt;&gt;F53,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="5" t="n">
@@ -13346,7 +13296,6 @@
         <f>IF(G54&lt;&gt;F54,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="5" t="n">
@@ -13383,7 +13332,6 @@
         <f>IF(G55&lt;&gt;F55,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="5" t="n">
@@ -13420,7 +13368,6 @@
         <f>IF(G56&lt;&gt;F56,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="5" t="n">
@@ -13457,7 +13404,6 @@
         <f>IF(G57&lt;&gt;F57,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="5" t="n">
@@ -13494,7 +13440,6 @@
         <f>IF(G58&lt;&gt;F58,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="5" t="n">
@@ -13531,7 +13476,6 @@
         <f>IF(G59&lt;&gt;F59,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="5" t="n">
@@ -13568,7 +13512,6 @@
         <f>IF(G60&lt;&gt;F60,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="5" t="n">
@@ -13605,7 +13548,6 @@
         <f>IF(G61&lt;&gt;F61,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="5" t="n">
@@ -13642,7 +13584,6 @@
         <f>IF(G62&lt;&gt;F62,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="5" t="n">
@@ -13679,7 +13620,6 @@
         <f>IF(G63&lt;&gt;F63,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="5" t="n">
@@ -13716,7 +13656,6 @@
         <f>IF(G64&lt;&gt;F64,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="5" t="n">
@@ -13753,7 +13692,6 @@
         <f>IF(G65&lt;&gt;F65,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="5" t="n">
@@ -13790,7 +13728,6 @@
         <f>IF(G66&lt;&gt;F66,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="5" t="n">
@@ -13827,7 +13764,6 @@
         <f>IF(G67&lt;&gt;F67,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="5" t="n">
@@ -13864,7 +13800,6 @@
         <f>IF(G68&lt;&gt;F68,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="5" t="n">
@@ -13901,7 +13836,6 @@
         <f>IF(G69&lt;&gt;F69,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="5" t="n">
@@ -13938,7 +13872,6 @@
         <f>IF(G70&lt;&gt;F70,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="5" t="n">
@@ -13975,7 +13908,6 @@
         <f>IF(G71&lt;&gt;F71,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="5" t="n">
@@ -14012,7 +13944,6 @@
         <f>IF(G72&lt;&gt;F72,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="5" t="n">
@@ -14049,7 +13980,6 @@
         <f>IF(G73&lt;&gt;F73,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="5" t="n">
@@ -14086,7 +14016,6 @@
         <f>IF(G74&lt;&gt;F74,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="5" t="n">
@@ -14123,7 +14052,6 @@
         <f>IF(G75&lt;&gt;F75,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="5" t="n">
@@ -14160,7 +14088,6 @@
         <f>IF(G76&lt;&gt;F76,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="5" t="n">
@@ -14197,7 +14124,6 @@
         <f>IF(G77&lt;&gt;F77,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="5" t="n">
@@ -14234,7 +14160,6 @@
         <f>IF(G78&lt;&gt;F78,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="5" t="n">
@@ -14271,7 +14196,6 @@
         <f>IF(G79&lt;&gt;F79,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="5" t="n">
@@ -14308,7 +14232,6 @@
         <f>IF(G80&lt;&gt;F80,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="5" t="n">
@@ -14345,7 +14268,6 @@
         <f>IF(G81&lt;&gt;F81,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="5" t="n">
@@ -14382,7 +14304,6 @@
         <f>IF(G82&lt;&gt;F82,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="5" t="n">
@@ -14419,7 +14340,6 @@
         <f>IF(G83&lt;&gt;F83,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="5" t="n">
@@ -14456,7 +14376,6 @@
         <f>IF(G84&lt;&gt;F84,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="5" t="n">
@@ -14493,7 +14412,6 @@
         <f>IF(G85&lt;&gt;F85,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="5" t="n">
@@ -14530,7 +14448,6 @@
         <f>IF(G86&lt;&gt;F86,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="5" t="n">
@@ -14567,7 +14484,6 @@
         <f>IF(G87&lt;&gt;F87,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="5" t="n">
@@ -14604,7 +14520,6 @@
         <f>IF(G88&lt;&gt;F88,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" s="5" t="n">
@@ -14641,7 +14556,6 @@
         <f>IF(G89&lt;&gt;F89,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="5" t="n">
@@ -14678,7 +14592,6 @@
         <f>IF(G90&lt;&gt;F90,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" s="5" t="n">
@@ -14715,7 +14628,6 @@
         <f>IF(G91&lt;&gt;F91,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" s="5" t="n">
@@ -14752,7 +14664,6 @@
         <f>IF(G92&lt;&gt;F92,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="5" t="n">
@@ -14789,7 +14700,6 @@
         <f>IF(G93&lt;&gt;F93,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="5" t="n">
@@ -14826,7 +14736,6 @@
         <f>IF(G94&lt;&gt;F94,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="5" t="n">
@@ -14863,7 +14772,6 @@
         <f>IF(G95&lt;&gt;F95,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" s="5" t="n">
@@ -14900,7 +14808,6 @@
         <f>IF(G96&lt;&gt;F96,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" s="5" t="n">
@@ -14937,7 +14844,6 @@
         <f>IF(G97&lt;&gt;F97,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" s="5" t="n">
@@ -14974,7 +14880,6 @@
         <f>IF(G98&lt;&gt;F98,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" s="5" t="n">
@@ -15011,7 +14916,6 @@
         <f>IF(G99&lt;&gt;F99,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" s="5" t="n">
@@ -15048,7 +14952,6 @@
         <f>IF(G100&lt;&gt;F100,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" s="5" t="n">
@@ -15085,7 +14988,6 @@
         <f>IF(G101&lt;&gt;F101,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" s="5" t="n">
@@ -15122,7 +15024,6 @@
         <f>IF(G102&lt;&gt;F102,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" s="5" t="n">
@@ -15159,7 +15060,6 @@
         <f>IF(G103&lt;&gt;F103,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" s="5" t="n">
@@ -15196,7 +15096,6 @@
         <f>IF(G104&lt;&gt;F104,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" s="5" t="n">
@@ -15233,7 +15132,6 @@
         <f>IF(G105&lt;&gt;F105,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" s="5" t="n">
@@ -15270,7 +15168,6 @@
         <f>IF(G106&lt;&gt;F106,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" s="5" t="n">
@@ -15307,7 +15204,6 @@
         <f>IF(G107&lt;&gt;F107,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" s="5" t="n">
@@ -15344,7 +15240,6 @@
         <f>IF(G108&lt;&gt;F108,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" s="5" t="n">
@@ -15381,7 +15276,6 @@
         <f>IF(G109&lt;&gt;F109,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" s="5" t="n">
@@ -15418,7 +15312,6 @@
         <f>IF(G110&lt;&gt;F110,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" s="5" t="n">
@@ -15455,7 +15348,6 @@
         <f>IF(G111&lt;&gt;F111,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" s="5" t="n">
@@ -15492,7 +15384,6 @@
         <f>IF(G112&lt;&gt;F112,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" s="5" t="n">
@@ -15529,7 +15420,6 @@
         <f>IF(G113&lt;&gt;F113,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" s="5" t="n">
@@ -15566,7 +15456,6 @@
         <f>IF(G114&lt;&gt;F114,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" s="5" t="n">
@@ -15603,7 +15492,6 @@
         <f>IF(G115&lt;&gt;F115,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" s="5" t="n">
@@ -15640,7 +15528,6 @@
         <f>IF(G116&lt;&gt;F116,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" s="5" t="n">
@@ -15677,7 +15564,6 @@
         <f>IF(G117&lt;&gt;F117,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" s="5" t="n">
@@ -15714,7 +15600,6 @@
         <f>IF(G118&lt;&gt;F118,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" s="5" t="n">
@@ -15751,7 +15636,6 @@
         <f>IF(G119&lt;&gt;F119,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" s="5" t="n">
@@ -15788,7 +15672,6 @@
         <f>IF(G120&lt;&gt;F120,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" s="5" t="n">
@@ -15825,7 +15708,6 @@
         <f>IF(G121&lt;&gt;F121,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" s="5" t="n">
@@ -15862,7 +15744,6 @@
         <f>IF(G122&lt;&gt;F122,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" s="5" t="n">
@@ -15899,7 +15780,6 @@
         <f>IF(G123&lt;&gt;F123,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" s="5" t="n">
@@ -15936,7 +15816,6 @@
         <f>IF(G124&lt;&gt;F124,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" s="5" t="n">
@@ -15973,7 +15852,6 @@
         <f>IF(G125&lt;&gt;F125,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" s="5" t="n">
@@ -16010,7 +15888,6 @@
         <f>IF(G126&lt;&gt;F126,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" s="5" t="n">
@@ -16047,7 +15924,6 @@
         <f>IF(G127&lt;&gt;F127,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" s="5" t="n">
@@ -16084,7 +15960,6 @@
         <f>IF(G128&lt;&gt;F128,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" s="5" t="n">
@@ -16121,7 +15996,6 @@
         <f>IF(G129&lt;&gt;F129,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" s="5" t="n">
@@ -16158,7 +16032,6 @@
         <f>IF(G130&lt;&gt;F130,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" s="5" t="n">
@@ -16195,7 +16068,6 @@
         <f>IF(G131&lt;&gt;F131,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" s="5" t="n">
@@ -16232,7 +16104,6 @@
         <f>IF(G132&lt;&gt;F132,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" s="5" t="n">
@@ -16269,7 +16140,6 @@
         <f>IF(G133&lt;&gt;F133,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" s="5" t="n">
@@ -16306,7 +16176,6 @@
         <f>IF(G134&lt;&gt;F134,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" s="5" t="n">
@@ -16343,7 +16212,6 @@
         <f>IF(G135&lt;&gt;F135,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" s="5" t="n">
@@ -16380,7 +16248,6 @@
         <f>IF(G136&lt;&gt;F136,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" s="5" t="n">
@@ -16417,7 +16284,6 @@
         <f>IF(G137&lt;&gt;F137,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" s="5" t="n">
@@ -16454,7 +16320,6 @@
         <f>IF(G138&lt;&gt;F138,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" s="5" t="n">
@@ -16491,7 +16356,6 @@
         <f>IF(G139&lt;&gt;F139,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" s="5" t="n">
@@ -16528,7 +16392,6 @@
         <f>IF(G140&lt;&gt;F140,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" s="5" t="n">
@@ -16565,7 +16428,6 @@
         <f>IF(G141&lt;&gt;F141,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" s="5" t="n">
@@ -16602,7 +16464,6 @@
         <f>IF(G142&lt;&gt;F142,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" s="5" t="n">
@@ -16639,7 +16500,6 @@
         <f>IF(G143&lt;&gt;F143,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" s="5" t="n">
@@ -16676,7 +16536,6 @@
         <f>IF(G144&lt;&gt;F144,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" s="5" t="n">
@@ -16713,7 +16572,6 @@
         <f>IF(G145&lt;&gt;F145,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" s="5" t="n">
@@ -16750,7 +16608,6 @@
         <f>IF(G146&lt;&gt;F146,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" s="5" t="n">
@@ -16787,7 +16644,6 @@
         <f>IF(G147&lt;&gt;F147,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" s="5" t="n">
@@ -16824,7 +16680,6 @@
         <f>IF(G148&lt;&gt;F148,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" s="5" t="n">
@@ -16861,7 +16716,6 @@
         <f>IF(G149&lt;&gt;F149,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" s="5" t="n">
@@ -16898,7 +16752,6 @@
         <f>IF(G150&lt;&gt;F150,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" s="5" t="n">
@@ -16935,7 +16788,6 @@
         <f>IF(G151&lt;&gt;F151,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" s="5" t="n">
@@ -16972,7 +16824,6 @@
         <f>IF(G152&lt;&gt;F152,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" s="5" t="n">
@@ -17009,7 +16860,6 @@
         <f>IF(G153&lt;&gt;F153,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" s="5" t="n">
@@ -17046,7 +16896,6 @@
         <f>IF(G154&lt;&gt;F154,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" s="5" t="n">
@@ -17083,7 +16932,6 @@
         <f>IF(G155&lt;&gt;F155,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" s="5" t="n">
@@ -17120,7 +16968,6 @@
         <f>IF(G156&lt;&gt;F156,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" s="5" t="n">
@@ -17157,7 +17004,6 @@
         <f>IF(G157&lt;&gt;F157,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" s="5" t="n">
@@ -17194,7 +17040,6 @@
         <f>IF(G158&lt;&gt;F158,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" s="5" t="n">
@@ -17231,7 +17076,6 @@
         <f>IF(G159&lt;&gt;F159,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" s="5" t="n">
@@ -17268,7 +17112,6 @@
         <f>IF(G160&lt;&gt;F160,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" s="5" t="n">
@@ -17305,7 +17148,6 @@
         <f>IF(G161&lt;&gt;F161,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" s="5" t="n">
@@ -17342,7 +17184,6 @@
         <f>IF(G162&lt;&gt;F162,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" s="5" t="n">
@@ -17379,7 +17220,6 @@
         <f>IF(G163&lt;&gt;F163,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" s="5" t="n">
@@ -17416,7 +17256,6 @@
         <f>IF(G164&lt;&gt;F164,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" s="5" t="n">
@@ -17453,7 +17292,6 @@
         <f>IF(G165&lt;&gt;F165,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" s="5" t="n">
@@ -17490,7 +17328,6 @@
         <f>IF(G166&lt;&gt;F166,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" s="5" t="n">
@@ -17527,7 +17364,6 @@
         <f>IF(G167&lt;&gt;F167,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" s="5" t="n">
@@ -17564,7 +17400,6 @@
         <f>IF(G168&lt;&gt;F168,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" s="5" t="n">
@@ -17601,7 +17436,6 @@
         <f>IF(G169&lt;&gt;F169,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" s="5" t="n">
@@ -17638,7 +17472,6 @@
         <f>IF(G170&lt;&gt;F170,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" s="5" t="n">
@@ -17675,7 +17508,6 @@
         <f>IF(G171&lt;&gt;F171,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" s="5" t="n">
@@ -17712,7 +17544,6 @@
         <f>IF(G172&lt;&gt;F172,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" s="5" t="n">
@@ -17749,7 +17580,6 @@
         <f>IF(G173&lt;&gt;F173,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" s="5" t="n">
@@ -17786,7 +17616,6 @@
         <f>IF(G174&lt;&gt;F174,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" s="5" t="n">
@@ -17823,7 +17652,6 @@
         <f>IF(G175&lt;&gt;F175,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" s="5" t="n">
@@ -17860,7 +17688,6 @@
         <f>IF(G176&lt;&gt;F176,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" s="5" t="n">
@@ -17897,7 +17724,6 @@
         <f>IF(G177&lt;&gt;F177,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" s="5" t="n">
@@ -17934,7 +17760,6 @@
         <f>IF(G178&lt;&gt;F178,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" s="5" t="n">
@@ -17971,7 +17796,6 @@
         <f>IF(G179&lt;&gt;F179,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" s="5" t="n">
@@ -18008,7 +17832,6 @@
         <f>IF(G180&lt;&gt;F180,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" s="5" t="n">
@@ -18045,7 +17868,6 @@
         <f>IF(G181&lt;&gt;F181,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" s="5" t="n">
@@ -18082,7 +17904,6 @@
         <f>IF(G182&lt;&gt;F182,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" s="5" t="n">
@@ -18119,7 +17940,6 @@
         <f>IF(G183&lt;&gt;F183,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" s="5" t="n">
@@ -18156,7 +17976,6 @@
         <f>IF(G184&lt;&gt;F184,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" s="5" t="n">
@@ -18193,7 +18012,6 @@
         <f>IF(G185&lt;&gt;F185,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" s="5" t="n">
@@ -18230,7 +18048,6 @@
         <f>IF(G186&lt;&gt;F186,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" s="5" t="n">
@@ -18267,7 +18084,6 @@
         <f>IF(G187&lt;&gt;F187,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" s="5" t="n">
@@ -18304,7 +18120,6 @@
         <f>IF(G188&lt;&gt;F188,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" s="5" t="n">
@@ -18341,7 +18156,6 @@
         <f>IF(G189&lt;&gt;F189,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" s="5" t="n">
@@ -18378,7 +18192,6 @@
         <f>IF(G190&lt;&gt;F190,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" s="5" t="n">
@@ -18415,7 +18228,6 @@
         <f>IF(G191&lt;&gt;F191,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" s="5" t="n">
@@ -18452,7 +18264,6 @@
         <f>IF(G192&lt;&gt;F192,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" s="5" t="n">
@@ -18489,7 +18300,6 @@
         <f>IF(G193&lt;&gt;F193,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" s="5" t="n">
@@ -18526,7 +18336,6 @@
         <f>IF(G194&lt;&gt;F194,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" s="5" t="n">
@@ -18563,7 +18372,6 @@
         <f>IF(G195&lt;&gt;F195,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" s="5" t="n">
@@ -18600,7 +18408,6 @@
         <f>IF(G196&lt;&gt;F196,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" s="5" t="n">
@@ -18637,7 +18444,6 @@
         <f>IF(G197&lt;&gt;F197,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" s="5" t="n">
@@ -18674,7 +18480,6 @@
         <f>IF(G198&lt;&gt;F198,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" s="5" t="n">
@@ -18711,7 +18516,6 @@
         <f>IF(G199&lt;&gt;F199,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" s="5" t="n">
@@ -18748,7 +18552,6 @@
         <f>IF(G200&lt;&gt;F200,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" s="5" t="n">
@@ -18785,7 +18588,6 @@
         <f>IF(G201&lt;&gt;F201,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" s="5" t="n">
@@ -18822,7 +18624,6 @@
         <f>IF(G202&lt;&gt;F202,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" s="5" t="n">
@@ -18859,7 +18660,6 @@
         <f>IF(G203&lt;&gt;F203,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" s="5" t="n">
@@ -18896,7 +18696,6 @@
         <f>IF(G204&lt;&gt;F204,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" s="5" t="n">
@@ -18933,7 +18732,6 @@
         <f>IF(G205&lt;&gt;F205,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" s="5" t="n">
@@ -18970,7 +18768,6 @@
         <f>IF(G206&lt;&gt;F206,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" s="5" t="n">
@@ -19007,7 +18804,6 @@
         <f>IF(G207&lt;&gt;F207,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" s="5" t="n">
@@ -19044,7 +18840,6 @@
         <f>IF(G208&lt;&gt;F208,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" s="5" t="n">
@@ -19081,7 +18876,6 @@
         <f>IF(G209&lt;&gt;F209,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" s="5" t="n">
@@ -19118,7 +18912,6 @@
         <f>IF(G210&lt;&gt;F210,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" s="5" t="n">
@@ -19155,7 +18948,6 @@
         <f>IF(G211&lt;&gt;F211,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" s="5" t="n">
@@ -19192,7 +18984,6 @@
         <f>IF(G212&lt;&gt;F212,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" s="5" t="n">
@@ -19229,7 +19020,6 @@
         <f>IF(G213&lt;&gt;F213,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" s="5" t="n">
@@ -19266,7 +19056,6 @@
         <f>IF(G214&lt;&gt;F214,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" s="5" t="n">
@@ -19303,7 +19092,6 @@
         <f>IF(G215&lt;&gt;F215,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" s="5" t="n">
@@ -19340,7 +19128,6 @@
         <f>IF(G216&lt;&gt;F216,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I216" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" s="5" t="n">
@@ -19377,7 +19164,6 @@
         <f>IF(G217&lt;&gt;F217,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I217" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" s="5" t="n">
@@ -19414,7 +19200,6 @@
         <f>IF(G218&lt;&gt;F218,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" s="5" t="n">
@@ -19451,7 +19236,6 @@
         <f>IF(G219&lt;&gt;F219,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" s="5" t="n">
@@ -19488,7 +19272,6 @@
         <f>IF(G220&lt;&gt;F220,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I220" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" s="5" t="n">
@@ -19525,7 +19308,6 @@
         <f>IF(G221&lt;&gt;F221,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I221" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" s="5" t="n">
@@ -19562,7 +19344,6 @@
         <f>IF(G222&lt;&gt;F222,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" s="5" t="n">
@@ -19599,7 +19380,6 @@
         <f>IF(G223&lt;&gt;F223,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" s="5" t="n">
@@ -19636,7 +19416,6 @@
         <f>IF(G224&lt;&gt;F224,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I224" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" s="5" t="n">
@@ -19673,7 +19452,6 @@
         <f>IF(G225&lt;&gt;F225,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I225" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" s="5" t="n">
@@ -19710,7 +19488,6 @@
         <f>IF(G226&lt;&gt;F226,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I226" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" s="5" t="n">
@@ -19747,7 +19524,6 @@
         <f>IF(G227&lt;&gt;F227,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I227" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" s="5" t="n">
@@ -19784,7 +19560,6 @@
         <f>IF(G228&lt;&gt;F228,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I228" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" s="5" t="n">
@@ -19821,7 +19596,6 @@
         <f>IF(G229&lt;&gt;F229,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I229" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" s="5" t="n">
@@ -19858,7 +19632,6 @@
         <f>IF(G230&lt;&gt;F230,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I230" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" s="5" t="n">
@@ -19895,7 +19668,6 @@
         <f>IF(G231&lt;&gt;F231,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I231" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" s="5" t="n">
@@ -19932,7 +19704,6 @@
         <f>IF(G232&lt;&gt;F232,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I232" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" s="5" t="n">
@@ -19969,7 +19740,6 @@
         <f>IF(G233&lt;&gt;F233,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I233" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" s="5" t="n">
@@ -20006,7 +19776,6 @@
         <f>IF(G234&lt;&gt;F234,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I234" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" s="5" t="n">
@@ -20043,7 +19812,6 @@
         <f>IF(G235&lt;&gt;F235,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I235" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" s="5" t="n">
@@ -20080,7 +19848,6 @@
         <f>IF(G236&lt;&gt;F236,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I236" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" s="5" t="n">
@@ -20117,7 +19884,6 @@
         <f>IF(G237&lt;&gt;F237,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I237" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" s="5" t="n">
@@ -20154,7 +19920,6 @@
         <f>IF(G238&lt;&gt;F238,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I238" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" s="5" t="n">
@@ -20191,7 +19956,6 @@
         <f>IF(G239&lt;&gt;F239,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I239" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" s="5" t="n">
@@ -20228,7 +19992,6 @@
         <f>IF(G240&lt;&gt;F240,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I240" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" s="5" t="n">
@@ -20265,7 +20028,6 @@
         <f>IF(G241&lt;&gt;F241,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I241" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" s="5" t="n">
@@ -20302,7 +20064,6 @@
         <f>IF(G242&lt;&gt;F242,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I242" t="inlineStr"/>
     </row>
     <row r="243">
       <c r="A243" s="5" t="n">
@@ -20339,7 +20100,6 @@
         <f>IF(G243&lt;&gt;F243,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I243" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" s="5" t="n">
@@ -20376,7 +20136,6 @@
         <f>IF(G244&lt;&gt;F244,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I244" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="A245" s="5" t="n">
@@ -20413,7 +20172,6 @@
         <f>IF(G245&lt;&gt;F245,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I245" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" s="5" t="n">
@@ -20450,7 +20208,6 @@
         <f>IF(G246&lt;&gt;F246,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I246" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" s="5" t="n">
@@ -20487,7 +20244,6 @@
         <f>IF(G247&lt;&gt;F247,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I247" t="inlineStr"/>
     </row>
     <row r="248">
       <c r="A248" s="5" t="n">
@@ -20524,7 +20280,6 @@
         <f>IF(G248&lt;&gt;F248,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I248" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" s="5" t="n">
@@ -20561,7 +20316,6 @@
         <f>IF(G249&lt;&gt;F249,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I249" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" s="5" t="n">
@@ -20598,7 +20352,6 @@
         <f>IF(G250&lt;&gt;F250,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I250" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" s="5" t="n">
@@ -20635,7 +20388,6 @@
         <f>IF(G251&lt;&gt;F251,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I251" t="inlineStr"/>
     </row>
     <row r="252">
       <c r="A252" s="5" t="n">
@@ -20672,7 +20424,6 @@
         <f>IF(G252&lt;&gt;F252,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I252" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" s="5" t="n">
@@ -20709,7 +20460,6 @@
         <f>IF(G253&lt;&gt;F253,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I253" t="inlineStr"/>
     </row>
     <row r="254">
       <c r="A254" s="5" t="n">
@@ -20746,7 +20496,6 @@
         <f>IF(G254&lt;&gt;F254,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I254" t="inlineStr"/>
     </row>
     <row r="255">
       <c r="A255" s="5" t="n">
@@ -20783,7 +20532,6 @@
         <f>IF(G255&lt;&gt;F255,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I255" t="inlineStr"/>
     </row>
     <row r="256">
       <c r="A256" s="5" t="n">
@@ -20820,7 +20568,6 @@
         <f>IF(G256&lt;&gt;F256,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I256" t="inlineStr"/>
     </row>
     <row r="257">
       <c r="A257" s="5" t="n">
@@ -20857,7 +20604,6 @@
         <f>IF(G257&lt;&gt;F257,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I257" t="inlineStr"/>
     </row>
     <row r="258">
       <c r="A258" s="5" t="n">
@@ -20894,7 +20640,6 @@
         <f>IF(G258&lt;&gt;F258,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I258" t="inlineStr"/>
     </row>
     <row r="259">
       <c r="A259" s="5" t="n">
@@ -20931,7 +20676,6 @@
         <f>IF(G259&lt;&gt;F259,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I259" t="inlineStr"/>
     </row>
     <row r="260">
       <c r="A260" s="5" t="n">
@@ -20968,7 +20712,6 @@
         <f>IF(G260&lt;&gt;F260,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I260" t="inlineStr"/>
     </row>
     <row r="261">
       <c r="A261" s="5" t="n">
@@ -21005,7 +20748,6 @@
         <f>IF(G261&lt;&gt;F261,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I261" t="inlineStr"/>
     </row>
     <row r="262">
       <c r="A262" s="5" t="n">
@@ -21042,7 +20784,6 @@
         <f>IF(G262&lt;&gt;F262,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I262" t="inlineStr"/>
     </row>
     <row r="263">
       <c r="A263" s="5" t="n">
@@ -21079,7 +20820,6 @@
         <f>IF(G263&lt;&gt;F263,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I263" t="inlineStr"/>
     </row>
     <row r="264">
       <c r="A264" s="5" t="n">
@@ -21116,7 +20856,6 @@
         <f>IF(G264&lt;&gt;F264,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I264" t="inlineStr"/>
     </row>
     <row r="265">
       <c r="A265" s="5" t="n">
@@ -21153,7 +20892,6 @@
         <f>IF(G265&lt;&gt;F265,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I265" t="inlineStr"/>
     </row>
     <row r="266">
       <c r="A266" s="5" t="n">
@@ -21190,7 +20928,6 @@
         <f>IF(G266&lt;&gt;F266,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I266" t="inlineStr"/>
     </row>
     <row r="267">
       <c r="A267" s="5" t="n">
@@ -21227,7 +20964,6 @@
         <f>IF(G267&lt;&gt;F267,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I267" t="inlineStr"/>
     </row>
     <row r="268">
       <c r="A268" s="5" t="n">
@@ -21264,7 +21000,6 @@
         <f>IF(G268&lt;&gt;F268,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I268" t="inlineStr"/>
     </row>
     <row r="269">
       <c r="A269" s="5" t="n">
@@ -21301,7 +21036,6 @@
         <f>IF(G269&lt;&gt;F269,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I269" t="inlineStr"/>
     </row>
     <row r="270">
       <c r="A270" s="5" t="n">
@@ -21338,7 +21072,6 @@
         <f>IF(G270&lt;&gt;F270,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I270" t="inlineStr"/>
     </row>
     <row r="271">
       <c r="A271" s="5" t="n">
@@ -21375,7 +21108,6 @@
         <f>IF(G271&lt;&gt;F271,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I271" t="inlineStr"/>
     </row>
     <row r="272">
       <c r="A272" s="5" t="n">
@@ -21412,7 +21144,6 @@
         <f>IF(G272&lt;&gt;F272,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I272" t="inlineStr"/>
     </row>
     <row r="273">
       <c r="A273" s="5" t="n">
@@ -21449,7 +21180,6 @@
         <f>IF(G273&lt;&gt;F273,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I273" t="inlineStr"/>
     </row>
     <row r="274">
       <c r="A274" s="5" t="n">
@@ -21486,7 +21216,6 @@
         <f>IF(G274&lt;&gt;F274,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I274" t="inlineStr"/>
     </row>
     <row r="275">
       <c r="A275" s="5" t="n">
@@ -21523,7 +21252,6 @@
         <f>IF(G275&lt;&gt;F275,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I275" t="inlineStr"/>
     </row>
     <row r="276">
       <c r="A276" s="5" t="n">
@@ -21560,7 +21288,6 @@
         <f>IF(G276&lt;&gt;F276,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I276" t="inlineStr"/>
     </row>
     <row r="277">
       <c r="A277" s="5" t="n">
@@ -21597,7 +21324,6 @@
         <f>IF(G277&lt;&gt;F277,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I277" t="inlineStr"/>
     </row>
     <row r="278">
       <c r="A278" s="5" t="n">
@@ -21634,7 +21360,6 @@
         <f>IF(G278&lt;&gt;F278,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I278" t="inlineStr"/>
     </row>
     <row r="279">
       <c r="A279" s="5" t="n">
@@ -21671,7 +21396,6 @@
         <f>IF(G279&lt;&gt;F279,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I279" t="inlineStr"/>
     </row>
     <row r="280">
       <c r="A280" s="5" t="n">
@@ -21708,7 +21432,6 @@
         <f>IF(G280&lt;&gt;F280,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I280" t="inlineStr"/>
     </row>
     <row r="281">
       <c r="A281" s="5" t="n">
@@ -21745,7 +21468,6 @@
         <f>IF(G281&lt;&gt;F281,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I281" t="inlineStr"/>
     </row>
     <row r="282">
       <c r="A282" s="5" t="n">
@@ -21782,7 +21504,6 @@
         <f>IF(G282&lt;&gt;F282,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I282" t="inlineStr"/>
     </row>
     <row r="283">
       <c r="A283" s="5" t="n">
@@ -21819,7 +21540,6 @@
         <f>IF(G283&lt;&gt;F283,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I283" t="inlineStr"/>
     </row>
     <row r="284">
       <c r="A284" s="5" t="n">
@@ -21856,7 +21576,6 @@
         <f>IF(G284&lt;&gt;F284,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I284" t="inlineStr"/>
     </row>
     <row r="285">
       <c r="A285" s="5" t="n">
@@ -21893,7 +21612,6 @@
         <f>IF(G285&lt;&gt;F285,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I285" t="inlineStr"/>
     </row>
     <row r="286">
       <c r="A286" s="5" t="n">
@@ -21930,7 +21648,6 @@
         <f>IF(G286&lt;&gt;F286,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I286" t="inlineStr"/>
     </row>
     <row r="287">
       <c r="A287" s="5" t="n">
@@ -21967,7 +21684,6 @@
         <f>IF(G287&lt;&gt;F287,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I287" t="inlineStr"/>
     </row>
     <row r="288">
       <c r="A288" s="5" t="n">
@@ -22004,7 +21720,6 @@
         <f>IF(G288&lt;&gt;F288,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I288" t="inlineStr"/>
     </row>
     <row r="289">
       <c r="A289" s="5" t="n">
@@ -22041,7 +21756,6 @@
         <f>IF(G289&lt;&gt;F289,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I289" t="inlineStr"/>
     </row>
     <row r="290">
       <c r="A290" s="5" t="n">
@@ -22078,7 +21792,6 @@
         <f>IF(G290&lt;&gt;F290,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I290" t="inlineStr"/>
     </row>
     <row r="291">
       <c r="A291" s="5" t="n">
@@ -22115,7 +21828,6 @@
         <f>IF(G291&lt;&gt;F291,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I291" t="inlineStr"/>
     </row>
     <row r="292">
       <c r="A292" s="5" t="n">
@@ -22152,7 +21864,6 @@
         <f>IF(G292&lt;&gt;F292,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I292" t="inlineStr"/>
     </row>
     <row r="293">
       <c r="A293" s="5" t="n">
@@ -22189,7 +21900,6 @@
         <f>IF(G293&lt;&gt;F293,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I293" t="inlineStr"/>
     </row>
     <row r="294">
       <c r="A294" s="5" t="n">
@@ -22226,7 +21936,6 @@
         <f>IF(G294&lt;&gt;F294,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I294" t="inlineStr"/>
     </row>
     <row r="295">
       <c r="A295" s="5" t="n">
@@ -22263,7 +21972,6 @@
         <f>IF(G295&lt;&gt;F295,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I295" t="inlineStr"/>
     </row>
     <row r="296">
       <c r="A296" s="5" t="n">
@@ -22300,7 +22008,6 @@
         <f>IF(G296&lt;&gt;F296,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I296" t="inlineStr"/>
     </row>
     <row r="297">
       <c r="A297" s="5" t="n">
@@ -22337,7 +22044,6 @@
         <f>IF(G297&lt;&gt;F297,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I297" t="inlineStr"/>
     </row>
     <row r="298">
       <c r="A298" s="5" t="n">
@@ -22374,7 +22080,6 @@
         <f>IF(G298&lt;&gt;F298,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I298" t="inlineStr"/>
     </row>
     <row r="299">
       <c r="A299" s="5" t="n">
@@ -22411,7 +22116,6 @@
         <f>IF(G299&lt;&gt;F299,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I299" t="inlineStr"/>
     </row>
     <row r="300">
       <c r="A300" s="5" t="n">
@@ -22448,7 +22152,6 @@
         <f>IF(G300&lt;&gt;F300,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I300" t="inlineStr"/>
     </row>
     <row r="301">
       <c r="A301" s="5" t="n">
@@ -22485,7 +22188,6 @@
         <f>IF(G301&lt;&gt;F301,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I301" t="inlineStr"/>
     </row>
     <row r="302">
       <c r="A302" s="5" t="n">
@@ -22522,7 +22224,6 @@
         <f>IF(G302&lt;&gt;F302,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I302" t="inlineStr"/>
     </row>
     <row r="303">
       <c r="A303" s="5" t="n">
@@ -22559,7 +22260,6 @@
         <f>IF(G303&lt;&gt;F303,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I303" t="inlineStr"/>
     </row>
     <row r="304">
       <c r="A304" s="5" t="n">
@@ -22596,7 +22296,6 @@
         <f>IF(G304&lt;&gt;F304,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I304" t="inlineStr"/>
     </row>
     <row r="305">
       <c r="A305" s="5" t="n">
@@ -22633,7 +22332,6 @@
         <f>IF(G305&lt;&gt;F305,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I305" t="inlineStr"/>
     </row>
     <row r="306">
       <c r="A306" s="5" t="n">
@@ -22670,7 +22368,6 @@
         <f>IF(G306&lt;&gt;F306,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I306" t="inlineStr"/>
     </row>
     <row r="307">
       <c r="A307" s="5" t="n">
@@ -22707,7 +22404,6 @@
         <f>IF(G307&lt;&gt;F307,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I307" t="inlineStr"/>
     </row>
     <row r="308">
       <c r="A308" s="5" t="n">
@@ -22744,7 +22440,6 @@
         <f>IF(G308&lt;&gt;F308,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I308" t="inlineStr"/>
     </row>
     <row r="309">
       <c r="A309" s="5" t="n">
@@ -22781,7 +22476,6 @@
         <f>IF(G309&lt;&gt;F309,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I309" t="inlineStr"/>
     </row>
     <row r="310">
       <c r="A310" s="5" t="n">
@@ -22818,7 +22512,6 @@
         <f>IF(G310&lt;&gt;F310,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I310" t="inlineStr"/>
     </row>
     <row r="311">
       <c r="A311" s="5" t="n">
@@ -22855,7 +22548,6 @@
         <f>IF(G311&lt;&gt;F311,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I311" t="inlineStr"/>
     </row>
     <row r="312">
       <c r="A312" s="5" t="n">
@@ -22892,7 +22584,6 @@
         <f>IF(G312&lt;&gt;F312,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I312" t="inlineStr"/>
     </row>
     <row r="313">
       <c r="A313" s="5" t="n">
@@ -22929,7 +22620,6 @@
         <f>IF(G313&lt;&gt;F313,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I313" t="inlineStr"/>
     </row>
     <row r="314">
       <c r="A314" s="5" t="n">
@@ -22966,7 +22656,6 @@
         <f>IF(G314&lt;&gt;F314,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I314" t="inlineStr"/>
     </row>
     <row r="315">
       <c r="A315" s="5" t="n">
@@ -23003,7 +22692,6 @@
         <f>IF(G315&lt;&gt;F315,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I315" t="inlineStr"/>
     </row>
     <row r="316">
       <c r="A316" s="5" t="n">
@@ -23040,7 +22728,6 @@
         <f>IF(G316&lt;&gt;F316,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I316" t="inlineStr"/>
     </row>
     <row r="317">
       <c r="A317" s="5" t="n">
@@ -23077,7 +22764,6 @@
         <f>IF(G317&lt;&gt;F317,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I317" t="inlineStr"/>
     </row>
     <row r="318">
       <c r="A318" s="5" t="n">
@@ -23114,7 +22800,6 @@
         <f>IF(G318&lt;&gt;F318,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I318" t="inlineStr"/>
     </row>
     <row r="319">
       <c r="A319" s="5" t="n">
@@ -23151,7 +22836,6 @@
         <f>IF(G319&lt;&gt;F319,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I319" t="inlineStr"/>
     </row>
     <row r="320">
       <c r="A320" s="5" t="n">
@@ -23188,7 +22872,6 @@
         <f>IF(G320&lt;&gt;F320,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I320" t="inlineStr"/>
     </row>
     <row r="321">
       <c r="A321" s="5" t="n">
@@ -23225,7 +22908,6 @@
         <f>IF(G321&lt;&gt;F321,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I321" t="inlineStr"/>
     </row>
     <row r="322">
       <c r="A322" s="5" t="n">
@@ -23262,7 +22944,6 @@
         <f>IF(G322&lt;&gt;F322,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I322" t="inlineStr"/>
     </row>
     <row r="323">
       <c r="A323" s="5" t="n">
@@ -23299,7 +22980,6 @@
         <f>IF(G323&lt;&gt;F323,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I323" t="inlineStr"/>
     </row>
     <row r="324">
       <c r="A324" s="5" t="n">
@@ -23336,7 +23016,6 @@
         <f>IF(G324&lt;&gt;F324,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I324" t="inlineStr"/>
     </row>
     <row r="325">
       <c r="A325" s="5" t="n">
@@ -23373,7 +23052,6 @@
         <f>IF(G325&lt;&gt;F325,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I325" t="inlineStr"/>
     </row>
     <row r="326">
       <c r="A326" s="5" t="n">
@@ -23410,7 +23088,6 @@
         <f>IF(G326&lt;&gt;F326,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I326" t="inlineStr"/>
     </row>
     <row r="327">
       <c r="A327" s="5" t="n">
@@ -23447,7 +23124,6 @@
         <f>IF(G327&lt;&gt;F327,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I327" t="inlineStr"/>
     </row>
     <row r="328">
       <c r="A328" s="5" t="n">
@@ -23484,7 +23160,6 @@
         <f>IF(G328&lt;&gt;F328,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I328" t="inlineStr"/>
     </row>
     <row r="329">
       <c r="A329" s="5" t="n">
@@ -23521,7 +23196,6 @@
         <f>IF(G329&lt;&gt;F329,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I329" t="inlineStr"/>
     </row>
     <row r="330">
       <c r="A330" s="5" t="n">
@@ -23558,7 +23232,6 @@
         <f>IF(G330&lt;&gt;F330,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I330" t="inlineStr"/>
     </row>
     <row r="331">
       <c r="A331" s="5" t="n">
@@ -23595,7 +23268,6 @@
         <f>IF(G331&lt;&gt;F331,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I331" t="inlineStr"/>
     </row>
     <row r="332">
       <c r="A332" s="5" t="n">
@@ -23632,7 +23304,6 @@
         <f>IF(G332&lt;&gt;F332,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I332" t="inlineStr"/>
     </row>
     <row r="333">
       <c r="A333" s="5" t="n">
@@ -23669,7 +23340,6 @@
         <f>IF(G333&lt;&gt;F333,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I333" t="inlineStr"/>
     </row>
     <row r="334">
       <c r="A334" s="5" t="n">
@@ -23706,7 +23376,6 @@
         <f>IF(G334&lt;&gt;F334,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I334" t="inlineStr"/>
     </row>
     <row r="335">
       <c r="A335" s="5" t="n">
@@ -23743,7 +23412,6 @@
         <f>IF(G335&lt;&gt;F335,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I335" t="inlineStr"/>
     </row>
     <row r="336">
       <c r="A336" s="5" t="n">
@@ -23780,7 +23448,6 @@
         <f>IF(G336&lt;&gt;F336,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I336" t="inlineStr"/>
     </row>
     <row r="337">
       <c r="A337" s="5" t="n">
@@ -23817,7 +23484,6 @@
         <f>IF(G337&lt;&gt;F337,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I337" t="inlineStr"/>
     </row>
     <row r="338">
       <c r="A338" s="5" t="n">
@@ -23854,7 +23520,6 @@
         <f>IF(G338&lt;&gt;F338,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I338" t="inlineStr"/>
     </row>
     <row r="339">
       <c r="A339" s="5" t="n">
@@ -23891,7 +23556,6 @@
         <f>IF(G339&lt;&gt;F339,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I339" t="inlineStr"/>
     </row>
     <row r="340">
       <c r="A340" s="5" t="n">
@@ -23928,7 +23592,6 @@
         <f>IF(G340&lt;&gt;F340,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I340" t="inlineStr"/>
     </row>
     <row r="341">
       <c r="A341" s="5" t="n">
@@ -23965,7 +23628,6 @@
         <f>IF(G341&lt;&gt;F341,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I341" t="inlineStr"/>
     </row>
     <row r="342">
       <c r="A342" s="5" t="n">
@@ -24002,7 +23664,6 @@
         <f>IF(G342&lt;&gt;F342,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I342" t="inlineStr"/>
     </row>
     <row r="343">
       <c r="A343" s="5" t="n">
@@ -24039,7 +23700,6 @@
         <f>IF(G343&lt;&gt;F343,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I343" t="inlineStr"/>
     </row>
     <row r="344">
       <c r="A344" s="5" t="n">
@@ -24076,7 +23736,6 @@
         <f>IF(G344&lt;&gt;F344,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I344" t="inlineStr"/>
     </row>
     <row r="345">
       <c r="A345" s="5" t="n">
@@ -24113,7 +23772,6 @@
         <f>IF(G345&lt;&gt;F345,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I345" t="inlineStr"/>
     </row>
     <row r="346">
       <c r="A346" s="5" t="n">
@@ -24150,7 +23808,6 @@
         <f>IF(G346&lt;&gt;F346,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I346" t="inlineStr"/>
     </row>
     <row r="347">
       <c r="A347" s="5" t="n">
@@ -24187,7 +23844,6 @@
         <f>IF(G347&lt;&gt;F347,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I347" t="inlineStr"/>
     </row>
     <row r="348">
       <c r="A348" s="5" t="n">
@@ -24224,7 +23880,6 @@
         <f>IF(G348&lt;&gt;F348,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I348" t="inlineStr"/>
     </row>
     <row r="349">
       <c r="A349" s="5" t="n">
@@ -24261,7 +23916,6 @@
         <f>IF(G349&lt;&gt;F349,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I349" t="inlineStr"/>
     </row>
     <row r="350">
       <c r="A350" s="5" t="n">
@@ -24298,7 +23952,6 @@
         <f>IF(G350&lt;&gt;F350,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I350" t="inlineStr"/>
     </row>
     <row r="351">
       <c r="A351" s="5" t="n">
@@ -24335,7 +23988,6 @@
         <f>IF(G351&lt;&gt;F351,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I351" t="inlineStr"/>
     </row>
     <row r="352">
       <c r="A352" s="5" t="n">
@@ -24372,7 +24024,6 @@
         <f>IF(G352&lt;&gt;F352,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I352" t="inlineStr"/>
     </row>
     <row r="353">
       <c r="A353" s="5" t="n">
@@ -24409,7 +24060,6 @@
         <f>IF(G353&lt;&gt;F353,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I353" t="inlineStr"/>
     </row>
     <row r="354">
       <c r="A354" s="5" t="n">
@@ -24446,7 +24096,6 @@
         <f>IF(G354&lt;&gt;F354,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I354" t="inlineStr"/>
     </row>
     <row r="355">
       <c r="A355" s="5" t="n">
@@ -24483,7 +24132,6 @@
         <f>IF(G355&lt;&gt;F355,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I355" t="inlineStr"/>
     </row>
     <row r="356">
       <c r="A356" s="5" t="n">
@@ -24520,7 +24168,6 @@
         <f>IF(G356&lt;&gt;F356,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I356" t="inlineStr"/>
     </row>
     <row r="357">
       <c r="A357" s="5" t="n">
@@ -24557,7 +24204,6 @@
         <f>IF(G357&lt;&gt;F357,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I357" t="inlineStr"/>
     </row>
     <row r="358">
       <c r="A358" s="5" t="n">
@@ -24594,7 +24240,6 @@
         <f>IF(G358&lt;&gt;F358,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I358" t="inlineStr"/>
     </row>
     <row r="359">
       <c r="A359" s="5" t="n">
@@ -24631,7 +24276,6 @@
         <f>IF(G359&lt;&gt;F359,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I359" t="inlineStr"/>
     </row>
     <row r="360">
       <c r="A360" s="5" t="n">
@@ -24668,7 +24312,6 @@
         <f>IF(G360&lt;&gt;F360,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I360" t="inlineStr"/>
     </row>
     <row r="361">
       <c r="A361" s="5" t="n">
@@ -24705,7 +24348,6 @@
         <f>IF(G361&lt;&gt;F361,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I361" t="inlineStr"/>
     </row>
     <row r="362">
       <c r="A362" s="5" t="n">
@@ -24742,7 +24384,6 @@
         <f>IF(G362&lt;&gt;F362,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I362" t="inlineStr"/>
     </row>
     <row r="363">
       <c r="A363" s="5" t="n">
@@ -24779,7 +24420,6 @@
         <f>IF(G363&lt;&gt;F363,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I363" t="inlineStr"/>
     </row>
     <row r="364">
       <c r="A364" s="5" t="n">
@@ -24816,7 +24456,6 @@
         <f>IF(G364&lt;&gt;F364,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I364" t="inlineStr"/>
     </row>
     <row r="365">
       <c r="A365" s="5" t="n">
@@ -24853,7 +24492,6 @@
         <f>IF(G365&lt;&gt;F365,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I365" t="inlineStr"/>
     </row>
     <row r="366">
       <c r="A366" s="5" t="n">
@@ -24890,7 +24528,6 @@
         <f>IF(G366&lt;&gt;F366,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I366" t="inlineStr"/>
     </row>
     <row r="367">
       <c r="A367" s="5" t="n">
@@ -24927,7 +24564,6 @@
         <f>IF(G367&lt;&gt;F367,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I367" t="inlineStr"/>
     </row>
     <row r="368">
       <c r="A368" s="5" t="n">
@@ -24964,7 +24600,6 @@
         <f>IF(G368&lt;&gt;F368,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I368" t="inlineStr"/>
     </row>
     <row r="369">
       <c r="A369" s="5" t="n">
@@ -25001,7 +24636,6 @@
         <f>IF(G369&lt;&gt;F369,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I369" t="inlineStr"/>
     </row>
     <row r="370">
       <c r="A370" s="5" t="n">
@@ -25038,7 +24672,6 @@
         <f>IF(G370&lt;&gt;F370,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I370" t="inlineStr"/>
     </row>
     <row r="371">
       <c r="A371" s="5" t="n">
@@ -25075,7 +24708,6 @@
         <f>IF(G371&lt;&gt;F371,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I371" t="inlineStr"/>
     </row>
     <row r="372">
       <c r="A372" s="5" t="n">
@@ -25112,7 +24744,6 @@
         <f>IF(G372&lt;&gt;F372,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I372" t="inlineStr"/>
     </row>
     <row r="373">
       <c r="A373" s="5" t="n">
@@ -25149,7 +24780,6 @@
         <f>IF(G373&lt;&gt;F373,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I373" t="inlineStr"/>
     </row>
     <row r="374">
       <c r="A374" s="5" t="n">
@@ -25186,7 +24816,6 @@
         <f>IF(G374&lt;&gt;F374,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I374" t="inlineStr"/>
     </row>
     <row r="375">
       <c r="A375" s="5" t="n">
@@ -25223,7 +24852,6 @@
         <f>IF(G375&lt;&gt;F375,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I375" t="inlineStr"/>
     </row>
     <row r="376">
       <c r="A376" s="5" t="n">
@@ -25260,7 +24888,6 @@
         <f>IF(G376&lt;&gt;F376,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I376" t="inlineStr"/>
     </row>
     <row r="377">
       <c r="A377" s="5" t="n">
@@ -25297,7 +24924,6 @@
         <f>IF(G377&lt;&gt;F377,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I377" t="inlineStr"/>
     </row>
     <row r="378">
       <c r="A378" s="5" t="n">
@@ -25334,7 +24960,6 @@
         <f>IF(G378&lt;&gt;F378,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I378" t="inlineStr"/>
     </row>
     <row r="379">
       <c r="A379" s="5" t="n">
@@ -25371,7 +24996,6 @@
         <f>IF(G379&lt;&gt;F379,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I379" t="inlineStr"/>
     </row>
     <row r="380">
       <c r="A380" s="5" t="n">
@@ -25408,7 +25032,6 @@
         <f>IF(G380&lt;&gt;F380,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I380" t="inlineStr"/>
     </row>
     <row r="381">
       <c r="A381" s="5" t="n">
@@ -25445,7 +25068,6 @@
         <f>IF(G381&lt;&gt;F381,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I381" t="inlineStr"/>
     </row>
     <row r="382">
       <c r="A382" s="5" t="n">
@@ -25482,7 +25104,6 @@
         <f>IF(G382&lt;&gt;F382,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I382" t="inlineStr"/>
     </row>
     <row r="383">
       <c r="A383" s="5" t="n">
@@ -25519,7 +25140,6 @@
         <f>IF(G383&lt;&gt;F383,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I383" t="inlineStr"/>
     </row>
     <row r="384">
       <c r="A384" s="5" t="n">
@@ -25556,7 +25176,6 @@
         <f>IF(G384&lt;&gt;F384,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I384" t="inlineStr"/>
     </row>
     <row r="385">
       <c r="A385" s="5" t="n">
@@ -25593,7 +25212,6 @@
         <f>IF(G385&lt;&gt;F385,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I385" t="inlineStr"/>
     </row>
     <row r="386">
       <c r="A386" s="5" t="n">
@@ -25630,7 +25248,6 @@
         <f>IF(G386&lt;&gt;F386,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I386" t="inlineStr"/>
     </row>
     <row r="387">
       <c r="A387" s="5" t="n">
@@ -25667,7 +25284,6 @@
         <f>IF(G387&lt;&gt;F387,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I387" t="inlineStr"/>
     </row>
     <row r="388">
       <c r="A388" s="5" t="n">
@@ -25704,7 +25320,6 @@
         <f>IF(G388&lt;&gt;F388,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I388" t="inlineStr"/>
     </row>
     <row r="389">
       <c r="A389" s="5" t="n">
@@ -25741,7 +25356,6 @@
         <f>IF(G389&lt;&gt;F389,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I389" t="inlineStr"/>
     </row>
     <row r="390">
       <c r="A390" s="5" t="n">
@@ -25778,7 +25392,6 @@
         <f>IF(G390&lt;&gt;F390,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I390" t="inlineStr"/>
     </row>
     <row r="391">
       <c r="A391" s="5" t="n">
@@ -25815,7 +25428,6 @@
         <f>IF(G391&lt;&gt;F391,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I391" t="inlineStr"/>
     </row>
     <row r="392">
       <c r="A392" s="5" t="n">
@@ -25852,7 +25464,6 @@
         <f>IF(G392&lt;&gt;F392,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I392" t="inlineStr"/>
     </row>
     <row r="393">
       <c r="A393" s="5" t="n">
@@ -25889,7 +25500,6 @@
         <f>IF(G393&lt;&gt;F393,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I393" t="inlineStr"/>
     </row>
     <row r="394">
       <c r="A394" s="5" t="n">
@@ -25926,7 +25536,6 @@
         <f>IF(G394&lt;&gt;F394,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I394" t="inlineStr"/>
     </row>
     <row r="395">
       <c r="A395" s="5" t="n">
@@ -25963,7 +25572,6 @@
         <f>IF(G395&lt;&gt;F395,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I395" t="inlineStr"/>
     </row>
     <row r="396">
       <c r="A396" s="5" t="n">
@@ -26000,7 +25608,6 @@
         <f>IF(G396&lt;&gt;F396,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I396" t="inlineStr"/>
     </row>
     <row r="397">
       <c r="A397" s="5" t="n">
@@ -26037,7 +25644,6 @@
         <f>IF(G397&lt;&gt;F397,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I397" t="inlineStr"/>
     </row>
     <row r="398">
       <c r="A398" s="5" t="n">
@@ -26074,7 +25680,6 @@
         <f>IF(G398&lt;&gt;F398,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I398" t="inlineStr"/>
     </row>
     <row r="399">
       <c r="A399" s="5" t="n">
@@ -26111,7 +25716,6 @@
         <f>IF(G399&lt;&gt;F399,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I399" t="inlineStr"/>
     </row>
     <row r="400">
       <c r="A400" s="5" t="n">
@@ -26148,7 +25752,6 @@
         <f>IF(G400&lt;&gt;F400,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I400" t="inlineStr"/>
     </row>
     <row r="401">
       <c r="A401" s="5" t="n">
@@ -26185,7 +25788,6 @@
         <f>IF(G401&lt;&gt;F401,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I401" t="inlineStr"/>
     </row>
     <row r="402">
       <c r="A402" s="5" t="n">
@@ -26222,7 +25824,6 @@
         <f>IF(G402&lt;&gt;F402,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I402" t="inlineStr"/>
     </row>
     <row r="403">
       <c r="A403" s="5" t="n">
@@ -26259,7 +25860,6 @@
         <f>IF(G403&lt;&gt;F403,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I403" t="inlineStr"/>
     </row>
     <row r="404">
       <c r="A404" s="5" t="n">
@@ -26296,7 +25896,6 @@
         <f>IF(G404&lt;&gt;F404,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I404" t="inlineStr"/>
     </row>
     <row r="405">
       <c r="A405" s="5" t="n">
@@ -26333,7 +25932,6 @@
         <f>IF(G405&lt;&gt;F405,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I405" t="inlineStr"/>
     </row>
     <row r="406">
       <c r="A406" s="5" t="n">
@@ -26370,7 +25968,6 @@
         <f>IF(G406&lt;&gt;F406,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I406" t="inlineStr"/>
     </row>
     <row r="407">
       <c r="A407" s="5" t="n">
@@ -26407,7 +26004,6 @@
         <f>IF(G407&lt;&gt;F407,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I407" t="inlineStr"/>
     </row>
     <row r="408">
       <c r="A408" s="5" t="n">
@@ -26444,7 +26040,6 @@
         <f>IF(G408&lt;&gt;F408,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I408" t="inlineStr"/>
     </row>
     <row r="409">
       <c r="A409" s="5" t="n">
@@ -26481,7 +26076,6 @@
         <f>IF(G409&lt;&gt;F409,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I409" t="inlineStr"/>
     </row>
     <row r="410">
       <c r="A410" s="5" t="n">
@@ -26518,7 +26112,6 @@
         <f>IF(G410&lt;&gt;F410,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I410" t="inlineStr"/>
     </row>
     <row r="411">
       <c r="A411" s="5" t="n">
@@ -26555,7 +26148,6 @@
         <f>IF(G411&lt;&gt;F411,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I411" t="inlineStr"/>
     </row>
     <row r="412">
       <c r="A412" s="5" t="n">
@@ -26592,7 +26184,6 @@
         <f>IF(G412&lt;&gt;F412,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I412" t="inlineStr"/>
     </row>
     <row r="413">
       <c r="A413" s="5" t="n">
@@ -26629,7 +26220,6 @@
         <f>IF(G413&lt;&gt;F413,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I413" t="inlineStr"/>
     </row>
     <row r="414">
       <c r="A414" s="5" t="n">
@@ -26666,7 +26256,6 @@
         <f>IF(G414&lt;&gt;F414,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I414" t="inlineStr"/>
     </row>
     <row r="415">
       <c r="A415" s="5" t="n">
@@ -26703,7 +26292,6 @@
         <f>IF(G415&lt;&gt;F415,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I415" t="inlineStr"/>
     </row>
     <row r="416">
       <c r="A416" s="5" t="n">
@@ -26740,7 +26328,6 @@
         <f>IF(G416&lt;&gt;F416,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I416" t="inlineStr"/>
     </row>
     <row r="417">
       <c r="A417" s="5" t="n">
@@ -26777,7 +26364,6 @@
         <f>IF(G417&lt;&gt;F417,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I417" t="inlineStr"/>
     </row>
     <row r="418">
       <c r="A418" s="5" t="n">
@@ -26814,7 +26400,6 @@
         <f>IF(G418&lt;&gt;F418,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I418" t="inlineStr"/>
     </row>
     <row r="419">
       <c r="A419" s="5" t="n">
@@ -26851,7 +26436,6 @@
         <f>IF(G419&lt;&gt;F419,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I419" t="inlineStr"/>
     </row>
     <row r="420">
       <c r="A420" s="5" t="n">
@@ -26888,7 +26472,6 @@
         <f>IF(G420&lt;&gt;F420,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I420" t="inlineStr"/>
     </row>
     <row r="421">
       <c r="A421" s="5" t="n">
@@ -26925,7 +26508,6 @@
         <f>IF(G421&lt;&gt;F421,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I421" t="inlineStr"/>
     </row>
     <row r="422">
       <c r="A422" s="5" t="n">
@@ -26962,7 +26544,6 @@
         <f>IF(G422&lt;&gt;F422,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I422" t="inlineStr"/>
     </row>
     <row r="423">
       <c r="A423" s="5" t="n">
@@ -26999,7 +26580,6 @@
         <f>IF(G423&lt;&gt;F423,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I423" t="inlineStr"/>
     </row>
     <row r="424">
       <c r="A424" s="5" t="n">
@@ -27036,7 +26616,6 @@
         <f>IF(G424&lt;&gt;F424,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I424" t="inlineStr"/>
     </row>
     <row r="425">
       <c r="A425" s="5" t="n">
@@ -27073,7 +26652,6 @@
         <f>IF(G425&lt;&gt;F425,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I425" t="inlineStr"/>
     </row>
     <row r="426">
       <c r="A426" s="5" t="n">
@@ -27110,7 +26688,6 @@
         <f>IF(G426&lt;&gt;F426,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I426" t="inlineStr"/>
     </row>
     <row r="427">
       <c r="A427" s="5" t="n">
@@ -27147,7 +26724,6 @@
         <f>IF(G427&lt;&gt;F427,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I427" t="inlineStr"/>
     </row>
     <row r="428">
       <c r="A428" s="5" t="n">
@@ -27184,7 +26760,6 @@
         <f>IF(G428&lt;&gt;F428,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I428" t="inlineStr"/>
     </row>
     <row r="429">
       <c r="A429" s="5" t="n">
@@ -27221,7 +26796,6 @@
         <f>IF(G429&lt;&gt;F429,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I429" t="inlineStr"/>
     </row>
     <row r="430">
       <c r="A430" s="5" t="n">
@@ -27258,7 +26832,6 @@
         <f>IF(G430&lt;&gt;F430,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I430" t="inlineStr"/>
     </row>
     <row r="431">
       <c r="A431" s="5" t="n">
@@ -27295,7 +26868,6 @@
         <f>IF(G431&lt;&gt;F431,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I431" t="inlineStr"/>
     </row>
     <row r="432">
       <c r="A432" s="5" t="n">
@@ -27332,7 +26904,6 @@
         <f>IF(G432&lt;&gt;F432,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I432" t="inlineStr"/>
     </row>
     <row r="433">
       <c r="A433" s="5" t="n">
@@ -27369,7 +26940,6 @@
         <f>IF(G433&lt;&gt;F433,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I433" t="inlineStr"/>
     </row>
     <row r="434">
       <c r="A434" s="5" t="n">
@@ -27406,7 +26976,6 @@
         <f>IF(G434&lt;&gt;F434,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I434" t="inlineStr"/>
     </row>
     <row r="435">
       <c r="A435" s="5" t="n">
@@ -27443,7 +27012,6 @@
         <f>IF(G435&lt;&gt;F435,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I435" t="inlineStr"/>
     </row>
     <row r="436">
       <c r="A436" s="5" t="n">
@@ -27480,7 +27048,6 @@
         <f>IF(G436&lt;&gt;F436,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I436" t="inlineStr"/>
     </row>
     <row r="437">
       <c r="A437" s="5" t="n">
@@ -27517,7 +27084,6 @@
         <f>IF(G437&lt;&gt;F437,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I437" t="inlineStr"/>
     </row>
     <row r="438">
       <c r="A438" s="5" t="n">
@@ -27554,7 +27120,6 @@
         <f>IF(G438&lt;&gt;F438,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I438" t="inlineStr"/>
     </row>
     <row r="439">
       <c r="A439" s="5" t="n">
@@ -27591,7 +27156,6 @@
         <f>IF(G439&lt;&gt;F439,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I439" t="inlineStr"/>
     </row>
     <row r="440">
       <c r="A440" s="5" t="n">
@@ -27628,7 +27192,6 @@
         <f>IF(G440&lt;&gt;F440,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I440" t="inlineStr"/>
     </row>
     <row r="441">
       <c r="A441" s="5" t="n">
@@ -27665,7 +27228,6 @@
         <f>IF(G441&lt;&gt;F441,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I441" t="inlineStr"/>
     </row>
     <row r="442">
       <c r="A442" s="5" t="n">
@@ -27702,7 +27264,6 @@
         <f>IF(G442&lt;&gt;F442,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I442" t="inlineStr"/>
     </row>
     <row r="443">
       <c r="A443" s="5" t="n">
@@ -27739,7 +27300,6 @@
         <f>IF(G443&lt;&gt;F443,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I443" t="inlineStr"/>
     </row>
     <row r="444">
       <c r="A444" s="5" t="n">
@@ -27776,7 +27336,6 @@
         <f>IF(G444&lt;&gt;F444,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I444" t="inlineStr"/>
     </row>
     <row r="445">
       <c r="A445" s="5" t="n">
@@ -27813,7 +27372,6 @@
         <f>IF(G445&lt;&gt;F445,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I445" t="inlineStr"/>
     </row>
     <row r="446">
       <c r="A446" s="5" t="n">
@@ -27850,7 +27408,6 @@
         <f>IF(G446&lt;&gt;F446,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I446" t="inlineStr"/>
     </row>
     <row r="447">
       <c r="A447" s="5" t="n">
@@ -27887,7 +27444,6 @@
         <f>IF(G447&lt;&gt;F447,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I447" t="inlineStr"/>
     </row>
     <row r="448">
       <c r="A448" s="5" t="n">
@@ -27924,7 +27480,6 @@
         <f>IF(G448&lt;&gt;F448,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I448" t="inlineStr"/>
     </row>
     <row r="449">
       <c r="A449" s="5" t="n">
@@ -27961,7 +27516,6 @@
         <f>IF(G449&lt;&gt;F449,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I449" t="inlineStr"/>
     </row>
     <row r="450">
       <c r="A450" s="5" t="n">
@@ -27998,7 +27552,6 @@
         <f>IF(G450&lt;&gt;F450,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I450" t="inlineStr"/>
     </row>
     <row r="451">
       <c r="A451" s="5" t="n">
@@ -28035,7 +27588,6 @@
         <f>IF(G451&lt;&gt;F451,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I451" t="inlineStr"/>
     </row>
     <row r="452">
       <c r="A452" s="5" t="n">
@@ -28072,7 +27624,6 @@
         <f>IF(G452&lt;&gt;F452,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I452" t="inlineStr"/>
     </row>
     <row r="453">
       <c r="A453" s="5" t="n">
@@ -28109,7 +27660,6 @@
         <f>IF(G453&lt;&gt;F453,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I453" t="inlineStr"/>
     </row>
     <row r="454">
       <c r="A454" s="5" t="n">
@@ -28146,7 +27696,6 @@
         <f>IF(G454&lt;&gt;F454,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I454" t="inlineStr"/>
     </row>
     <row r="455">
       <c r="A455" s="5" t="n">
@@ -28183,7 +27732,6 @@
         <f>IF(G455&lt;&gt;F455,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I455" t="inlineStr"/>
     </row>
     <row r="456">
       <c r="A456" s="5" t="n">
@@ -28220,7 +27768,6 @@
         <f>IF(G456&lt;&gt;F456,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I456" t="inlineStr"/>
     </row>
     <row r="457">
       <c r="A457" s="5" t="n">
@@ -28257,7 +27804,6 @@
         <f>IF(G457&lt;&gt;F457,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I457" t="inlineStr"/>
     </row>
     <row r="458">
       <c r="A458" s="5" t="n">
@@ -28294,7 +27840,6 @@
         <f>IF(G458&lt;&gt;F458,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I458" t="inlineStr"/>
     </row>
     <row r="459">
       <c r="A459" s="5" t="n">
@@ -28331,7 +27876,6 @@
         <f>IF(G459&lt;&gt;F459,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I459" t="inlineStr"/>
     </row>
     <row r="460">
       <c r="A460" s="5" t="n">
@@ -28368,7 +27912,6 @@
         <f>IF(G460&lt;&gt;F460,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I460" t="inlineStr"/>
     </row>
     <row r="461">
       <c r="A461" s="5" t="n">
@@ -28405,7 +27948,6 @@
         <f>IF(G461&lt;&gt;F461,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I461" t="inlineStr"/>
     </row>
     <row r="462">
       <c r="A462" s="5" t="n">
@@ -28442,7 +27984,6 @@
         <f>IF(G462&lt;&gt;F462,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I462" t="inlineStr"/>
     </row>
     <row r="463">
       <c r="A463" s="5" t="n">
@@ -28479,7 +28020,6 @@
         <f>IF(G463&lt;&gt;F463,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I463" t="inlineStr"/>
     </row>
     <row r="464">
       <c r="A464" s="5" t="n">
@@ -28516,7 +28056,6 @@
         <f>IF(G464&lt;&gt;F464,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I464" t="inlineStr"/>
     </row>
     <row r="465">
       <c r="A465" s="5" t="n">
@@ -28553,7 +28092,6 @@
         <f>IF(G465&lt;&gt;F465,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I465" t="inlineStr"/>
     </row>
     <row r="466">
       <c r="A466" s="5" t="n">
@@ -28590,7 +28128,6 @@
         <f>IF(G466&lt;&gt;F466,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I466" t="inlineStr"/>
     </row>
     <row r="467">
       <c r="A467" s="5" t="n">
@@ -28627,7 +28164,6 @@
         <f>IF(G467&lt;&gt;F467,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I467" t="inlineStr"/>
     </row>
     <row r="468">
       <c r="A468" s="5" t="n">
@@ -28664,7 +28200,6 @@
         <f>IF(G468&lt;&gt;F468,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I468" t="inlineStr"/>
     </row>
     <row r="469">
       <c r="A469" s="5" t="n">
@@ -28701,7 +28236,6 @@
         <f>IF(G469&lt;&gt;F469,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I469" t="inlineStr"/>
     </row>
     <row r="470">
       <c r="A470" s="5" t="n">
@@ -28738,7 +28272,6 @@
         <f>IF(G470&lt;&gt;F470,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I470" t="inlineStr"/>
     </row>
     <row r="471">
       <c r="A471" s="5" t="n">
@@ -28775,7 +28308,6 @@
         <f>IF(G471&lt;&gt;F471,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I471" t="inlineStr"/>
     </row>
     <row r="472">
       <c r="A472" s="5" t="n">
@@ -28812,7 +28344,6 @@
         <f>IF(G472&lt;&gt;F472,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I472" t="inlineStr"/>
     </row>
     <row r="473">
       <c r="A473" s="5" t="n">
@@ -28849,7 +28380,6 @@
         <f>IF(G473&lt;&gt;F473,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I473" t="inlineStr"/>
     </row>
     <row r="474">
       <c r="A474" s="5" t="n">
@@ -28886,7 +28416,6 @@
         <f>IF(G474&lt;&gt;F474,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I474" t="inlineStr"/>
     </row>
     <row r="475">
       <c r="A475" s="5" t="n">
@@ -28923,7 +28452,6 @@
         <f>IF(G475&lt;&gt;F475,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I475" t="inlineStr"/>
     </row>
     <row r="476">
       <c r="A476" s="5" t="n">
@@ -28960,7 +28488,6 @@
         <f>IF(G476&lt;&gt;F476,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I476" t="inlineStr"/>
     </row>
     <row r="477">
       <c r="A477" s="5" t="n">
@@ -28997,7 +28524,6 @@
         <f>IF(G477&lt;&gt;F477,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I477" t="inlineStr"/>
     </row>
     <row r="478">
       <c r="A478" s="5" t="n">
@@ -29034,7 +28560,6 @@
         <f>IF(G478&lt;&gt;F478,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I478" t="inlineStr"/>
     </row>
     <row r="479">
       <c r="A479" s="5" t="n">
@@ -29071,7 +28596,6 @@
         <f>IF(G479&lt;&gt;F479,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I479" t="inlineStr"/>
     </row>
     <row r="480">
       <c r="A480" s="5" t="n">
@@ -29108,7 +28632,6 @@
         <f>IF(G480&lt;&gt;F480,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I480" t="inlineStr"/>
     </row>
     <row r="481">
       <c r="A481" s="5" t="n">
@@ -29145,7 +28668,6 @@
         <f>IF(G481&lt;&gt;F481,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I481" t="inlineStr"/>
     </row>
     <row r="482">
       <c r="A482" s="5" t="n">
@@ -29182,7 +28704,6 @@
         <f>IF(G482&lt;&gt;F482,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I482" t="inlineStr"/>
     </row>
     <row r="483">
       <c r="A483" s="5" t="n">
@@ -29219,7 +28740,6 @@
         <f>IF(G483&lt;&gt;F483,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I483" t="inlineStr"/>
     </row>
     <row r="484">
       <c r="A484" s="5" t="n">
@@ -29256,7 +28776,6 @@
         <f>IF(G484&lt;&gt;F484,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I484" t="inlineStr"/>
     </row>
     <row r="485">
       <c r="A485" s="5" t="n">
@@ -29293,7 +28812,6 @@
         <f>IF(G485&lt;&gt;F485,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I485" t="inlineStr"/>
     </row>
     <row r="486">
       <c r="A486" s="5" t="n">
@@ -29330,7 +28848,6 @@
         <f>IF(G486&lt;&gt;F486,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I486" t="inlineStr"/>
     </row>
     <row r="487">
       <c r="A487" s="5" t="n">
@@ -29367,7 +28884,6 @@
         <f>IF(G487&lt;&gt;F487,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I487" t="inlineStr"/>
     </row>
     <row r="488">
       <c r="A488" s="5" t="n">
@@ -29404,7 +28920,6 @@
         <f>IF(G488&lt;&gt;F488,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I488" t="inlineStr"/>
     </row>
     <row r="489">
       <c r="A489" s="5" t="n">
@@ -29441,7 +28956,6 @@
         <f>IF(G489&lt;&gt;F489,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I489" t="inlineStr"/>
     </row>
     <row r="490">
       <c r="A490" s="5" t="n">
@@ -29478,7 +28992,6 @@
         <f>IF(G490&lt;&gt;F490,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I490" t="inlineStr"/>
     </row>
     <row r="491">
       <c r="A491" s="5" t="n">
@@ -29515,7 +29028,6 @@
         <f>IF(G491&lt;&gt;F491,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I491" t="inlineStr"/>
     </row>
     <row r="492">
       <c r="A492" s="5" t="n">
@@ -29552,7 +29064,6 @@
         <f>IF(G492&lt;&gt;F492,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I492" t="inlineStr"/>
     </row>
     <row r="493">
       <c r="A493" s="5" t="n">
@@ -29589,7 +29100,6 @@
         <f>IF(G493&lt;&gt;F493,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I493" t="inlineStr"/>
     </row>
     <row r="494">
       <c r="A494" s="5" t="n">
@@ -29626,7 +29136,6 @@
         <f>IF(G494&lt;&gt;F494,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I494" t="inlineStr"/>
     </row>
     <row r="495">
       <c r="A495" s="5" t="n">
@@ -29663,7 +29172,6 @@
         <f>IF(G495&lt;&gt;F495,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I495" t="inlineStr"/>
     </row>
     <row r="496">
       <c r="A496" s="5" t="n">
@@ -29700,7 +29208,6 @@
         <f>IF(G496&lt;&gt;F496,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I496" t="inlineStr"/>
     </row>
     <row r="497">
       <c r="A497" s="5" t="n">
@@ -29737,7 +29244,6 @@
         <f>IF(G497&lt;&gt;F497,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I497" t="inlineStr"/>
     </row>
     <row r="498">
       <c r="A498" s="5" t="n">
@@ -29774,7 +29280,6 @@
         <f>IF(G498&lt;&gt;F498,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I498" t="inlineStr"/>
     </row>
     <row r="499">
       <c r="A499" s="5" t="n">
@@ -29811,7 +29316,6 @@
         <f>IF(G499&lt;&gt;F499,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I499" t="inlineStr"/>
     </row>
     <row r="500">
       <c r="A500" s="5" t="n">
@@ -29848,7 +29352,6 @@
         <f>IF(G500&lt;&gt;F500,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I500" t="inlineStr"/>
     </row>
     <row r="501">
       <c r="A501" s="5" t="n">
@@ -29885,7 +29388,6 @@
         <f>IF(G501&lt;&gt;F501,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I501" t="inlineStr"/>
     </row>
     <row r="502">
       <c r="A502" s="5" t="n">
@@ -29922,7 +29424,6 @@
         <f>IF(G502&lt;&gt;F502,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I502" t="inlineStr"/>
     </row>
     <row r="503">
       <c r="A503" s="5" t="n">
@@ -29959,7 +29460,6 @@
         <f>IF(G503&lt;&gt;F503,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I503" t="inlineStr"/>
     </row>
     <row r="504">
       <c r="A504" s="5" t="n">
@@ -29996,7 +29496,6 @@
         <f>IF(G504&lt;&gt;F504,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I504" t="inlineStr"/>
     </row>
     <row r="505">
       <c r="A505" s="5" t="n">
@@ -30033,7 +29532,6 @@
         <f>IF(G505&lt;&gt;F505,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I505" t="inlineStr"/>
     </row>
     <row r="506">
       <c r="A506" s="5" t="n">
@@ -30070,7 +29568,6 @@
         <f>IF(G506&lt;&gt;F506,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I506" t="inlineStr"/>
     </row>
     <row r="507">
       <c r="A507" s="5" t="n">
@@ -30107,7 +29604,6 @@
         <f>IF(G507&lt;&gt;F507,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I507" t="inlineStr"/>
     </row>
     <row r="508">
       <c r="A508" s="5" t="n">
@@ -30144,7 +29640,6 @@
         <f>IF(G508&lt;&gt;F508,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I508" t="inlineStr"/>
     </row>
     <row r="509">
       <c r="A509" s="5" t="n">
@@ -30181,7 +29676,6 @@
         <f>IF(G509&lt;&gt;F509,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I509" t="inlineStr"/>
     </row>
     <row r="510">
       <c r="A510" s="5" t="n">
@@ -30218,7 +29712,6 @@
         <f>IF(G510&lt;&gt;F510,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I510" t="inlineStr"/>
     </row>
     <row r="511">
       <c r="A511" s="5" t="n">
@@ -30255,7 +29748,6 @@
         <f>IF(G511&lt;&gt;F511,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I511" t="inlineStr"/>
     </row>
     <row r="512">
       <c r="A512" s="5" t="n">
@@ -30292,7 +29784,6 @@
         <f>IF(G512&lt;&gt;F512,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I512" t="inlineStr"/>
     </row>
     <row r="513">
       <c r="A513" s="5" t="n">
@@ -30329,7 +29820,6 @@
         <f>IF(G513&lt;&gt;F513,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I513" t="inlineStr"/>
     </row>
     <row r="514">
       <c r="A514" s="5" t="n">
@@ -30366,7 +29856,6 @@
         <f>IF(G514&lt;&gt;F514,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I514" t="inlineStr"/>
     </row>
     <row r="515">
       <c r="A515" s="5" t="n">
@@ -30403,7 +29892,6 @@
         <f>IF(G515&lt;&gt;F515,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I515" t="inlineStr"/>
     </row>
     <row r="516">
       <c r="A516" s="5" t="n">
@@ -30440,7 +29928,6 @@
         <f>IF(G516&lt;&gt;F516,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I516" t="inlineStr"/>
     </row>
     <row r="517">
       <c r="A517" s="5" t="n">
@@ -30477,7 +29964,6 @@
         <f>IF(G517&lt;&gt;F517,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I517" t="inlineStr"/>
     </row>
     <row r="518">
       <c r="A518" s="5" t="n">
@@ -30514,7 +30000,6 @@
         <f>IF(G518&lt;&gt;F518,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I518" t="inlineStr"/>
     </row>
     <row r="519">
       <c r="A519" s="5" t="n">
@@ -30551,7 +30036,6 @@
         <f>IF(G519&lt;&gt;F519,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I519" t="inlineStr"/>
     </row>
     <row r="520">
       <c r="A520" s="5" t="n">
@@ -30588,7 +30072,6 @@
         <f>IF(G520&lt;&gt;F520,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I520" t="inlineStr"/>
     </row>
     <row r="521">
       <c r="A521" s="5" t="n">
@@ -30625,7 +30108,6 @@
         <f>IF(G521&lt;&gt;F521,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I521" t="inlineStr"/>
     </row>
     <row r="522">
       <c r="A522" s="5" t="n">
@@ -30662,7 +30144,6 @@
         <f>IF(G522&lt;&gt;F522,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I522" t="inlineStr"/>
     </row>
     <row r="523">
       <c r="A523" s="5" t="n">
@@ -30699,7 +30180,6 @@
         <f>IF(G523&lt;&gt;F523,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I523" t="inlineStr"/>
     </row>
     <row r="524">
       <c r="A524" s="5" t="n">
@@ -30736,7 +30216,6 @@
         <f>IF(G524&lt;&gt;F524,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I524" t="inlineStr"/>
     </row>
     <row r="525">
       <c r="A525" s="5" t="n">
@@ -30773,7 +30252,6 @@
         <f>IF(G525&lt;&gt;F525,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I525" t="inlineStr"/>
     </row>
     <row r="526">
       <c r="A526" s="5" t="n">
@@ -30810,7 +30288,6 @@
         <f>IF(G526&lt;&gt;F526,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I526" t="inlineStr"/>
     </row>
     <row r="527">
       <c r="A527" s="5" t="n">
@@ -30847,7 +30324,6 @@
         <f>IF(G527&lt;&gt;F527,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I527" t="inlineStr"/>
     </row>
     <row r="528">
       <c r="A528" s="5" t="n">
@@ -30884,7 +30360,6 @@
         <f>IF(G528&lt;&gt;F528,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I528" t="inlineStr"/>
     </row>
     <row r="529">
       <c r="A529" s="5" t="n">
@@ -30921,7 +30396,6 @@
         <f>IF(G529&lt;&gt;F529,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I529" t="inlineStr"/>
     </row>
     <row r="530">
       <c r="A530" s="5" t="n">
@@ -30958,7 +30432,6 @@
         <f>IF(G530&lt;&gt;F530,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I530" t="inlineStr"/>
     </row>
     <row r="531">
       <c r="A531" s="5" t="n">
@@ -30995,7 +30468,6 @@
         <f>IF(G531&lt;&gt;F531,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I531" t="inlineStr"/>
     </row>
     <row r="532">
       <c r="A532" s="5" t="n">
@@ -31032,7 +30504,6 @@
         <f>IF(G532&lt;&gt;F532,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I532" t="inlineStr"/>
     </row>
     <row r="533">
       <c r="A533" s="5" t="n">
@@ -31069,7 +30540,6 @@
         <f>IF(G533&lt;&gt;F533,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I533" t="inlineStr"/>
     </row>
     <row r="534">
       <c r="A534" s="5" t="n">
@@ -31106,7 +30576,6 @@
         <f>IF(G534&lt;&gt;F534,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I534" t="inlineStr"/>
     </row>
     <row r="535">
       <c r="A535" s="5" t="n">
@@ -31143,7 +30612,6 @@
         <f>IF(G535&lt;&gt;F535,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I535" t="inlineStr"/>
     </row>
     <row r="536">
       <c r="A536" s="5" t="n">
@@ -31180,7 +30648,6 @@
         <f>IF(G536&lt;&gt;F536,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I536" t="inlineStr"/>
     </row>
     <row r="537">
       <c r="A537" s="5" t="n">
@@ -31217,7 +30684,6 @@
         <f>IF(G537&lt;&gt;F537,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I537" t="inlineStr"/>
     </row>
     <row r="538">
       <c r="A538" s="5" t="n">
@@ -31254,7 +30720,6 @@
         <f>IF(G538&lt;&gt;F538,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I538" t="inlineStr"/>
     </row>
     <row r="539">
       <c r="A539" s="5" t="n">
@@ -31291,7 +30756,6 @@
         <f>IF(G539&lt;&gt;F539,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I539" t="inlineStr"/>
     </row>
     <row r="540">
       <c r="A540" s="5" t="n">
@@ -31328,7 +30792,6 @@
         <f>IF(G540&lt;&gt;F540,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I540" t="inlineStr"/>
     </row>
     <row r="541">
       <c r="A541" s="5" t="n">
@@ -31365,7 +30828,6 @@
         <f>IF(G541&lt;&gt;F541,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I541" t="inlineStr"/>
     </row>
     <row r="542">
       <c r="A542" s="5" t="n">
@@ -31402,7 +30864,6 @@
         <f>IF(G542&lt;&gt;F542,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I542" t="inlineStr"/>
     </row>
     <row r="543">
       <c r="A543" s="5" t="n">
@@ -31439,7 +30900,6 @@
         <f>IF(G543&lt;&gt;F543,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I543" t="inlineStr"/>
     </row>
     <row r="544">
       <c r="A544" s="5" t="n">
@@ -31476,7 +30936,6 @@
         <f>IF(G544&lt;&gt;F544,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I544" t="inlineStr"/>
     </row>
     <row r="545">
       <c r="A545" s="5" t="n">
@@ -31513,7 +30972,6 @@
         <f>IF(G545&lt;&gt;F545,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I545" t="inlineStr"/>
     </row>
     <row r="546">
       <c r="A546" s="5" t="n">
@@ -31550,7 +31008,6 @@
         <f>IF(G546&lt;&gt;F546,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I546" t="inlineStr"/>
     </row>
     <row r="547">
       <c r="A547" s="5" t="n">
@@ -31587,7 +31044,6 @@
         <f>IF(G547&lt;&gt;F547,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I547" t="inlineStr"/>
     </row>
     <row r="548">
       <c r="A548" s="5" t="n">
@@ -31624,7 +31080,6 @@
         <f>IF(G548&lt;&gt;F548,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I548" t="inlineStr"/>
     </row>
     <row r="549">
       <c r="A549" s="5" t="n">
@@ -31661,7 +31116,6 @@
         <f>IF(G549&lt;&gt;F549,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I549" t="inlineStr"/>
     </row>
     <row r="550">
       <c r="A550" s="5" t="n">
@@ -31698,7 +31152,6 @@
         <f>IF(G550&lt;&gt;F550,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I550" t="inlineStr"/>
     </row>
     <row r="551">
       <c r="A551" s="5" t="n">
@@ -31735,7 +31188,6 @@
         <f>IF(G551&lt;&gt;F551,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I551" t="inlineStr"/>
     </row>
     <row r="552">
       <c r="A552" s="5" t="n">
@@ -31772,7 +31224,6 @@
         <f>IF(G552&lt;&gt;F552,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I552" t="inlineStr"/>
     </row>
     <row r="553">
       <c r="A553" s="5" t="n">
@@ -31809,7 +31260,6 @@
         <f>IF(G553&lt;&gt;F553,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I553" t="inlineStr"/>
     </row>
     <row r="554">
       <c r="A554" s="5" t="n">
@@ -31846,7 +31296,6 @@
         <f>IF(G554&lt;&gt;F554,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I554" t="inlineStr"/>
     </row>
     <row r="555">
       <c r="A555" s="5" t="n">
@@ -31883,7 +31332,6 @@
         <f>IF(G555&lt;&gt;F555,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I555" t="inlineStr"/>
     </row>
     <row r="556">
       <c r="A556" s="5" t="n">
@@ -31920,7 +31368,6 @@
         <f>IF(G556&lt;&gt;F556,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I556" t="inlineStr"/>
     </row>
     <row r="557">
       <c r="A557" s="5" t="n">
@@ -31957,7 +31404,6 @@
         <f>IF(G557&lt;&gt;F557,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I557" t="inlineStr"/>
     </row>
     <row r="558">
       <c r="A558" s="5" t="n">
@@ -31994,7 +31440,6 @@
         <f>IF(G558&lt;&gt;F558,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I558" t="inlineStr"/>
     </row>
     <row r="559">
       <c r="A559" s="5" t="n">
@@ -32031,7 +31476,6 @@
         <f>IF(G559&lt;&gt;F559,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I559" t="inlineStr"/>
     </row>
     <row r="560">
       <c r="A560" s="5" t="n">
@@ -32068,7 +31512,6 @@
         <f>IF(G560&lt;&gt;F560,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I560" t="inlineStr"/>
     </row>
     <row r="561">
       <c r="A561" s="5" t="n">
@@ -32105,7 +31548,6 @@
         <f>IF(G561&lt;&gt;F561,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I561" t="inlineStr"/>
     </row>
     <row r="562">
       <c r="A562" s="5" t="n">
@@ -32142,7 +31584,6 @@
         <f>IF(G562&lt;&gt;F562,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I562" t="inlineStr"/>
     </row>
     <row r="563">
       <c r="A563" s="5" t="n">
@@ -32179,7 +31620,6 @@
         <f>IF(G563&lt;&gt;F563,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I563" t="inlineStr"/>
     </row>
     <row r="564">
       <c r="A564" s="5" t="n">
@@ -32216,7 +31656,6 @@
         <f>IF(G564&lt;&gt;F564,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I564" t="inlineStr"/>
     </row>
     <row r="565">
       <c r="A565" s="5" t="n">
@@ -32253,7 +31692,6 @@
         <f>IF(G565&lt;&gt;F565,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I565" t="inlineStr"/>
     </row>
     <row r="566">
       <c r="A566" s="5" t="n">
@@ -32290,7 +31728,6 @@
         <f>IF(G566&lt;&gt;F566,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I566" t="inlineStr"/>
     </row>
     <row r="567">
       <c r="A567" s="5" t="n">
@@ -32327,7 +31764,6 @@
         <f>IF(G567&lt;&gt;F567,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I567" t="inlineStr"/>
     </row>
     <row r="568">
       <c r="A568" s="5" t="n">
@@ -32364,7 +31800,6 @@
         <f>IF(G568&lt;&gt;F568,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I568" t="inlineStr"/>
     </row>
     <row r="569">
       <c r="A569" s="5" t="n">
@@ -32401,7 +31836,6 @@
         <f>IF(G569&lt;&gt;F569,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I569" t="inlineStr"/>
     </row>
     <row r="570">
       <c r="A570" s="5" t="n">
@@ -32438,7 +31872,6 @@
         <f>IF(G570&lt;&gt;F570,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I570" t="inlineStr"/>
     </row>
     <row r="571">
       <c r="A571" s="5" t="n">
@@ -32475,7 +31908,6 @@
         <f>IF(G571&lt;&gt;F571,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I571" t="inlineStr"/>
     </row>
     <row r="572">
       <c r="A572" s="5" t="n">
@@ -32512,7 +31944,6 @@
         <f>IF(G572&lt;&gt;F572,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I572" t="inlineStr"/>
     </row>
     <row r="573">
       <c r="A573" s="5" t="n">
@@ -32549,7 +31980,6 @@
         <f>IF(G573&lt;&gt;F573,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I573" t="inlineStr"/>
     </row>
     <row r="574">
       <c r="A574" s="5" t="n">
@@ -32586,7 +32016,6 @@
         <f>IF(G574&lt;&gt;F574,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I574" t="inlineStr"/>
     </row>
     <row r="575">
       <c r="A575" s="5" t="n">
@@ -32623,7 +32052,6 @@
         <f>IF(G575&lt;&gt;F575,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I575" t="inlineStr"/>
     </row>
     <row r="576">
       <c r="A576" s="5" t="n">
@@ -32660,7 +32088,6 @@
         <f>IF(G576&lt;&gt;F576,"YES","NO")</f>
         <v/>
       </c>
-      <c r="I576" t="inlineStr"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A2:I2">
@@ -35569,15 +34996,11 @@
     <row r="1">
       <c r="A1" s="7" t="inlineStr">
         <is>
-          <t>ALL PRO METRO EAST CONSTRUCTION LLC - Profit &amp; Loss 2025</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr"/>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr"/>
-      <c r="B2" t="inlineStr"/>
-    </row>
+          <t>AllPro Construction &amp; Landscape - Profit &amp; Loss 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
@@ -36041,6 +35464,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
         <is>
@@ -36048,6 +35472,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
@@ -36070,6 +35495,7 @@
         <v/>
       </c>
     </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
@@ -36746,6 +36172,7 @@
         <v/>
       </c>
     </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" s="8" t="inlineStr">
         <is>
